--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="766" firstSheet="1" activeTab="6"/>
+    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="766" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="TacticsComand" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="729">
   <si>
     <t>Id</t>
   </si>
@@ -331,7 +331,7 @@
     <t>HavingArtifactMinus</t>
   </si>
   <si>
-    <t>アーティファクト所有移動時評価値減少値</t>
+    <t>アーティファクト所有数毎の評価値減少値</t>
   </si>
   <si>
     <t>ChangeArtifactCurrency</t>
@@ -344,6 +344,12 @@
   </si>
   <si>
     <t>はずすの装備Id</t>
+  </si>
+  <si>
+    <t>BaseGetExp</t>
+  </si>
+  <si>
+    <t>バトル基礎獲得Exp</t>
   </si>
   <si>
     <t>Text</t>
@@ -1129,6 +1135,9 @@
     <t>The item you found is an artifact. 
 All artifacts rightfully belong to Lord Odin. 
 Keeping this artifact will lower your Evaluation.</t>
+  </si>
+  <si>
+    <t>アーティファクトを持ち込んだため評価値が減少しました！</t>
   </si>
   <si>
     <t>エインフェリアを招聘しますか？
@@ -2219,9 +2228,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -2246,7 +2255,128 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2261,129 +2391,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2398,7 +2407,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2410,97 +2545,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2518,67 +2563,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2589,15 +2598,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2634,8 +2634,26 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2647,21 +2665,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2681,11 +2684,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2697,145 +2706,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5595,7 +5604,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="20.5454545454545" customWidth="1"/>
@@ -5703,7 +5712,7 @@
         <v>102</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
         <v>103</v>
@@ -5729,6 +5738,17 @@
       </c>
       <c r="C14" t="s">
         <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -5740,7 +5760,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I334"/>
+  <dimension ref="A1:I335"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.54545454545455" customWidth="1"/>
@@ -5757,16 +5777,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5774,16 +5794,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -5791,16 +5811,16 @@
         <v>400</v>
       </c>
       <c r="B3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -5808,16 +5828,16 @@
         <v>401</v>
       </c>
       <c r="B4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5825,16 +5845,16 @@
         <v>402</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:7">
@@ -5842,16 +5862,16 @@
         <v>403</v>
       </c>
       <c r="B6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:7">
@@ -5859,16 +5879,16 @@
         <v>404</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:7">
@@ -5876,16 +5896,16 @@
         <v>405</v>
       </c>
       <c r="B8" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -5893,19 +5913,19 @@
         <v>600</v>
       </c>
       <c r="B9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5913,16 +5933,16 @@
         <v>601</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -5930,16 +5950,16 @@
         <v>602</v>
       </c>
       <c r="B11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G11" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -5947,16 +5967,16 @@
         <v>603</v>
       </c>
       <c r="B12" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F12" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5964,16 +5984,16 @@
         <v>606</v>
       </c>
       <c r="B13" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F13" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -5981,16 +6001,16 @@
         <v>611</v>
       </c>
       <c r="B14" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G14" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -5998,16 +6018,16 @@
         <v>620</v>
       </c>
       <c r="B15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -6015,16 +6035,16 @@
         <v>621</v>
       </c>
       <c r="B16" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F16" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G16" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -6032,16 +6052,16 @@
         <v>622</v>
       </c>
       <c r="B17" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F17" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G17" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -6049,16 +6069,16 @@
         <v>623</v>
       </c>
       <c r="B18" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -6066,16 +6086,16 @@
         <v>624</v>
       </c>
       <c r="B19" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -6083,16 +6103,16 @@
         <v>625</v>
       </c>
       <c r="B20" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F20" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G20" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -6100,16 +6120,16 @@
         <v>651</v>
       </c>
       <c r="B21" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F21" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -6117,16 +6137,16 @@
         <v>652</v>
       </c>
       <c r="B22" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F22" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G22" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -6134,16 +6154,16 @@
         <v>1000</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G23" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -6151,19 +6171,19 @@
         <v>2000</v>
       </c>
       <c r="B24" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F24" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G24" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H24" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -6171,16 +6191,16 @@
         <v>2001</v>
       </c>
       <c r="B25" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F25" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G25" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -6188,16 +6208,16 @@
         <v>2002</v>
       </c>
       <c r="B26" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C26" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F26" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G26" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -6205,16 +6225,16 @@
         <v>2003</v>
       </c>
       <c r="B27" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F27" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G27" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -6222,16 +6242,16 @@
         <v>2004</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -6239,16 +6259,16 @@
         <v>2005</v>
       </c>
       <c r="B29" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F29" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G29" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -6256,16 +6276,16 @@
         <v>2006</v>
       </c>
       <c r="B30" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F30" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G30" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -6273,16 +6293,16 @@
         <v>2007</v>
       </c>
       <c r="B31" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F31" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G31" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -6290,19 +6310,19 @@
         <v>2100</v>
       </c>
       <c r="B32" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F32" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G32" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H32" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -6310,16 +6330,16 @@
         <v>2101</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -6327,16 +6347,16 @@
         <v>2102</v>
       </c>
       <c r="B34" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F34" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G34" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -6344,16 +6364,16 @@
         <v>2103</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C35" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F35" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G35" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -6361,16 +6381,16 @@
         <v>2104</v>
       </c>
       <c r="B36" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C36" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F36" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G36" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -6378,16 +6398,16 @@
         <v>2105</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C37" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G37" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -6395,16 +6415,16 @@
         <v>2106</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C38" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G38" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -6412,19 +6432,19 @@
         <v>2200</v>
       </c>
       <c r="B39" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C39" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F39" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G39" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -6432,16 +6452,16 @@
         <v>2210</v>
       </c>
       <c r="B40" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C40" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F40" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G40" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -6449,16 +6469,16 @@
         <v>2220</v>
       </c>
       <c r="B41" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C41" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F41" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G41" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -6466,16 +6486,16 @@
         <v>2300</v>
       </c>
       <c r="B42" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C42" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F42" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G42" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -6483,16 +6503,16 @@
         <v>2310</v>
       </c>
       <c r="B43" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C43" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F43" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G43" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -6500,16 +6520,16 @@
         <v>2320</v>
       </c>
       <c r="B44" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C44" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F44" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G44" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -6517,16 +6537,16 @@
         <v>2330</v>
       </c>
       <c r="B45" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C45" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F45" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G45" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -6534,16 +6554,16 @@
         <v>2340</v>
       </c>
       <c r="B46" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C46" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F46" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G46" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -6551,16 +6571,16 @@
         <v>2400</v>
       </c>
       <c r="B47" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C47" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F47" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G47" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -6568,16 +6588,16 @@
         <v>2410</v>
       </c>
       <c r="B48" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C48" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F48" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G48" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -6585,16 +6605,16 @@
         <v>2420</v>
       </c>
       <c r="B49" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C49" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F49" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G49" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -6602,16 +6622,16 @@
         <v>2430</v>
       </c>
       <c r="B50" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C50" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F50" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G50" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -6619,16 +6639,16 @@
         <v>2440</v>
       </c>
       <c r="B51" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C51" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F51" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G51" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -6636,16 +6656,16 @@
         <v>2500</v>
       </c>
       <c r="B52" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C52" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F52" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G52" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:7">
@@ -6653,16 +6673,16 @@
         <v>2510</v>
       </c>
       <c r="B53" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F53" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G53" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:7">
@@ -6670,16 +6690,16 @@
         <v>2520</v>
       </c>
       <c r="B54" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C54" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F54" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G54" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:7">
@@ -6687,16 +6707,16 @@
         <v>2530</v>
       </c>
       <c r="B55" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C55" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F55" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G55" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -6704,16 +6724,16 @@
         <v>2610</v>
       </c>
       <c r="B56" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C56" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F56" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G56" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -6721,19 +6741,19 @@
         <v>3010</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G57" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H57" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -6741,16 +6761,16 @@
         <v>3020</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C58" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G58" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:7">
@@ -6758,16 +6778,16 @@
         <v>3030</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C59" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G59" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:7">
@@ -6775,16 +6795,16 @@
         <v>3031</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G60" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -6792,16 +6812,16 @@
         <v>3040</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C61" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G61" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -6812,13 +6832,13 @@
         <v>38</v>
       </c>
       <c r="C62" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G62" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -6826,16 +6846,16 @@
         <v>3051</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C63" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G63" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -6843,16 +6863,16 @@
         <v>3052</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C64" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G64" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -6860,16 +6880,16 @@
         <v>3100</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C65" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G65" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -6877,16 +6897,16 @@
         <v>3110</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C66" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G66" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -6894,16 +6914,16 @@
         <v>3120</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C67" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G67" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -6911,16 +6931,16 @@
         <v>3130</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C68" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G68" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:7">
@@ -6928,16 +6948,16 @@
         <v>3140</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C69" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G69" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:7">
@@ -6945,16 +6965,16 @@
         <v>3150</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C70" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G70" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -6962,16 +6982,16 @@
         <v>3200</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C71" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G71" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -6979,16 +6999,16 @@
         <v>3210</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C72" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G72" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -6996,19 +7016,19 @@
         <v>6001</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C73" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G73" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H73" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -7016,16 +7036,16 @@
         <v>6002</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C74" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="G74" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -7033,16 +7053,16 @@
         <v>6100</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C75" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -7050,16 +7070,16 @@
         <v>6010</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C76" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G76" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -7067,16 +7087,16 @@
         <v>6011</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C77" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G77" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -7084,16 +7104,16 @@
         <v>6012</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C78" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G78" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -7101,16 +7121,16 @@
         <v>6020</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C79" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G79" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -7118,16 +7138,16 @@
         <v>6030</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C80" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G80" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -7135,16 +7155,16 @@
         <v>6040</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C81" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G81" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="1:7">
@@ -7152,16 +7172,16 @@
         <v>6050</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C82" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="G82" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:7">
@@ -7169,16 +7189,16 @@
         <v>6051</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C83" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G83" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:7">
@@ -7186,16 +7206,16 @@
         <v>6052</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C84" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G84" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -7203,16 +7223,16 @@
         <v>6210</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C85" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G85" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -7220,16 +7240,16 @@
         <v>6220</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C86" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G86" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -7237,16 +7257,16 @@
         <v>6230</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C87" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G87" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -7254,16 +7274,16 @@
         <v>6240</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C88" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G88" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -7271,16 +7291,16 @@
         <v>6250</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C89" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G89" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -7288,16 +7308,16 @@
         <v>6260</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C90" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G90" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -7305,16 +7325,16 @@
         <v>6270</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C91" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G91" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -7322,16 +7342,16 @@
         <v>6280</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C92" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G92" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="93" customFormat="1" spans="1:7">
@@ -7339,16 +7359,16 @@
         <v>6290</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C93" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G93" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:7">
@@ -7356,16 +7376,16 @@
         <v>6300</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C94" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G94" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -7373,16 +7393,16 @@
         <v>6810</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C95" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G95" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -7390,16 +7410,16 @@
         <v>6820</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C96" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G96" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -7407,16 +7427,16 @@
         <v>6830</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C97" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G97" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -7424,16 +7444,16 @@
         <v>6840</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C98" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G98" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -7441,16 +7461,16 @@
         <v>6850</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C99" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G99" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -7458,16 +7478,16 @@
         <v>6860</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C100" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G100" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -7475,16 +7495,16 @@
         <v>6870</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C101" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G101" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -7492,16 +7512,16 @@
         <v>6880</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C102" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G102" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -7509,16 +7529,16 @@
         <v>6890</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C103" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G103" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="104" customFormat="1" spans="1:7">
@@ -7526,16 +7546,16 @@
         <v>6900</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C104" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G104" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:7">
@@ -7543,16 +7563,16 @@
         <v>6910</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C105" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G105" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -7560,19 +7580,19 @@
         <v>10010</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C106" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G106" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H106" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -7580,16 +7600,16 @@
         <v>10100</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C107" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="G107" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -7597,16 +7617,16 @@
         <v>10101</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C108" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G108" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -7614,16 +7634,16 @@
         <v>10110</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C109" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G109" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -7631,16 +7651,16 @@
         <v>10120</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C110" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G110" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -7648,16 +7668,16 @@
         <v>10121</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C111" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G111" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -7665,16 +7685,16 @@
         <v>10130</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C112" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G112" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -7682,16 +7702,16 @@
         <v>10131</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C113" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G113" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="114" ht="26" spans="1:7">
@@ -7699,16 +7719,16 @@
         <v>10132</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C114" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G114" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="115" ht="26" spans="1:7">
@@ -7716,16 +7736,16 @@
         <v>10133</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C115" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G115" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -7733,16 +7753,16 @@
         <v>10140</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C116" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G116" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -7750,16 +7770,16 @@
         <v>10141</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C117" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G117" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="118" customFormat="1" spans="1:7">
@@ -7767,16 +7787,16 @@
         <v>10142</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C118" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G118" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="119" customFormat="1" spans="1:7">
@@ -7784,16 +7804,16 @@
         <v>10143</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C119" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G119" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -7801,16 +7821,16 @@
         <v>10150</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C120" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G120" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -7818,16 +7838,16 @@
         <v>10160</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C121" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G121" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="122" customFormat="1" spans="1:7">
@@ -7835,16 +7855,16 @@
         <v>10170</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C122" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G122" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="123" customFormat="1" spans="1:7">
@@ -7852,16 +7872,16 @@
         <v>10171</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C123" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G123" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="124" customFormat="1" ht="26" spans="1:7">
@@ -7869,16 +7889,16 @@
         <v>10180</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C124" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G124" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="125" customFormat="1" spans="1:7">
@@ -7886,16 +7906,16 @@
         <v>10181</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C125" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G125" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="126" customFormat="1" ht="26" spans="1:7">
@@ -7903,16 +7923,16 @@
         <v>10182</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C126" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G126" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="127" customFormat="1" spans="1:7">
@@ -7920,16 +7940,16 @@
         <v>10190</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C127" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G127" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="128" customFormat="1" ht="26" spans="1:7">
@@ -7937,16 +7957,16 @@
         <v>10200</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C128" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G128" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="129" customFormat="1" spans="1:7">
@@ -7954,16 +7974,16 @@
         <v>10210</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C129" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G129" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="130" customFormat="1" spans="1:7">
@@ -7971,16 +7991,16 @@
         <v>10220</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C130" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G130" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="131" customFormat="1" ht="52" spans="1:7">
@@ -7988,3504 +8008,3521 @@
         <v>10230</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C131" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G131" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="132" ht="26" spans="1:8">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="132" customFormat="1" spans="1:7">
       <c r="A132">
+        <v>10240</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="C132" t="s">
+        <v>114</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G132" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="133" ht="26" spans="1:8">
+      <c r="A133">
         <v>11010</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C132" t="s">
-        <v>112</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="G132" t="s">
-        <v>112</v>
-      </c>
-      <c r="H132" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="133" ht="26" spans="1:7">
-      <c r="A133">
-        <v>11011</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>371</v>
       </c>
       <c r="C133" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>372</v>
       </c>
       <c r="G133" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="134" customFormat="1" spans="1:7">
+        <v>114</v>
+      </c>
+      <c r="H133" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="134" ht="26" spans="1:7">
       <c r="A134">
-        <v>11012</v>
+        <v>11011</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C134" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G134" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="135" customFormat="1" spans="1:7">
       <c r="A135">
-        <v>11013</v>
+        <v>11012</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C135" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G135" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="136" customFormat="1" spans="1:7">
       <c r="A136">
+        <v>11013</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="C136" t="s">
+        <v>114</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="G136" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="137" customFormat="1" spans="1:7">
+      <c r="A137">
         <v>11014</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="C136" t="s">
-        <v>112</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="G136" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7">
-      <c r="A137">
+      <c r="B137" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="C137" t="s">
+        <v>114</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="G137" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138">
         <v>11020</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="C137" t="s">
-        <v>112</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="G137" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="138" customFormat="1" spans="1:7">
-      <c r="A138">
+      <c r="B138" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C138" t="s">
+        <v>114</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="G138" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="139" customFormat="1" spans="1:7">
+      <c r="A139">
         <v>11030</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="C138" t="s">
-        <v>112</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="G138" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7">
-      <c r="A139">
+      <c r="B139" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C139" t="s">
+        <v>114</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="G139" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140">
         <v>11040</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="C139" t="s">
-        <v>112</v>
-      </c>
-      <c r="F139" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="G139" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="140" customFormat="1" spans="1:7">
-      <c r="A140">
-        <v>11050</v>
-      </c>
       <c r="B140" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C140" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G140" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="141" customFormat="1" spans="1:7">
       <c r="A141">
-        <v>11060</v>
+        <v>11050</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C141" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G141" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="142" customFormat="1" spans="1:7">
       <c r="A142">
+        <v>11060</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C142" t="s">
+        <v>114</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="G142" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="143" customFormat="1" spans="1:7">
+      <c r="A143">
         <v>11070</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="C142" t="s">
-        <v>112</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="G142" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="143" ht="52" spans="1:8">
-      <c r="A143">
+      <c r="B143" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C143" t="s">
+        <v>114</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="G143" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="144" ht="52" spans="1:8">
+      <c r="A144">
         <v>12010</v>
       </c>
-      <c r="B143" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C143" t="s">
-        <v>112</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="G143" t="s">
-        <v>112</v>
-      </c>
-      <c r="H143" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8">
-      <c r="A144">
+      <c r="B144" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C144" t="s">
+        <v>114</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="G144" t="s">
+        <v>114</v>
+      </c>
+      <c r="H144" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145">
         <v>13010</v>
       </c>
-      <c r="B144" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="C144" t="s">
-        <v>112</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="G144" t="s">
-        <v>112</v>
-      </c>
-      <c r="H144" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7">
-      <c r="A145">
-        <v>13020</v>
-      </c>
       <c r="B145" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C145" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>397</v>
       </c>
       <c r="G145" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="H145" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146">
-        <v>13110</v>
-      </c>
-      <c r="B146" t="s">
-        <v>398</v>
+        <v>13020</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>399</v>
       </c>
       <c r="C146" t="s">
-        <v>112</v>
-      </c>
-      <c r="F146" t="s">
-        <v>398</v>
+        <v>114</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>400</v>
       </c>
       <c r="G146" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147">
-        <v>13210</v>
-      </c>
-      <c r="B147" s="1" t="s">
-        <v>399</v>
+        <v>13110</v>
+      </c>
+      <c r="B147" t="s">
+        <v>401</v>
       </c>
       <c r="C147" t="s">
-        <v>112</v>
-      </c>
-      <c r="F147" s="1" t="s">
-        <v>400</v>
+        <v>114</v>
+      </c>
+      <c r="F147" t="s">
+        <v>401</v>
       </c>
       <c r="G147" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="148" spans="1:7">
       <c r="A148">
-        <v>13220</v>
+        <v>13210</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C148" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G148" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="149" spans="1:7">
       <c r="A149">
-        <v>13230</v>
+        <v>13220</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C149" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G149" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="150" spans="1:7">
       <c r="A150">
+        <v>13230</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="C150" t="s">
+        <v>114</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="G150" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151">
         <v>13320</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="C150" t="s">
-        <v>112</v>
-      </c>
-      <c r="F150" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="G150" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="151" customFormat="1" spans="1:7">
-      <c r="A151">
+      <c r="B151" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C151" t="s">
+        <v>114</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="G151" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="152" customFormat="1" spans="1:7">
+      <c r="A152">
         <v>13410</v>
       </c>
-      <c r="B151" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C151" t="s">
-        <v>112</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="G151" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7">
-      <c r="A152">
+      <c r="B152" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C152" t="s">
+        <v>114</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="G152" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153">
         <v>13510</v>
       </c>
-      <c r="B152" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C152" t="s">
-        <v>112</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="G152" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8">
-      <c r="A153">
+      <c r="B153" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C153" t="s">
+        <v>114</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="G153" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154">
         <v>14010</v>
-      </c>
-      <c r="B153" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C153" t="s">
-        <v>112</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="G153" t="s">
-        <v>112</v>
-      </c>
-      <c r="H153" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7">
-      <c r="A154">
-        <v>14020</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>414</v>
       </c>
       <c r="C154" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>415</v>
       </c>
       <c r="G154" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="H154" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155">
-        <v>14021</v>
+        <v>14020</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C155" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G155" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156">
-        <v>14030</v>
+        <v>14021</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C156" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G156" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157">
-        <v>14040</v>
+        <v>14030</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C157" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G157" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158">
-        <v>14050</v>
+        <v>14040</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C158" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G158" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159">
-        <v>14060</v>
+        <v>14050</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>201</v>
+        <v>425</v>
       </c>
       <c r="C159" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>201</v>
+        <v>426</v>
       </c>
       <c r="G159" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160">
-        <v>14070</v>
-      </c>
-      <c r="B160" s="6" t="s">
-        <v>424</v>
+        <v>14060</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="C160" t="s">
-        <v>112</v>
-      </c>
-      <c r="F160" s="6" t="s">
-        <v>424</v>
+        <v>114</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="G160" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161">
-        <v>14080</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>425</v>
+        <v>14070</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="C161" t="s">
-        <v>112</v>
-      </c>
-      <c r="F161" s="1" t="s">
-        <v>426</v>
+        <v>114</v>
+      </c>
+      <c r="F161" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="G161" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162">
-        <v>14090</v>
+        <v>14080</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C162" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G162" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163">
-        <v>14100</v>
+        <v>14090</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C163" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="G163" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164">
+        <v>14100</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C164" t="s">
+        <v>114</v>
+      </c>
+      <c r="F164" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="G164" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165">
         <v>14110</v>
       </c>
-      <c r="B164" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C164" t="s">
-        <v>112</v>
-      </c>
-      <c r="F164" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="G164" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="165" customFormat="1" spans="1:7">
-      <c r="A165">
-        <v>14120</v>
-      </c>
       <c r="B165" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C165" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G165" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="166" customFormat="1" spans="1:7">
       <c r="A166">
-        <v>14121</v>
+        <v>14120</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C166" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>133</v>
+        <v>435</v>
       </c>
       <c r="G166" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="167" customFormat="1" spans="1:7">
       <c r="A167">
-        <v>14122</v>
+        <v>14121</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C167" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>435</v>
+        <v>135</v>
       </c>
       <c r="G167" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="168" customFormat="1" spans="1:7">
       <c r="A168">
-        <v>14123</v>
+        <v>14122</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C168" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G168" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="169" customFormat="1" spans="1:7">
       <c r="A169">
-        <v>14124</v>
+        <v>14123</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C169" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G169" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="170" customFormat="1" spans="1:7">
       <c r="A170">
-        <v>14125</v>
+        <v>14124</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C170" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G170" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="171" customFormat="1" spans="1:7">
       <c r="A171">
-        <v>14126</v>
+        <v>14125</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C171" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G171" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="172" customFormat="1" spans="1:7">
       <c r="A172">
-        <v>14127</v>
+        <v>14126</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C172" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G172" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="173" customFormat="1" spans="1:7">
       <c r="A173">
-        <v>14130</v>
+        <v>14127</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C173" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G173" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="174" customFormat="1" spans="1:7">
       <c r="A174">
-        <v>14140</v>
+        <v>14130</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>221</v>
+        <v>449</v>
       </c>
       <c r="C174" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>222</v>
+        <v>450</v>
       </c>
       <c r="G174" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="175" customFormat="1" spans="1:7">
       <c r="A175">
-        <v>14150</v>
+        <v>14140</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>425</v>
+        <v>223</v>
       </c>
       <c r="C175" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>426</v>
+        <v>224</v>
       </c>
       <c r="G175" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="176" customFormat="1" spans="1:7">
       <c r="A176">
-        <v>14160</v>
+        <v>14150</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="C176" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="G176" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="177" customFormat="1" spans="1:7">
       <c r="A177">
-        <v>14170</v>
+        <v>14160</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C177" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G177" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="178" customFormat="1" spans="1:7">
       <c r="A178">
-        <v>14180</v>
+        <v>14170</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C178" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G178" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="179" customFormat="1" spans="1:7">
       <c r="A179">
-        <v>14190</v>
+        <v>14180</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C179" t="s">
-        <v>112</v>
-      </c>
-      <c r="F179" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="F179" s="1" t="s">
+        <v>456</v>
+      </c>
       <c r="G179" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="180" customFormat="1" spans="1:7">
       <c r="A180">
-        <v>14200</v>
+        <v>14190</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C180" t="s">
-        <v>112</v>
-      </c>
-      <c r="F180" s="1" t="s">
-        <v>456</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="F180" s="1"/>
       <c r="G180" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="181" customFormat="1" spans="1:7">
       <c r="A181">
-        <v>14210</v>
+        <v>14200</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C181" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G181" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="182" customFormat="1" spans="1:7">
       <c r="A182">
-        <v>14220</v>
+        <v>14210</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C182" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G182" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="183" customFormat="1" spans="1:7">
       <c r="A183">
-        <v>14230</v>
+        <v>14220</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C183" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G183" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="184" customFormat="1" spans="1:7">
       <c r="A184">
-        <v>14231</v>
+        <v>14230</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C184" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G184" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="185" customFormat="1" spans="1:7">
       <c r="A185">
+        <v>14231</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="C185" t="s">
+        <v>114</v>
+      </c>
+      <c r="F185" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="G185" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="186" customFormat="1" spans="1:7">
+      <c r="A186">
         <v>14240</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="C185" t="s">
-        <v>112</v>
-      </c>
-      <c r="F185" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="G185" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="186" customFormat="1" spans="1:8">
-      <c r="A186">
+      <c r="B186" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="C186" t="s">
+        <v>114</v>
+      </c>
+      <c r="F186" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="G186" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="187" customFormat="1" spans="1:8">
+      <c r="A187">
         <v>15010</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="C186" t="s">
-        <v>112</v>
-      </c>
-      <c r="F186" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="G186" t="s">
-        <v>112</v>
-      </c>
-      <c r="H186" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="187" customFormat="1" spans="1:7">
-      <c r="A187">
-        <v>15020</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>470</v>
       </c>
       <c r="C187" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>471</v>
       </c>
       <c r="G187" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="188" ht="14" spans="1:9">
+        <v>114</v>
+      </c>
+      <c r="H187" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="188" customFormat="1" spans="1:7">
       <c r="A188">
-        <v>16010</v>
-      </c>
-      <c r="B188" t="s">
-        <v>305</v>
+        <v>15020</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>473</v>
       </c>
       <c r="C188" t="s">
-        <v>112</v>
-      </c>
-      <c r="F188" t="s">
-        <v>305</v>
+        <v>114</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>474</v>
       </c>
       <c r="G188" t="s">
-        <v>112</v>
-      </c>
-      <c r="H188" t="s">
-        <v>472</v>
-      </c>
-      <c r="I188" s="4"/>
+        <v>114</v>
+      </c>
     </row>
     <row r="189" ht="14" spans="1:9">
       <c r="A189">
-        <v>16020</v>
+        <v>16010</v>
       </c>
       <c r="B189" t="s">
-        <v>473</v>
+        <v>307</v>
       </c>
       <c r="C189" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F189" t="s">
-        <v>474</v>
+        <v>307</v>
       </c>
       <c r="G189" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="H189" t="s">
+        <v>475</v>
       </c>
       <c r="I189" s="4"/>
     </row>
     <row r="190" ht="14" spans="1:9">
       <c r="A190">
-        <v>16030</v>
+        <v>16020</v>
       </c>
       <c r="B190" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C190" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F190" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G190" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I190" s="4"/>
     </row>
     <row r="191" ht="14" spans="1:9">
       <c r="A191">
-        <v>16040</v>
+        <v>16030</v>
       </c>
       <c r="B191" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C191" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F191" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="G191" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I191" s="4"/>
     </row>
     <row r="192" ht="14" spans="1:9">
       <c r="A192">
+        <v>16040</v>
+      </c>
+      <c r="B192" t="s">
+        <v>480</v>
+      </c>
+      <c r="C192" t="s">
+        <v>114</v>
+      </c>
+      <c r="F192" t="s">
+        <v>480</v>
+      </c>
+      <c r="G192" t="s">
+        <v>114</v>
+      </c>
+      <c r="I192" s="4"/>
+    </row>
+    <row r="193" ht="14" spans="1:9">
+      <c r="A193">
         <v>16041</v>
       </c>
-      <c r="B192" t="s">
-        <v>477</v>
-      </c>
-      <c r="C192" t="s">
-        <v>112</v>
-      </c>
-      <c r="F192" t="s">
-        <v>477</v>
-      </c>
-      <c r="G192" t="s">
-        <v>112</v>
-      </c>
-      <c r="I192" s="4"/>
-    </row>
-    <row r="193" spans="1:7">
-      <c r="A193">
-        <v>16100</v>
-      </c>
       <c r="B193" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C193" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F193" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="G193" t="s">
-        <v>112</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="I193" s="4"/>
     </row>
     <row r="194" spans="1:7">
       <c r="A194">
-        <v>16110</v>
+        <v>16100</v>
       </c>
       <c r="B194" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C194" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F194" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G194" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195">
-        <v>16200</v>
+        <v>16110</v>
       </c>
       <c r="B195" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C195" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F195" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G195" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196">
-        <v>16210</v>
+        <v>16200</v>
       </c>
       <c r="B196" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C196" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F196" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G196" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="197" spans="1:7">
       <c r="A197">
-        <v>16220</v>
+        <v>16210</v>
       </c>
       <c r="B197" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C197" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F197" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G197" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198">
-        <v>16230</v>
+        <v>16220</v>
       </c>
       <c r="B198" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C198" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F198" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G198" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="199" spans="1:7">
       <c r="A199">
-        <v>16400</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>488</v>
+        <v>16230</v>
+      </c>
+      <c r="B199" t="s">
+        <v>489</v>
       </c>
       <c r="C199" t="s">
-        <v>112</v>
-      </c>
-      <c r="F199" s="2" t="s">
-        <v>489</v>
+        <v>114</v>
+      </c>
+      <c r="F199" t="s">
+        <v>490</v>
       </c>
       <c r="G199" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="200" spans="1:7">
       <c r="A200">
+        <v>16400</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C200" t="s">
+        <v>114</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="G200" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201">
         <v>16410</v>
       </c>
-      <c r="B200" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="C200" t="s">
-        <v>112</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="G200" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8">
-      <c r="A201">
-        <v>16800</v>
-      </c>
-      <c r="B201" t="s">
-        <v>155</v>
+      <c r="B201" s="2" t="s">
+        <v>493</v>
       </c>
       <c r="C201" t="s">
-        <v>112</v>
-      </c>
-      <c r="F201" t="s">
-        <v>155</v>
+        <v>114</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>494</v>
       </c>
       <c r="G201" t="s">
-        <v>112</v>
-      </c>
-      <c r="H201" t="s">
-        <v>492</v>
+        <v>114</v>
       </c>
     </row>
     <row r="202" spans="1:8">
       <c r="A202">
-        <v>16801</v>
+        <v>16800</v>
       </c>
       <c r="B202" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C202" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F202" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G202" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H202" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203">
-        <v>16802</v>
+        <v>16801</v>
       </c>
       <c r="B203" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C203" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F203" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G203" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H203" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="204" spans="1:8">
       <c r="A204">
-        <v>16803</v>
+        <v>16802</v>
       </c>
       <c r="B204" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C204" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F204" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G204" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H204" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205">
-        <v>16804</v>
+        <v>16803</v>
       </c>
       <c r="B205" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C205" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F205" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G205" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H205" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="206" spans="1:8">
       <c r="A206">
-        <v>16805</v>
+        <v>16804</v>
       </c>
       <c r="B206" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C206" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F206" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G206" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H206" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207">
+        <v>16805</v>
+      </c>
+      <c r="B207" t="s">
+        <v>162</v>
+      </c>
+      <c r="C207" t="s">
+        <v>114</v>
+      </c>
+      <c r="F207" t="s">
+        <v>162</v>
+      </c>
+      <c r="G207" t="s">
+        <v>114</v>
+      </c>
+      <c r="H207" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="A208">
         <v>16806</v>
       </c>
-      <c r="B207" t="s">
-        <v>161</v>
-      </c>
-      <c r="C207" t="s">
-        <v>112</v>
-      </c>
-      <c r="F207" t="s">
-        <v>161</v>
-      </c>
-      <c r="G207" t="s">
-        <v>112</v>
-      </c>
-      <c r="H207" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="208" ht="14" spans="1:9">
-      <c r="A208">
-        <v>19000</v>
-      </c>
-      <c r="B208" s="1" t="s">
-        <v>493</v>
+      <c r="B208" t="s">
+        <v>163</v>
       </c>
       <c r="C208" t="s">
-        <v>112</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>494</v>
+        <v>114</v>
+      </c>
+      <c r="F208" t="s">
+        <v>163</v>
       </c>
       <c r="G208" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H208" t="s">
         <v>495</v>
       </c>
-      <c r="I208" s="4"/>
-    </row>
-    <row r="209" spans="1:7">
+    </row>
+    <row r="209" ht="14" spans="1:9">
       <c r="A209">
-        <v>19001</v>
+        <v>19000</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>496</v>
       </c>
       <c r="C209" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>497</v>
       </c>
       <c r="G209" t="s">
-        <v>112</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="H209" t="s">
+        <v>498</v>
+      </c>
+      <c r="I209" s="4"/>
     </row>
     <row r="210" spans="1:7">
       <c r="A210">
-        <v>19002</v>
+        <v>19001</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C210" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G210" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="211" spans="1:7">
       <c r="A211">
-        <v>19003</v>
+        <v>19002</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C211" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G211" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="212" spans="1:7">
       <c r="A212">
-        <v>19004</v>
+        <v>19003</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C212" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G212" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="213" spans="1:7">
       <c r="A213">
-        <v>19005</v>
+        <v>19004</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C213" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>8</v>
+        <v>506</v>
       </c>
       <c r="G213" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="214" spans="1:7">
       <c r="A214">
-        <v>19006</v>
+        <v>19005</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C214" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>413</v>
+        <v>8</v>
       </c>
       <c r="G214" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="215" spans="1:7">
       <c r="A215">
-        <v>19007</v>
+        <v>19006</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C215" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>9</v>
+        <v>416</v>
       </c>
       <c r="G215" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="216" spans="1:7">
       <c r="A216">
-        <v>19100</v>
+        <v>19007</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C216" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>508</v>
+        <v>9</v>
       </c>
       <c r="G216" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="217" spans="1:7">
       <c r="A217">
-        <v>19101</v>
-      </c>
-      <c r="B217" t="s">
-        <v>40</v>
+        <v>19100</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>510</v>
       </c>
       <c r="C217" t="s">
-        <v>509</v>
-      </c>
-      <c r="F217" t="s">
-        <v>510</v>
+        <v>114</v>
+      </c>
+      <c r="F217" s="1" t="s">
+        <v>511</v>
       </c>
       <c r="G217" t="s">
-        <v>511</v>
+        <v>114</v>
       </c>
     </row>
     <row r="218" spans="1:7">
       <c r="A218">
-        <v>19102</v>
-      </c>
-      <c r="B218" s="2" t="s">
+        <v>19101</v>
+      </c>
+      <c r="B218" t="s">
+        <v>40</v>
+      </c>
+      <c r="C218" t="s">
         <v>512</v>
       </c>
-      <c r="C218" t="s">
-        <v>112</v>
-      </c>
-      <c r="F218" s="2" t="s">
-        <v>109</v>
+      <c r="F218" t="s">
+        <v>513</v>
       </c>
       <c r="G218" t="s">
-        <v>112</v>
+        <v>514</v>
       </c>
     </row>
     <row r="219" spans="1:7">
       <c r="A219">
-        <v>19103</v>
+        <v>19102</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C219" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>514</v>
+        <v>111</v>
       </c>
       <c r="G219" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="220" spans="1:7">
       <c r="A220">
-        <v>19104</v>
+        <v>19103</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C220" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G220" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="221" spans="1:7">
       <c r="A221">
-        <v>19105</v>
+        <v>19104</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C221" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G221" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="222" spans="1:7">
       <c r="A222">
-        <v>19106</v>
+        <v>19105</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C222" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G222" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="223" spans="1:7">
       <c r="A223">
-        <v>19107</v>
+        <v>19106</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C223" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G223" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="224" spans="1:7">
       <c r="A224">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C224" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G224" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="225" spans="1:7">
       <c r="A225">
+        <v>19108</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C225" t="s">
+        <v>114</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="G225" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226">
         <v>19109</v>
       </c>
-      <c r="B225" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="C225" t="s">
-        <v>112</v>
-      </c>
-      <c r="F225" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="G225" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8">
-      <c r="A226">
+      <c r="B226" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C226" t="s">
+        <v>114</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="G226" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8">
+      <c r="A227">
         <v>20010</v>
-      </c>
-      <c r="B226" t="s">
-        <v>527</v>
-      </c>
-      <c r="C226" t="s">
-        <v>112</v>
-      </c>
-      <c r="F226" t="s">
-        <v>528</v>
-      </c>
-      <c r="G226" t="s">
-        <v>112</v>
-      </c>
-      <c r="H226" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7">
-      <c r="A227">
-        <v>20020</v>
       </c>
       <c r="B227" t="s">
         <v>530</v>
       </c>
       <c r="C227" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F227" t="s">
         <v>531</v>
       </c>
       <c r="G227" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="H227" t="s">
+        <v>532</v>
       </c>
     </row>
     <row r="228" spans="1:7">
       <c r="A228">
-        <v>20030</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>532</v>
+        <v>20020</v>
+      </c>
+      <c r="B228" t="s">
+        <v>533</v>
       </c>
       <c r="C228" t="s">
-        <v>112</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>532</v>
+        <v>114</v>
+      </c>
+      <c r="F228" t="s">
+        <v>534</v>
       </c>
       <c r="G228" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="229" spans="1:7">
       <c r="A229">
-        <v>20040</v>
-      </c>
-      <c r="B229" t="s">
-        <v>533</v>
+        <v>20030</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>535</v>
       </c>
       <c r="C229" t="s">
-        <v>112</v>
-      </c>
-      <c r="F229" t="s">
-        <v>534</v>
+        <v>114</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>535</v>
       </c>
       <c r="G229" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="230" spans="1:7">
       <c r="A230">
-        <v>20050</v>
+        <v>20040</v>
       </c>
       <c r="B230" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C230" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F230" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G230" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="231" spans="1:7">
       <c r="A231">
-        <v>20100</v>
+        <v>20050</v>
       </c>
       <c r="B231" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C231" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F231" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G231" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="232" spans="1:7">
       <c r="A232">
-        <v>20110</v>
+        <v>20100</v>
       </c>
       <c r="B232" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C232" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F232" t="s">
-        <v>415</v>
+        <v>541</v>
       </c>
       <c r="G232" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="233" spans="1:7">
       <c r="A233">
-        <v>20111</v>
+        <v>20110</v>
       </c>
       <c r="B233" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C233" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F233" t="s">
-        <v>541</v>
+        <v>418</v>
       </c>
       <c r="G233" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="234" spans="1:7">
       <c r="A234">
+        <v>20111</v>
+      </c>
+      <c r="B234" t="s">
+        <v>543</v>
+      </c>
+      <c r="C234" t="s">
+        <v>114</v>
+      </c>
+      <c r="F234" t="s">
+        <v>544</v>
+      </c>
+      <c r="G234" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235">
         <v>20120</v>
       </c>
-      <c r="B234" t="s">
-        <v>542</v>
-      </c>
-      <c r="C234" t="s">
-        <v>112</v>
-      </c>
-      <c r="F234" t="s">
-        <v>543</v>
-      </c>
-      <c r="G234" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="235" customFormat="1" spans="1:7">
-      <c r="A235">
+      <c r="B235" t="s">
+        <v>545</v>
+      </c>
+      <c r="C235" t="s">
+        <v>114</v>
+      </c>
+      <c r="F235" t="s">
+        <v>546</v>
+      </c>
+      <c r="G235" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="236" customFormat="1" spans="1:7">
+      <c r="A236">
         <v>20130</v>
       </c>
-      <c r="B235" t="s">
-        <v>544</v>
-      </c>
-      <c r="C235" t="s">
-        <v>112</v>
-      </c>
-      <c r="F235" t="s">
-        <v>545</v>
-      </c>
-      <c r="G235" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7">
-      <c r="A236">
-        <v>20200</v>
-      </c>
       <c r="B236" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C236" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F236" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="G236" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="237" spans="1:7">
       <c r="A237">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B237" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C237" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F237" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="G237" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="238" spans="1:7">
       <c r="A238">
-        <v>20210</v>
+        <v>20201</v>
       </c>
       <c r="B238" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C238" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F238" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="G238" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="239" spans="1:7">
       <c r="A239">
-        <v>20220</v>
+        <v>20210</v>
       </c>
       <c r="B239" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C239" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F239" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="G239" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="240" spans="1:7">
       <c r="A240">
-        <v>20230</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>553</v>
+        <v>20220</v>
+      </c>
+      <c r="B240" t="s">
+        <v>554</v>
       </c>
       <c r="C240" t="s">
-        <v>112</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>554</v>
+        <v>114</v>
+      </c>
+      <c r="F240" t="s">
+        <v>555</v>
       </c>
       <c r="G240" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="241" spans="1:7">
       <c r="A241">
-        <v>20240</v>
+        <v>20230</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C241" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="G241" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="242" spans="1:7">
       <c r="A242">
-        <v>20250</v>
+        <v>20240</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C242" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="G242" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="243" spans="1:7">
       <c r="A243">
+        <v>20250</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="C243" t="s">
+        <v>114</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="G243" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244">
         <v>20270</v>
       </c>
-      <c r="B243" t="s">
-        <v>559</v>
-      </c>
-      <c r="C243" t="s">
-        <v>112</v>
-      </c>
-      <c r="F243" t="s">
-        <v>560</v>
-      </c>
-      <c r="G243" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="244" customFormat="1" spans="1:7">
-      <c r="A244">
+      <c r="B244" t="s">
+        <v>562</v>
+      </c>
+      <c r="C244" t="s">
+        <v>114</v>
+      </c>
+      <c r="F244" t="s">
+        <v>563</v>
+      </c>
+      <c r="G244" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="245" customFormat="1" spans="1:7">
+      <c r="A245">
         <v>20280</v>
       </c>
-      <c r="B244" t="s">
-        <v>561</v>
-      </c>
-      <c r="C244" t="s">
-        <v>112</v>
-      </c>
-      <c r="F244" t="s">
-        <v>562</v>
-      </c>
-      <c r="G244" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7">
-      <c r="A245">
-        <v>20300</v>
-      </c>
       <c r="B245" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C245" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F245" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G245" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="246" spans="1:7">
       <c r="A246">
-        <v>20301</v>
+        <v>20300</v>
       </c>
       <c r="B246" t="s">
-        <v>179</v>
+        <v>566</v>
       </c>
       <c r="C246" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="F246" t="s">
+        <v>567</v>
       </c>
       <c r="G246" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="247" spans="1:7">
       <c r="A247">
-        <v>20310</v>
+        <v>20301</v>
       </c>
       <c r="B247" t="s">
-        <v>565</v>
+        <v>181</v>
       </c>
       <c r="C247" t="s">
-        <v>112</v>
-      </c>
-      <c r="F247" t="s">
-        <v>566</v>
+        <v>114</v>
       </c>
       <c r="G247" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="248" spans="1:7">
       <c r="A248">
-        <v>20320</v>
+        <v>20310</v>
       </c>
       <c r="B248" t="s">
-        <v>213</v>
+        <v>568</v>
       </c>
       <c r="C248" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F248" t="s">
-        <v>214</v>
+        <v>569</v>
       </c>
       <c r="G248" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="249" spans="1:7">
       <c r="A249">
+        <v>20320</v>
+      </c>
+      <c r="B249" t="s">
+        <v>215</v>
+      </c>
+      <c r="C249" t="s">
+        <v>114</v>
+      </c>
+      <c r="F249" t="s">
+        <v>216</v>
+      </c>
+      <c r="G249" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250">
         <v>20330</v>
       </c>
-      <c r="B249" t="s">
-        <v>567</v>
-      </c>
-      <c r="C249" t="s">
-        <v>112</v>
-      </c>
-      <c r="F249" t="s">
-        <v>568</v>
-      </c>
-      <c r="G249" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6">
-      <c r="A250">
-        <v>20340</v>
-      </c>
       <c r="B250" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C250" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F250" t="s">
-        <v>570</v>
+        <v>571</v>
+      </c>
+      <c r="G250" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251">
+        <v>20340</v>
+      </c>
+      <c r="B251" t="s">
+        <v>572</v>
+      </c>
+      <c r="C251" t="s">
+        <v>114</v>
+      </c>
+      <c r="F251" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252">
         <v>20350</v>
       </c>
-      <c r="B251" t="s">
-        <v>571</v>
-      </c>
-      <c r="C251" t="s">
-        <v>112</v>
-      </c>
-      <c r="F251" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="252" customFormat="1" spans="1:6">
-      <c r="A252">
-        <v>20360</v>
-      </c>
       <c r="B252" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C252" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F252" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="253" customFormat="1" spans="1:6">
       <c r="A253">
-        <v>20370</v>
+        <v>20360</v>
       </c>
       <c r="B253" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C253" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F253" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="254" customFormat="1" spans="1:6">
       <c r="A254">
-        <v>20380</v>
+        <v>20370</v>
       </c>
       <c r="B254" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C254" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F254" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="255" customFormat="1" spans="1:6">
       <c r="A255">
-        <v>20390</v>
+        <v>20380</v>
       </c>
       <c r="B255" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C255" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F255" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="256" customFormat="1" spans="1:6">
       <c r="A256">
+        <v>20390</v>
+      </c>
+      <c r="B256" t="s">
+        <v>582</v>
+      </c>
+      <c r="C256" t="s">
+        <v>114</v>
+      </c>
+      <c r="F256" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="257" customFormat="1" spans="1:6">
+      <c r="A257">
         <v>20400</v>
       </c>
-      <c r="B256" t="s">
-        <v>581</v>
-      </c>
-      <c r="C256" t="s">
-        <v>112</v>
-      </c>
-      <c r="F256" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="257" customFormat="1" spans="1:8">
-      <c r="A257">
+      <c r="B257" t="s">
+        <v>584</v>
+      </c>
+      <c r="C257" t="s">
+        <v>114</v>
+      </c>
+      <c r="F257" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="258" customFormat="1" spans="1:8">
+      <c r="A258">
         <v>20410</v>
-      </c>
-      <c r="B257" t="s">
-        <v>583</v>
-      </c>
-      <c r="C257" t="s">
-        <v>112</v>
-      </c>
-      <c r="F257" t="s">
-        <v>584</v>
-      </c>
-      <c r="H257" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="258" customFormat="1" spans="1:6">
-      <c r="A258">
-        <v>20411</v>
       </c>
       <c r="B258" t="s">
         <v>586</v>
       </c>
       <c r="C258" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F258" t="s">
         <v>587</v>
       </c>
+      <c r="H258" t="s">
+        <v>588</v>
+      </c>
     </row>
     <row r="259" customFormat="1" spans="1:6">
       <c r="A259">
-        <v>20420</v>
+        <v>20411</v>
       </c>
       <c r="B259" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C259" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F259" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="260" customFormat="1" spans="1:6">
       <c r="A260">
-        <v>20430</v>
+        <v>20420</v>
       </c>
       <c r="B260" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C260" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F260" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="261" customFormat="1" spans="1:6">
       <c r="A261">
+        <v>20430</v>
+      </c>
+      <c r="B261" t="s">
+        <v>593</v>
+      </c>
+      <c r="C261" t="s">
+        <v>114</v>
+      </c>
+      <c r="F261" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="262" customFormat="1" spans="1:6">
+      <c r="A262">
         <v>20440</v>
       </c>
-      <c r="B261" t="s">
-        <v>592</v>
-      </c>
-      <c r="C261" t="s">
-        <v>112</v>
-      </c>
-      <c r="F261" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8">
-      <c r="A262">
+      <c r="B262" t="s">
+        <v>595</v>
+      </c>
+      <c r="C262" t="s">
+        <v>114</v>
+      </c>
+      <c r="F262" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8">
+      <c r="A263">
         <v>31010</v>
-      </c>
-      <c r="B262" t="s">
-        <v>594</v>
-      </c>
-      <c r="C262" t="s">
-        <v>112</v>
-      </c>
-      <c r="F262" t="s">
-        <v>595</v>
-      </c>
-      <c r="H262" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6">
-      <c r="A263">
-        <v>31020</v>
       </c>
       <c r="B263" t="s">
         <v>597</v>
       </c>
       <c r="C263" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F263" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="264" customFormat="1" spans="1:6">
+      <c r="H263" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
       <c r="A264">
-        <v>31030</v>
+        <v>31020</v>
       </c>
       <c r="B264" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C264" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F264" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="265" customFormat="1" spans="1:6">
       <c r="A265">
+        <v>31030</v>
+      </c>
+      <c r="B265" t="s">
+        <v>602</v>
+      </c>
+      <c r="C265" t="s">
+        <v>114</v>
+      </c>
+      <c r="F265" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="266" customFormat="1" spans="1:6">
+      <c r="A266">
         <v>31040</v>
       </c>
-      <c r="B265" t="s">
-        <v>600</v>
-      </c>
-      <c r="C265" t="s">
-        <v>112</v>
-      </c>
-      <c r="F265" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6">
-      <c r="A266">
+      <c r="B266" t="s">
+        <v>603</v>
+      </c>
+      <c r="C266" t="s">
+        <v>114</v>
+      </c>
+      <c r="F266" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267">
         <v>31050</v>
       </c>
-      <c r="B266" t="s">
-        <v>601</v>
-      </c>
-      <c r="C266" t="s">
-        <v>112</v>
-      </c>
-      <c r="F266" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="267" customFormat="1" spans="1:6">
-      <c r="A267">
-        <v>31060</v>
-      </c>
       <c r="B267" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C267" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F267" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="268" customFormat="1" spans="1:6">
       <c r="A268">
+        <v>31060</v>
+      </c>
+      <c r="B268" t="s">
+        <v>606</v>
+      </c>
+      <c r="C268" t="s">
+        <v>114</v>
+      </c>
+      <c r="F268" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="269" customFormat="1" spans="1:6">
+      <c r="A269">
         <v>31061</v>
       </c>
-      <c r="B268" t="s">
+      <c r="B269" t="s">
+        <v>608</v>
+      </c>
+      <c r="C269" t="s">
+        <v>114</v>
+      </c>
+      <c r="F269" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="270" customFormat="1" spans="1:7">
+      <c r="A270">
+        <v>31070</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="C270" t="s">
+        <v>114</v>
+      </c>
+      <c r="F270" t="s">
+        <v>611</v>
+      </c>
+      <c r="G270" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="271" customFormat="1" ht="26" spans="1:7">
+      <c r="A271">
+        <v>31071</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="C271" t="s">
+        <v>114</v>
+      </c>
+      <c r="F271" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="G271" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="272" customFormat="1" spans="1:7">
+      <c r="A272">
+        <v>31080</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C272" t="s">
+        <v>114</v>
+      </c>
+      <c r="F272" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="G272" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8">
+      <c r="A273">
+        <v>32010</v>
+      </c>
+      <c r="B273" t="s">
+        <v>614</v>
+      </c>
+      <c r="C273" t="s">
+        <v>114</v>
+      </c>
+      <c r="F273" t="s">
         <v>605</v>
       </c>
-      <c r="C268" t="s">
-        <v>112</v>
-      </c>
-      <c r="F268" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="269" customFormat="1" spans="1:7">
-      <c r="A269">
-        <v>31070</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="C269" t="s">
-        <v>112</v>
-      </c>
-      <c r="F269" t="s">
-        <v>608</v>
-      </c>
-      <c r="G269" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="270" customFormat="1" ht="26" spans="1:7">
-      <c r="A270">
-        <v>31071</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="C270" t="s">
-        <v>112</v>
-      </c>
-      <c r="F270" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="G270" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="271" customFormat="1" spans="1:7">
-      <c r="A271">
-        <v>31080</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="C271" t="s">
-        <v>112</v>
-      </c>
-      <c r="F271" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="G271" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="272" spans="1:8">
-      <c r="A272">
-        <v>32010</v>
-      </c>
-      <c r="B272" t="s">
-        <v>611</v>
-      </c>
-      <c r="C272" t="s">
-        <v>112</v>
-      </c>
-      <c r="F272" t="s">
-        <v>602</v>
-      </c>
-      <c r="G272" t="s">
-        <v>112</v>
-      </c>
-      <c r="H272" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7">
-      <c r="A273">
-        <v>32020</v>
-      </c>
-      <c r="B273" t="s">
-        <v>613</v>
-      </c>
-      <c r="C273" t="s">
-        <v>112</v>
-      </c>
-      <c r="F273" t="s">
-        <v>613</v>
-      </c>
       <c r="G273" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="H273" t="s">
+        <v>615</v>
       </c>
     </row>
     <row r="274" spans="1:7">
       <c r="A274">
-        <v>32030</v>
+        <v>32020</v>
       </c>
       <c r="B274" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C274" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F274" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G274" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="275" spans="1:7">
       <c r="A275">
-        <v>32040</v>
+        <v>32030</v>
       </c>
       <c r="B275" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C275" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F275" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G275" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="276" spans="1:7">
       <c r="A276">
-        <v>32050</v>
+        <v>32040</v>
       </c>
       <c r="B276" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C276" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F276" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="G276" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="277" spans="1:7">
       <c r="A277">
-        <v>32060</v>
+        <v>32050</v>
       </c>
       <c r="B277" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C277" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F277" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="G277" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="278" spans="1:7">
       <c r="A278">
-        <v>32070</v>
+        <v>32060</v>
       </c>
       <c r="B278" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C278" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F278" t="s">
-        <v>174</v>
+        <v>623</v>
       </c>
       <c r="G278" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="279" spans="1:7">
       <c r="A279">
-        <v>32080</v>
+        <v>32070</v>
       </c>
       <c r="B279" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C279" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F279" t="s">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="G279" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="280" spans="1:7">
       <c r="A280">
-        <v>32090</v>
+        <v>32080</v>
       </c>
       <c r="B280" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C280" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F280" t="s">
-        <v>623</v>
+        <v>201</v>
       </c>
       <c r="G280" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="281" spans="1:7">
       <c r="A281">
-        <v>32091</v>
+        <v>32090</v>
       </c>
       <c r="B281" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C281" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F281" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G281" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="282" spans="1:7">
       <c r="A282">
-        <v>32092</v>
+        <v>32091</v>
       </c>
       <c r="B282" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C282" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F282" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="G282" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="283" spans="1:7">
       <c r="A283">
+        <v>32092</v>
+      </c>
+      <c r="B283" t="s">
+        <v>628</v>
+      </c>
+      <c r="C283" t="s">
+        <v>114</v>
+      </c>
+      <c r="F283" t="s">
+        <v>628</v>
+      </c>
+      <c r="G283" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284">
         <v>32100</v>
       </c>
-      <c r="B283" t="s">
-        <v>626</v>
-      </c>
-      <c r="C283" t="s">
-        <v>112</v>
-      </c>
-      <c r="F283" t="s">
-        <v>627</v>
-      </c>
-      <c r="G283" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="284" customFormat="1" spans="1:7">
-      <c r="A284">
+      <c r="B284" t="s">
+        <v>629</v>
+      </c>
+      <c r="C284" t="s">
+        <v>114</v>
+      </c>
+      <c r="F284" t="s">
+        <v>630</v>
+      </c>
+      <c r="G284" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="285" customFormat="1" spans="1:7">
+      <c r="A285">
         <v>32110</v>
       </c>
-      <c r="B284" t="s">
-        <v>628</v>
-      </c>
-      <c r="C284" t="s">
-        <v>112</v>
-      </c>
-      <c r="F284" t="s">
-        <v>629</v>
-      </c>
-      <c r="G284" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="285" spans="1:8">
-      <c r="A285">
+      <c r="B285" t="s">
+        <v>631</v>
+      </c>
+      <c r="C285" t="s">
+        <v>114</v>
+      </c>
+      <c r="F285" t="s">
+        <v>632</v>
+      </c>
+      <c r="G285" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8">
+      <c r="A286">
         <v>33010</v>
-      </c>
-      <c r="B285" t="s">
-        <v>630</v>
-      </c>
-      <c r="C285" t="s">
-        <v>112</v>
-      </c>
-      <c r="F285" t="s">
-        <v>631</v>
-      </c>
-      <c r="G285" t="s">
-        <v>112</v>
-      </c>
-      <c r="H285" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7">
-      <c r="A286">
-        <v>33011</v>
       </c>
       <c r="B286" t="s">
         <v>633</v>
       </c>
       <c r="C286" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F286" t="s">
         <v>634</v>
       </c>
       <c r="G286" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="H286" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="287" spans="1:7">
       <c r="A287">
-        <v>33020</v>
+        <v>33011</v>
       </c>
       <c r="B287" t="s">
-        <v>174</v>
+        <v>636</v>
       </c>
       <c r="C287" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F287" t="s">
-        <v>174</v>
+        <v>637</v>
       </c>
       <c r="G287" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="288" spans="1:7">
       <c r="A288">
-        <v>33030</v>
+        <v>33020</v>
       </c>
       <c r="B288" t="s">
-        <v>635</v>
+        <v>176</v>
       </c>
       <c r="C288" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F288" t="s">
-        <v>636</v>
+        <v>176</v>
       </c>
       <c r="G288" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="289" spans="1:7">
       <c r="A289">
+        <v>33030</v>
+      </c>
+      <c r="B289" t="s">
+        <v>638</v>
+      </c>
+      <c r="C289" t="s">
+        <v>114</v>
+      </c>
+      <c r="F289" t="s">
+        <v>639</v>
+      </c>
+      <c r="G289" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290">
         <v>33040</v>
       </c>
-      <c r="B289" t="s">
-        <v>565</v>
-      </c>
-      <c r="C289" t="s">
-        <v>112</v>
-      </c>
-      <c r="F289" t="s">
-        <v>637</v>
-      </c>
-      <c r="G289" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="290" spans="1:8">
-      <c r="A290">
+      <c r="B290" t="s">
+        <v>568</v>
+      </c>
+      <c r="C290" t="s">
+        <v>114</v>
+      </c>
+      <c r="F290" t="s">
+        <v>640</v>
+      </c>
+      <c r="G290" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8">
+      <c r="A291">
         <v>34010</v>
-      </c>
-      <c r="B290" t="s">
-        <v>638</v>
-      </c>
-      <c r="C290" t="s">
-        <v>112</v>
-      </c>
-      <c r="F290" t="s">
-        <v>639</v>
-      </c>
-      <c r="G290" t="s">
-        <v>112</v>
-      </c>
-      <c r="H290" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7">
-      <c r="A291">
-        <v>34020</v>
       </c>
       <c r="B291" t="s">
         <v>641</v>
       </c>
       <c r="C291" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F291" t="s">
         <v>642</v>
       </c>
       <c r="G291" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="H291" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="292" spans="1:7">
       <c r="A292">
-        <v>34030</v>
+        <v>34020</v>
       </c>
       <c r="B292" t="s">
-        <v>343</v>
+        <v>644</v>
       </c>
       <c r="C292" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F292" t="s">
-        <v>344</v>
+        <v>645</v>
       </c>
       <c r="G292" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="293" spans="1:7">
       <c r="A293">
-        <v>34040</v>
+        <v>34030</v>
       </c>
       <c r="B293" t="s">
-        <v>643</v>
+        <v>345</v>
       </c>
       <c r="C293" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F293" t="s">
-        <v>644</v>
+        <v>346</v>
       </c>
       <c r="G293" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="294" spans="1:7">
       <c r="A294">
+        <v>34040</v>
+      </c>
+      <c r="B294" t="s">
+        <v>646</v>
+      </c>
+      <c r="C294" t="s">
+        <v>114</v>
+      </c>
+      <c r="F294" t="s">
+        <v>647</v>
+      </c>
+      <c r="G294" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295">
         <v>34050</v>
       </c>
-      <c r="B294" t="s">
-        <v>645</v>
-      </c>
-      <c r="C294" t="s">
-        <v>112</v>
-      </c>
-      <c r="F294" t="s">
-        <v>646</v>
-      </c>
-      <c r="G294" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="295" customFormat="1" spans="1:7">
-      <c r="A295">
-        <v>34060</v>
-      </c>
       <c r="B295" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C295" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F295" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="G295" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="296" customFormat="1" spans="1:7">
       <c r="A296">
+        <v>34060</v>
+      </c>
+      <c r="B296" t="s">
+        <v>650</v>
+      </c>
+      <c r="C296" t="s">
+        <v>114</v>
+      </c>
+      <c r="F296" t="s">
+        <v>651</v>
+      </c>
+      <c r="G296" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="297" customFormat="1" spans="1:7">
+      <c r="A297">
         <v>34070</v>
       </c>
-      <c r="B296" t="s">
-        <v>649</v>
-      </c>
-      <c r="C296" t="s">
-        <v>112</v>
-      </c>
-      <c r="F296" t="s">
-        <v>650</v>
-      </c>
-      <c r="G296" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="297" spans="1:8">
-      <c r="A297">
+      <c r="B297" t="s">
+        <v>652</v>
+      </c>
+      <c r="C297" t="s">
+        <v>114</v>
+      </c>
+      <c r="F297" t="s">
+        <v>653</v>
+      </c>
+      <c r="G297" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8">
+      <c r="A298">
         <v>35010</v>
       </c>
-      <c r="B297" t="s">
-        <v>651</v>
-      </c>
-      <c r="C297" t="s">
-        <v>112</v>
-      </c>
-      <c r="F297" t="s">
-        <v>652</v>
-      </c>
-      <c r="G297" t="s">
-        <v>112</v>
-      </c>
-      <c r="H297" t="s">
+      <c r="B298" t="s">
+        <v>654</v>
+      </c>
+      <c r="C298" t="s">
+        <v>114</v>
+      </c>
+      <c r="F298" t="s">
+        <v>655</v>
+      </c>
+      <c r="G298" t="s">
+        <v>114</v>
+      </c>
+      <c r="H298" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="298" spans="1:7">
-      <c r="A298">
+    <row r="299" spans="1:7">
+      <c r="A299">
         <v>35020</v>
       </c>
-      <c r="B298" t="s">
-        <v>653</v>
-      </c>
-      <c r="C298" t="s">
-        <v>112</v>
-      </c>
-      <c r="F298" t="s">
-        <v>654</v>
-      </c>
-      <c r="G298" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="299" customFormat="1" spans="1:7">
-      <c r="A299">
-        <v>35021</v>
-      </c>
       <c r="B299" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C299" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F299" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G299" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="300" customFormat="1" spans="1:7">
       <c r="A300">
-        <v>35030</v>
+        <v>35021</v>
       </c>
       <c r="B300" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C300" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F300" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G300" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="301" customFormat="1" spans="1:7">
       <c r="A301">
+        <v>35030</v>
+      </c>
+      <c r="B301" t="s">
+        <v>660</v>
+      </c>
+      <c r="C301" t="s">
+        <v>114</v>
+      </c>
+      <c r="F301" t="s">
+        <v>661</v>
+      </c>
+      <c r="G301" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="302" customFormat="1" spans="1:7">
+      <c r="A302">
         <v>35040</v>
       </c>
-      <c r="B301" t="s">
-        <v>659</v>
-      </c>
-      <c r="C301" t="s">
-        <v>112</v>
-      </c>
-      <c r="F301" t="s">
-        <v>660</v>
-      </c>
-      <c r="G301" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="302" spans="1:8">
-      <c r="A302">
+      <c r="B302" t="s">
+        <v>662</v>
+      </c>
+      <c r="C302" t="s">
+        <v>114</v>
+      </c>
+      <c r="F302" t="s">
+        <v>663</v>
+      </c>
+      <c r="G302" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8">
+      <c r="A303">
         <v>36010</v>
-      </c>
-      <c r="B302" t="s">
-        <v>661</v>
-      </c>
-      <c r="C302" t="s">
-        <v>112</v>
-      </c>
-      <c r="F302" t="s">
-        <v>662</v>
-      </c>
-      <c r="G302" t="s">
-        <v>112</v>
-      </c>
-      <c r="H302" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7">
-      <c r="A303">
-        <v>36011</v>
       </c>
       <c r="B303" t="s">
         <v>664</v>
       </c>
       <c r="C303" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F303" t="s">
         <v>665</v>
       </c>
       <c r="G303" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="304" spans="1:8">
+        <v>114</v>
+      </c>
+      <c r="H303" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7">
       <c r="A304">
+        <v>36011</v>
+      </c>
+      <c r="B304" t="s">
+        <v>667</v>
+      </c>
+      <c r="C304" t="s">
+        <v>114</v>
+      </c>
+      <c r="F304" t="s">
+        <v>668</v>
+      </c>
+      <c r="G304" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8">
+      <c r="A305">
         <v>37000</v>
-      </c>
-      <c r="B304" t="s">
-        <v>666</v>
-      </c>
-      <c r="C304" t="s">
-        <v>112</v>
-      </c>
-      <c r="F304" t="s">
-        <v>667</v>
-      </c>
-      <c r="G304" t="s">
-        <v>112</v>
-      </c>
-      <c r="H304" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7">
-      <c r="A305">
-        <v>37010</v>
       </c>
       <c r="B305" t="s">
         <v>669</v>
       </c>
       <c r="C305" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F305" t="s">
         <v>670</v>
       </c>
       <c r="G305" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="H305" t="s">
+        <v>671</v>
       </c>
     </row>
     <row r="306" spans="1:7">
       <c r="A306">
+        <v>37010</v>
+      </c>
+      <c r="B306" t="s">
+        <v>672</v>
+      </c>
+      <c r="C306" t="s">
+        <v>114</v>
+      </c>
+      <c r="F306" t="s">
+        <v>673</v>
+      </c>
+      <c r="G306" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7">
+      <c r="A307">
         <v>37020</v>
       </c>
-      <c r="B306" t="s">
-        <v>671</v>
-      </c>
-      <c r="C306" t="s">
-        <v>112</v>
-      </c>
-      <c r="F306" t="s">
-        <v>672</v>
-      </c>
-      <c r="G306" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="307" spans="1:8">
-      <c r="A307">
+      <c r="B307" t="s">
+        <v>674</v>
+      </c>
+      <c r="C307" t="s">
+        <v>114</v>
+      </c>
+      <c r="F307" t="s">
+        <v>675</v>
+      </c>
+      <c r="G307" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8">
+      <c r="A308">
         <v>38010</v>
-      </c>
-      <c r="B307" t="s">
-        <v>673</v>
-      </c>
-      <c r="C307" t="s">
-        <v>112</v>
-      </c>
-      <c r="F307" t="s">
-        <v>674</v>
-      </c>
-      <c r="G307" t="s">
-        <v>112</v>
-      </c>
-      <c r="H307" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7">
-      <c r="A308">
-        <v>38020</v>
       </c>
       <c r="B308" t="s">
         <v>676</v>
       </c>
       <c r="C308" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F308" t="s">
         <v>677</v>
       </c>
       <c r="G308" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="H308" t="s">
+        <v>678</v>
       </c>
     </row>
     <row r="309" spans="1:7">
       <c r="A309">
+        <v>38020</v>
+      </c>
+      <c r="B309" t="s">
+        <v>679</v>
+      </c>
+      <c r="C309" t="s">
+        <v>114</v>
+      </c>
+      <c r="F309" t="s">
+        <v>680</v>
+      </c>
+      <c r="G309" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="310" spans="1:7">
+      <c r="A310">
         <v>38030</v>
       </c>
-      <c r="B309" t="s">
-        <v>678</v>
-      </c>
-      <c r="C309" t="s">
-        <v>112</v>
-      </c>
-      <c r="F309" t="s">
-        <v>679</v>
-      </c>
-      <c r="G309" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="310" spans="1:8">
-      <c r="A310">
+      <c r="B310" t="s">
+        <v>681</v>
+      </c>
+      <c r="C310" t="s">
+        <v>114</v>
+      </c>
+      <c r="F310" t="s">
+        <v>682</v>
+      </c>
+      <c r="G310" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8">
+      <c r="A311">
         <v>39010</v>
       </c>
-      <c r="B310" t="s">
-        <v>680</v>
-      </c>
-      <c r="C310" t="s">
-        <v>112</v>
-      </c>
-      <c r="F310" t="s">
+      <c r="B311" t="s">
+        <v>683</v>
+      </c>
+      <c r="C311" t="s">
+        <v>114</v>
+      </c>
+      <c r="F311" t="s">
         <v>9</v>
       </c>
-      <c r="G310" t="s">
-        <v>112</v>
-      </c>
-      <c r="H310" t="s">
+      <c r="G311" t="s">
+        <v>114</v>
+      </c>
+      <c r="H311" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="311" spans="1:7">
-      <c r="A311">
+    <row r="312" spans="1:7">
+      <c r="A312">
         <v>39020</v>
       </c>
-      <c r="B311" t="s">
+      <c r="B312" t="s">
         <v>58</v>
       </c>
-      <c r="C311" t="s">
-        <v>112</v>
-      </c>
-      <c r="F311" t="s">
-        <v>681</v>
-      </c>
-      <c r="G311" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="312" customFormat="1" spans="1:7">
-      <c r="A312">
+      <c r="C312" t="s">
+        <v>114</v>
+      </c>
+      <c r="F312" t="s">
+        <v>684</v>
+      </c>
+      <c r="G312" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="313" customFormat="1" spans="1:7">
+      <c r="A313">
         <v>39030</v>
       </c>
-      <c r="B312" t="s">
-        <v>682</v>
-      </c>
-      <c r="C312" t="s">
-        <v>112</v>
-      </c>
-      <c r="F312" t="s">
-        <v>683</v>
-      </c>
-      <c r="G312" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="313" spans="1:7">
-      <c r="A313">
+      <c r="B313" t="s">
+        <v>685</v>
+      </c>
+      <c r="C313" t="s">
+        <v>114</v>
+      </c>
+      <c r="F313" t="s">
+        <v>686</v>
+      </c>
+      <c r="G313" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7">
+      <c r="A314">
         <v>39040</v>
       </c>
-      <c r="B313" t="s">
-        <v>684</v>
-      </c>
-      <c r="C313" t="s">
-        <v>112</v>
-      </c>
-      <c r="F313" t="s">
-        <v>685</v>
-      </c>
-      <c r="G313" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="314" customFormat="1" spans="1:7">
-      <c r="A314">
-        <v>39050</v>
-      </c>
       <c r="B314" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="C314" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F314" t="s">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="G314" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="315" customFormat="1" spans="1:7">
       <c r="A315">
-        <v>39051</v>
+        <v>39050</v>
       </c>
       <c r="B315" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="C315" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F315" t="s">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="G315" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="316" customFormat="1" spans="1:7">
       <c r="A316">
-        <v>39060</v>
+        <v>39051</v>
       </c>
       <c r="B316" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C316" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F316" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="G316" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="317" customFormat="1" spans="1:7">
       <c r="A317">
-        <v>39070</v>
+        <v>39060</v>
       </c>
       <c r="B317" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C317" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F317" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G317" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="318" customFormat="1" spans="1:7">
       <c r="A318">
-        <v>39080</v>
+        <v>39070</v>
       </c>
       <c r="B318" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C318" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F318" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G318" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="319" customFormat="1" spans="1:7">
       <c r="A319">
-        <v>39090</v>
+        <v>39080</v>
       </c>
       <c r="B319" t="s">
-        <v>638</v>
+        <v>695</v>
       </c>
       <c r="C319" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F319" t="s">
-        <v>639</v>
+        <v>696</v>
       </c>
       <c r="G319" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="320" customFormat="1" spans="1:7">
       <c r="A320">
+        <v>39090</v>
+      </c>
+      <c r="B320" t="s">
+        <v>641</v>
+      </c>
+      <c r="C320" t="s">
+        <v>114</v>
+      </c>
+      <c r="F320" t="s">
+        <v>642</v>
+      </c>
+      <c r="G320" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="321" customFormat="1" spans="1:7">
+      <c r="A321">
         <v>39100</v>
       </c>
-      <c r="B320" t="s">
-        <v>694</v>
-      </c>
-      <c r="C320" t="s">
-        <v>112</v>
-      </c>
-      <c r="F320" t="s">
-        <v>695</v>
-      </c>
-      <c r="G320" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="321" spans="1:8">
-      <c r="A321">
+      <c r="B321" t="s">
+        <v>697</v>
+      </c>
+      <c r="C321" t="s">
+        <v>114</v>
+      </c>
+      <c r="F321" t="s">
+        <v>698</v>
+      </c>
+      <c r="G321" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8">
+      <c r="A322">
         <v>40010</v>
       </c>
-      <c r="B321" t="s">
-        <v>696</v>
-      </c>
-      <c r="C321" t="s">
-        <v>112</v>
-      </c>
-      <c r="F321" t="s">
-        <v>697</v>
-      </c>
-      <c r="G321" t="s">
-        <v>112</v>
-      </c>
-      <c r="H321" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="322" spans="1:7">
-      <c r="A322">
+      <c r="B322" t="s">
+        <v>699</v>
+      </c>
+      <c r="C322" t="s">
+        <v>114</v>
+      </c>
+      <c r="F322" t="s">
+        <v>700</v>
+      </c>
+      <c r="G322" t="s">
+        <v>114</v>
+      </c>
+      <c r="H322" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7">
+      <c r="A323">
         <v>40020</v>
       </c>
-      <c r="B322" t="s">
-        <v>621</v>
-      </c>
-      <c r="C322" t="s">
-        <v>112</v>
-      </c>
-      <c r="F322" t="s">
-        <v>699</v>
-      </c>
-      <c r="G322" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="323" spans="1:8">
-      <c r="A323">
-        <v>41010</v>
-      </c>
       <c r="B323" t="s">
-        <v>700</v>
+        <v>624</v>
       </c>
       <c r="C323" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F323" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="G323" t="s">
-        <v>112</v>
-      </c>
-      <c r="H323" t="s">
-        <v>701</v>
+        <v>114</v>
       </c>
     </row>
     <row r="324" spans="1:8">
       <c r="A324">
-        <v>42010</v>
+        <v>41010</v>
       </c>
       <c r="B324" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C324" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F324" t="s">
         <v>703</v>
       </c>
       <c r="G324" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H324" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="325" spans="1:7">
+    <row r="325" spans="1:8">
       <c r="A325">
-        <v>42011</v>
+        <v>42010</v>
       </c>
       <c r="B325" t="s">
         <v>705</v>
       </c>
       <c r="C325" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F325" t="s">
         <v>706</v>
       </c>
       <c r="G325" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="326" customFormat="1" spans="1:7">
+        <v>114</v>
+      </c>
+      <c r="H325" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7">
       <c r="A326">
-        <v>42020</v>
+        <v>42011</v>
       </c>
       <c r="B326" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C326" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F326" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="G326" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="327" customFormat="1" spans="1:7">
       <c r="A327">
-        <v>42030</v>
+        <v>42020</v>
       </c>
       <c r="B327" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C327" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F327" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="G327" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="328" customFormat="1" spans="1:7">
       <c r="A328">
+        <v>42030</v>
+      </c>
+      <c r="B328" t="s">
+        <v>712</v>
+      </c>
+      <c r="C328" t="s">
+        <v>114</v>
+      </c>
+      <c r="F328" t="s">
+        <v>713</v>
+      </c>
+      <c r="G328" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="329" customFormat="1" spans="1:7">
+      <c r="A329">
         <v>42040</v>
       </c>
-      <c r="B328" t="s">
-        <v>711</v>
-      </c>
-      <c r="C328" t="s">
-        <v>112</v>
-      </c>
-      <c r="F328" t="s">
-        <v>712</v>
-      </c>
-      <c r="G328" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="329" spans="1:8">
-      <c r="A329">
+      <c r="B329" t="s">
+        <v>714</v>
+      </c>
+      <c r="C329" t="s">
+        <v>114</v>
+      </c>
+      <c r="F329" t="s">
+        <v>715</v>
+      </c>
+      <c r="G329" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8">
+      <c r="A330">
         <v>43010</v>
       </c>
-      <c r="B329" t="s">
-        <v>713</v>
-      </c>
-      <c r="C329" t="s">
-        <v>112</v>
-      </c>
-      <c r="F329" t="s">
-        <v>714</v>
-      </c>
-      <c r="G329" t="s">
-        <v>112</v>
-      </c>
-      <c r="H329" t="s">
+      <c r="B330" t="s">
+        <v>716</v>
+      </c>
+      <c r="C330" t="s">
+        <v>114</v>
+      </c>
+      <c r="F330" t="s">
+        <v>717</v>
+      </c>
+      <c r="G330" t="s">
+        <v>114</v>
+      </c>
+      <c r="H330" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="330" spans="1:7">
-      <c r="A330">
+    <row r="331" spans="1:7">
+      <c r="A331">
         <v>43020</v>
       </c>
-      <c r="B330" t="s">
-        <v>715</v>
-      </c>
-      <c r="C330" t="s">
-        <v>112</v>
-      </c>
-      <c r="F330" t="s">
-        <v>491</v>
-      </c>
-      <c r="G330" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="331" customFormat="1" spans="1:8">
-      <c r="A331">
+      <c r="B331" t="s">
+        <v>718</v>
+      </c>
+      <c r="C331" t="s">
+        <v>114</v>
+      </c>
+      <c r="F331" t="s">
+        <v>494</v>
+      </c>
+      <c r="G331" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="332" customFormat="1" spans="1:8">
+      <c r="A332">
         <v>44010</v>
-      </c>
-      <c r="B331" t="s">
-        <v>716</v>
-      </c>
-      <c r="C331" t="s">
-        <v>112</v>
-      </c>
-      <c r="F331" t="s">
-        <v>717</v>
-      </c>
-      <c r="G331" t="s">
-        <v>112</v>
-      </c>
-      <c r="H331" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="332" spans="1:8">
-      <c r="A332">
-        <v>45010</v>
       </c>
       <c r="B332" t="s">
         <v>719</v>
       </c>
       <c r="C332" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F332" t="s">
         <v>720</v>
       </c>
       <c r="G332" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H332" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="333" spans="1:7">
+    <row r="333" spans="1:8">
       <c r="A333">
-        <v>45020</v>
+        <v>45010</v>
       </c>
       <c r="B333" t="s">
         <v>722</v>
       </c>
       <c r="C333" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F333" t="s">
         <v>723</v>
       </c>
       <c r="G333" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="H333" t="s">
+        <v>724</v>
       </c>
     </row>
     <row r="334" spans="1:7">
       <c r="A334">
+        <v>45020</v>
+      </c>
+      <c r="B334" t="s">
+        <v>725</v>
+      </c>
+      <c r="C334" t="s">
+        <v>114</v>
+      </c>
+      <c r="F334" t="s">
+        <v>726</v>
+      </c>
+      <c r="G334" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7">
+      <c r="A335">
         <v>45030</v>
       </c>
-      <c r="B334" t="s">
-        <v>724</v>
-      </c>
-      <c r="C334" t="s">
-        <v>112</v>
-      </c>
-      <c r="F334" t="s">
-        <v>725</v>
-      </c>
-      <c r="G334" t="s">
-        <v>112</v>
+      <c r="B335" t="s">
+        <v>727</v>
+      </c>
+      <c r="C335" t="s">
+        <v>114</v>
+      </c>
+      <c r="F335" t="s">
+        <v>728</v>
+      </c>
+      <c r="G335" t="s">
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="731">
   <si>
     <t>Id</t>
   </si>
@@ -350,6 +350,12 @@
   </si>
   <si>
     <t>バトル基礎獲得Exp</t>
+  </si>
+  <si>
+    <t>PlusAttackValue</t>
+  </si>
+  <si>
+    <t>攻撃計算式のLv以下の時の最低保証値</t>
   </si>
   <si>
     <t>Text</t>
@@ -2228,9 +2234,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -2254,8 +2260,24 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2276,20 +2298,6 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2298,7 +2306,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2314,23 +2322,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2351,9 +2350,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2361,9 +2366,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2375,24 +2388,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2407,7 +2413,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2419,7 +2533,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2431,163 +2581,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2617,6 +2623,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -2631,11 +2652,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2645,6 +2672,15 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2668,36 +2704,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2706,145 +2712,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5604,7 +5610,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="20.5454545454545" customWidth="1"/>
@@ -5745,10 +5751,21 @@
         <v>108</v>
       </c>
       <c r="B15">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -5777,16 +5794,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5794,16 +5811,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -5811,16 +5828,16 @@
         <v>400</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -5828,16 +5845,16 @@
         <v>401</v>
       </c>
       <c r="B4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5845,16 +5862,16 @@
         <v>402</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:7">
@@ -5862,16 +5879,16 @@
         <v>403</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:7">
@@ -5879,16 +5896,16 @@
         <v>404</v>
       </c>
       <c r="B7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:7">
@@ -5896,16 +5913,16 @@
         <v>405</v>
       </c>
       <c r="B8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -5913,19 +5930,19 @@
         <v>600</v>
       </c>
       <c r="B9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5933,16 +5950,16 @@
         <v>601</v>
       </c>
       <c r="B10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F10" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -5950,16 +5967,16 @@
         <v>602</v>
       </c>
       <c r="B11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -5967,16 +5984,16 @@
         <v>603</v>
       </c>
       <c r="B12" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G12" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5984,16 +6001,16 @@
         <v>606</v>
       </c>
       <c r="B13" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F13" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -6001,16 +6018,16 @@
         <v>611</v>
       </c>
       <c r="B14" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F14" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -6018,16 +6035,16 @@
         <v>620</v>
       </c>
       <c r="B15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F15" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G15" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -6035,16 +6052,16 @@
         <v>621</v>
       </c>
       <c r="B16" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F16" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G16" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -6052,16 +6069,16 @@
         <v>622</v>
       </c>
       <c r="B17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F17" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G17" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -6069,16 +6086,16 @@
         <v>623</v>
       </c>
       <c r="B18" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -6086,16 +6103,16 @@
         <v>624</v>
       </c>
       <c r="B19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -6103,16 +6120,16 @@
         <v>625</v>
       </c>
       <c r="B20" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F20" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G20" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -6120,16 +6137,16 @@
         <v>651</v>
       </c>
       <c r="B21" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F21" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G21" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -6137,16 +6154,16 @@
         <v>652</v>
       </c>
       <c r="B22" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F22" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G22" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -6154,16 +6171,16 @@
         <v>1000</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G23" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -6171,19 +6188,19 @@
         <v>2000</v>
       </c>
       <c r="B24" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F24" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G24" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H24" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -6191,16 +6208,16 @@
         <v>2001</v>
       </c>
       <c r="B25" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F25" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G25" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -6208,16 +6225,16 @@
         <v>2002</v>
       </c>
       <c r="B26" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F26" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G26" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -6225,16 +6242,16 @@
         <v>2003</v>
       </c>
       <c r="B27" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C27" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F27" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G27" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -6242,16 +6259,16 @@
         <v>2004</v>
       </c>
       <c r="B28" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F28" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G28" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -6259,16 +6276,16 @@
         <v>2005</v>
       </c>
       <c r="B29" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C29" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F29" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G29" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -6276,16 +6293,16 @@
         <v>2006</v>
       </c>
       <c r="B30" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C30" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F30" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G30" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -6293,16 +6310,16 @@
         <v>2007</v>
       </c>
       <c r="B31" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F31" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G31" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -6310,19 +6327,19 @@
         <v>2100</v>
       </c>
       <c r="B32" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C32" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F32" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G32" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H32" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -6330,16 +6347,16 @@
         <v>2101</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -6347,16 +6364,16 @@
         <v>2102</v>
       </c>
       <c r="B34" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C34" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F34" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G34" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -6364,16 +6381,16 @@
         <v>2103</v>
       </c>
       <c r="B35" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F35" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G35" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -6381,16 +6398,16 @@
         <v>2104</v>
       </c>
       <c r="B36" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C36" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F36" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G36" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -6398,16 +6415,16 @@
         <v>2105</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C37" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G37" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -6415,16 +6432,16 @@
         <v>2106</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C38" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G38" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -6432,19 +6449,19 @@
         <v>2200</v>
       </c>
       <c r="B39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C39" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G39" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H39" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -6452,16 +6469,16 @@
         <v>2210</v>
       </c>
       <c r="B40" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C40" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F40" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G40" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -6469,16 +6486,16 @@
         <v>2220</v>
       </c>
       <c r="B41" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C41" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F41" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G41" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -6486,16 +6503,16 @@
         <v>2300</v>
       </c>
       <c r="B42" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C42" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F42" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G42" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -6503,16 +6520,16 @@
         <v>2310</v>
       </c>
       <c r="B43" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F43" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G43" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -6520,16 +6537,16 @@
         <v>2320</v>
       </c>
       <c r="B44" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F44" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G44" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -6537,16 +6554,16 @@
         <v>2330</v>
       </c>
       <c r="B45" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C45" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F45" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G45" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -6554,16 +6571,16 @@
         <v>2340</v>
       </c>
       <c r="B46" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C46" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F46" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G46" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -6571,16 +6588,16 @@
         <v>2400</v>
       </c>
       <c r="B47" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C47" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F47" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G47" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -6588,16 +6605,16 @@
         <v>2410</v>
       </c>
       <c r="B48" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C48" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F48" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G48" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -6605,16 +6622,16 @@
         <v>2420</v>
       </c>
       <c r="B49" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C49" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F49" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G49" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -6622,16 +6639,16 @@
         <v>2430</v>
       </c>
       <c r="B50" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C50" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F50" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G50" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -6639,16 +6656,16 @@
         <v>2440</v>
       </c>
       <c r="B51" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C51" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F51" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G51" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -6656,16 +6673,16 @@
         <v>2500</v>
       </c>
       <c r="B52" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C52" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F52" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G52" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" customFormat="1" spans="1:7">
@@ -6673,16 +6690,16 @@
         <v>2510</v>
       </c>
       <c r="B53" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C53" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F53" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G53" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:7">
@@ -6690,16 +6707,16 @@
         <v>2520</v>
       </c>
       <c r="B54" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C54" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F54" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G54" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:7">
@@ -6707,16 +6724,16 @@
         <v>2530</v>
       </c>
       <c r="B55" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F55" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G55" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -6724,16 +6741,16 @@
         <v>2610</v>
       </c>
       <c r="B56" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C56" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F56" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G56" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:8">
@@ -6741,19 +6758,19 @@
         <v>3010</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C57" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G57" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H57" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -6761,16 +6778,16 @@
         <v>3020</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C58" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G58" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="59" customFormat="1" spans="1:7">
@@ -6778,16 +6795,16 @@
         <v>3030</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C59" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G59" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:7">
@@ -6795,16 +6812,16 @@
         <v>3031</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C60" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G60" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -6812,16 +6829,16 @@
         <v>3040</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C61" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G61" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -6832,13 +6849,13 @@
         <v>38</v>
       </c>
       <c r="C62" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G62" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -6846,16 +6863,16 @@
         <v>3051</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C63" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G63" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -6863,16 +6880,16 @@
         <v>3052</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -6880,16 +6897,16 @@
         <v>3100</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C65" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G65" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -6897,16 +6914,16 @@
         <v>3110</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C66" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G66" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -6914,16 +6931,16 @@
         <v>3120</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C67" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G67" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -6931,16 +6948,16 @@
         <v>3130</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C68" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G68" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69" customFormat="1" spans="1:7">
@@ -6948,16 +6965,16 @@
         <v>3140</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C69" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G69" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:7">
@@ -6965,16 +6982,16 @@
         <v>3150</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C70" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G70" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -6982,16 +6999,16 @@
         <v>3200</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C71" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G71" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -6999,16 +7016,16 @@
         <v>3210</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C72" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G72" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="73" spans="1:8">
@@ -7016,19 +7033,19 @@
         <v>6001</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C73" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G73" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H73" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -7036,16 +7053,16 @@
         <v>6002</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C74" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G74" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -7053,16 +7070,16 @@
         <v>6100</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C75" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -7070,16 +7087,16 @@
         <v>6010</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C76" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G76" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -7087,16 +7104,16 @@
         <v>6011</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C77" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="G77" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -7104,16 +7121,16 @@
         <v>6012</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C78" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G78" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -7121,16 +7138,16 @@
         <v>6020</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C79" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G79" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -7138,16 +7155,16 @@
         <v>6030</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C80" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G80" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -7155,16 +7172,16 @@
         <v>6040</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C81" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G81" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="82" customFormat="1" spans="1:7">
@@ -7172,16 +7189,16 @@
         <v>6050</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C82" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G82" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:7">
@@ -7189,16 +7206,16 @@
         <v>6051</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G83" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:7">
@@ -7206,16 +7223,16 @@
         <v>6052</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C84" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G84" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -7223,16 +7240,16 @@
         <v>6210</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C85" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G85" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -7240,16 +7257,16 @@
         <v>6220</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C86" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G86" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -7257,16 +7274,16 @@
         <v>6230</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C87" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G87" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -7274,16 +7291,16 @@
         <v>6240</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C88" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G88" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -7291,16 +7308,16 @@
         <v>6250</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C89" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G89" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -7308,16 +7325,16 @@
         <v>6260</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C90" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G90" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -7325,16 +7342,16 @@
         <v>6270</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C91" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="G91" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -7342,16 +7359,16 @@
         <v>6280</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C92" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G92" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="93" customFormat="1" spans="1:7">
@@ -7359,16 +7376,16 @@
         <v>6290</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C93" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G93" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:7">
@@ -7376,16 +7393,16 @@
         <v>6300</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C94" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G94" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -7393,16 +7410,16 @@
         <v>6810</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C95" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G95" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -7410,16 +7427,16 @@
         <v>6820</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C96" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="G96" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -7427,16 +7444,16 @@
         <v>6830</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C97" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G97" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -7444,16 +7461,16 @@
         <v>6840</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C98" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G98" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -7461,16 +7478,16 @@
         <v>6850</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C99" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G99" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -7478,16 +7495,16 @@
         <v>6860</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C100" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G100" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -7495,16 +7512,16 @@
         <v>6870</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C101" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G101" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -7512,16 +7529,16 @@
         <v>6880</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C102" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G102" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -7529,16 +7546,16 @@
         <v>6890</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C103" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G103" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="104" customFormat="1" spans="1:7">
@@ -7546,16 +7563,16 @@
         <v>6900</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C104" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G104" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:7">
@@ -7563,16 +7580,16 @@
         <v>6910</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C105" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G105" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -7580,19 +7597,19 @@
         <v>10010</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C106" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G106" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H106" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -7600,16 +7617,16 @@
         <v>10100</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C107" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G107" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -7617,16 +7634,16 @@
         <v>10101</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C108" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G108" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -7634,16 +7651,16 @@
         <v>10110</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C109" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G109" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -7651,16 +7668,16 @@
         <v>10120</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C110" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G110" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -7668,16 +7685,16 @@
         <v>10121</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C111" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G111" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -7685,16 +7702,16 @@
         <v>10130</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C112" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="G112" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -7702,16 +7719,16 @@
         <v>10131</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C113" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G113" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" ht="26" spans="1:7">
@@ -7719,16 +7736,16 @@
         <v>10132</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C114" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G114" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="115" ht="26" spans="1:7">
@@ -7736,16 +7753,16 @@
         <v>10133</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C115" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G115" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -7753,16 +7770,16 @@
         <v>10140</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C116" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="G116" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -7770,16 +7787,16 @@
         <v>10141</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C117" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G117" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="118" customFormat="1" spans="1:7">
@@ -7787,16 +7804,16 @@
         <v>10142</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C118" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G118" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="119" customFormat="1" spans="1:7">
@@ -7804,16 +7821,16 @@
         <v>10143</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C119" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="G119" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -7821,16 +7838,16 @@
         <v>10150</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C120" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G120" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -7838,16 +7855,16 @@
         <v>10160</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C121" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G121" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="122" customFormat="1" spans="1:7">
@@ -7855,16 +7872,16 @@
         <v>10170</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C122" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="G122" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="123" customFormat="1" spans="1:7">
@@ -7872,16 +7889,16 @@
         <v>10171</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C123" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G123" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="124" customFormat="1" ht="26" spans="1:7">
@@ -7889,16 +7906,16 @@
         <v>10180</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C124" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G124" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="125" customFormat="1" spans="1:7">
@@ -7906,16 +7923,16 @@
         <v>10181</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C125" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G125" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="126" customFormat="1" ht="26" spans="1:7">
@@ -7923,16 +7940,16 @@
         <v>10182</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C126" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G126" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="127" customFormat="1" spans="1:7">
@@ -7940,16 +7957,16 @@
         <v>10190</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C127" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G127" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="128" customFormat="1" ht="26" spans="1:7">
@@ -7957,16 +7974,16 @@
         <v>10200</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C128" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G128" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="129" customFormat="1" spans="1:7">
@@ -7974,16 +7991,16 @@
         <v>10210</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C129" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="G129" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="130" customFormat="1" spans="1:7">
@@ -7991,16 +8008,16 @@
         <v>10220</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C130" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G130" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="131" customFormat="1" ht="52" spans="1:7">
@@ -8008,16 +8025,16 @@
         <v>10230</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C131" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="G131" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="132" customFormat="1" spans="1:7">
@@ -8025,16 +8042,16 @@
         <v>10240</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C132" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G132" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="133" ht="26" spans="1:8">
@@ -8042,19 +8059,19 @@
         <v>11010</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C133" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G133" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H133" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="134" ht="26" spans="1:7">
@@ -8062,16 +8079,16 @@
         <v>11011</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C134" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G134" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="135" customFormat="1" spans="1:7">
@@ -8079,16 +8096,16 @@
         <v>11012</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C135" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G135" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="136" customFormat="1" spans="1:7">
@@ -8096,16 +8113,16 @@
         <v>11013</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C136" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G136" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="137" customFormat="1" spans="1:7">
@@ -8113,16 +8130,16 @@
         <v>11014</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C137" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G137" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -8130,16 +8147,16 @@
         <v>11020</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C138" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G138" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="139" customFormat="1" spans="1:7">
@@ -8147,16 +8164,16 @@
         <v>11030</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C139" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G139" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -8164,16 +8181,16 @@
         <v>11040</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C140" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G140" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="141" customFormat="1" spans="1:7">
@@ -8181,16 +8198,16 @@
         <v>11050</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C141" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G141" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="142" customFormat="1" spans="1:7">
@@ -8198,16 +8215,16 @@
         <v>11060</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C142" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G142" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="143" customFormat="1" spans="1:7">
@@ -8215,16 +8232,16 @@
         <v>11070</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C143" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="G143" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="144" ht="52" spans="1:8">
@@ -8232,19 +8249,19 @@
         <v>12010</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C144" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G144" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H144" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -8252,19 +8269,19 @@
         <v>13010</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C145" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G145" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H145" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -8272,16 +8289,16 @@
         <v>13020</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C146" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G146" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -8289,16 +8306,16 @@
         <v>13110</v>
       </c>
       <c r="B147" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C147" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F147" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G147" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -8306,16 +8323,16 @@
         <v>13210</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C148" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G148" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -8323,16 +8340,16 @@
         <v>13220</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C149" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="G149" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -8340,16 +8357,16 @@
         <v>13230</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C150" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G150" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -8357,16 +8374,16 @@
         <v>13320</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C151" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="G151" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="152" customFormat="1" spans="1:7">
@@ -8374,16 +8391,16 @@
         <v>13410</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C152" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G152" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -8391,16 +8408,16 @@
         <v>13510</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C153" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="G153" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -8408,19 +8425,19 @@
         <v>14010</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C154" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G154" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H154" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -8428,16 +8445,16 @@
         <v>14020</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C155" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="G155" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -8445,16 +8462,16 @@
         <v>14021</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C156" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G156" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -8462,16 +8479,16 @@
         <v>14030</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C157" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G157" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -8479,16 +8496,16 @@
         <v>14040</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C158" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G158" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -8496,16 +8513,16 @@
         <v>14050</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C159" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G159" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -8513,16 +8530,16 @@
         <v>14060</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C160" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G160" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -8530,16 +8547,16 @@
         <v>14070</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C161" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="G161" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -8547,16 +8564,16 @@
         <v>14080</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C162" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="G162" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -8564,16 +8581,16 @@
         <v>14090</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C163" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G163" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -8581,16 +8598,16 @@
         <v>14100</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C164" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G164" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -8598,16 +8615,16 @@
         <v>14110</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C165" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="G165" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="166" customFormat="1" spans="1:7">
@@ -8615,16 +8632,16 @@
         <v>14120</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C166" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="G166" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="167" customFormat="1" spans="1:7">
@@ -8632,16 +8649,16 @@
         <v>14121</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C167" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G167" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="168" customFormat="1" spans="1:7">
@@ -8649,16 +8666,16 @@
         <v>14122</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C168" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G168" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="169" customFormat="1" spans="1:7">
@@ -8666,16 +8683,16 @@
         <v>14123</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C169" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G169" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="170" customFormat="1" spans="1:7">
@@ -8683,16 +8700,16 @@
         <v>14124</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C170" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G170" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="171" customFormat="1" spans="1:7">
@@ -8700,16 +8717,16 @@
         <v>14125</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C171" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G171" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="172" customFormat="1" spans="1:7">
@@ -8717,16 +8734,16 @@
         <v>14126</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C172" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G172" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="173" customFormat="1" spans="1:7">
@@ -8734,16 +8751,16 @@
         <v>14127</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C173" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G173" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="174" customFormat="1" spans="1:7">
@@ -8751,16 +8768,16 @@
         <v>14130</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C174" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G174" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="175" customFormat="1" spans="1:7">
@@ -8768,16 +8785,16 @@
         <v>14140</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C175" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G175" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="176" customFormat="1" spans="1:7">
@@ -8785,16 +8802,16 @@
         <v>14150</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C176" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="G176" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="177" customFormat="1" spans="1:7">
@@ -8802,16 +8819,16 @@
         <v>14160</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C177" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G177" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="178" customFormat="1" spans="1:7">
@@ -8819,16 +8836,16 @@
         <v>14170</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C178" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="G178" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="179" customFormat="1" spans="1:7">
@@ -8836,16 +8853,16 @@
         <v>14180</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C179" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G179" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="180" customFormat="1" spans="1:7">
@@ -8853,14 +8870,14 @@
         <v>14190</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C180" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F180" s="1"/>
       <c r="G180" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="181" customFormat="1" spans="1:7">
@@ -8868,16 +8885,16 @@
         <v>14200</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C181" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G181" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="182" customFormat="1" spans="1:7">
@@ -8885,16 +8902,16 @@
         <v>14210</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C182" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="G182" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="183" customFormat="1" spans="1:7">
@@ -8902,16 +8919,16 @@
         <v>14220</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C183" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="G183" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="184" customFormat="1" spans="1:7">
@@ -8919,16 +8936,16 @@
         <v>14230</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C184" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G184" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="185" customFormat="1" spans="1:7">
@@ -8936,16 +8953,16 @@
         <v>14231</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C185" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="G185" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="186" customFormat="1" spans="1:7">
@@ -8953,16 +8970,16 @@
         <v>14240</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C186" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G186" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="187" customFormat="1" spans="1:8">
@@ -8970,19 +8987,19 @@
         <v>15010</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C187" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G187" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H187" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="188" customFormat="1" spans="1:7">
@@ -8990,16 +9007,16 @@
         <v>15020</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C188" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="G188" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="189" ht="14" spans="1:9">
@@ -9007,19 +9024,19 @@
         <v>16010</v>
       </c>
       <c r="B189" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C189" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F189" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G189" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H189" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="I189" s="4"/>
     </row>
@@ -9028,16 +9045,16 @@
         <v>16020</v>
       </c>
       <c r="B190" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C190" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F190" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="G190" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I190" s="4"/>
     </row>
@@ -9046,16 +9063,16 @@
         <v>16030</v>
       </c>
       <c r="B191" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C191" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F191" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G191" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I191" s="4"/>
     </row>
@@ -9064,16 +9081,16 @@
         <v>16040</v>
       </c>
       <c r="B192" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C192" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F192" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G192" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I192" s="4"/>
     </row>
@@ -9082,16 +9099,16 @@
         <v>16041</v>
       </c>
       <c r="B193" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C193" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F193" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G193" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I193" s="4"/>
     </row>
@@ -9100,16 +9117,16 @@
         <v>16100</v>
       </c>
       <c r="B194" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C194" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F194" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="G194" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -9117,16 +9134,16 @@
         <v>16110</v>
       </c>
       <c r="B195" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C195" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F195" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G195" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -9134,16 +9151,16 @@
         <v>16200</v>
       </c>
       <c r="B196" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C196" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F196" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="G196" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -9151,16 +9168,16 @@
         <v>16210</v>
       </c>
       <c r="B197" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C197" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F197" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G197" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -9168,16 +9185,16 @@
         <v>16220</v>
       </c>
       <c r="B198" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C198" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F198" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G198" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -9185,16 +9202,16 @@
         <v>16230</v>
       </c>
       <c r="B199" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C199" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F199" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G199" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -9202,16 +9219,16 @@
         <v>16400</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C200" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="G200" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -9219,16 +9236,16 @@
         <v>16410</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C201" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G201" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -9236,19 +9253,19 @@
         <v>16800</v>
       </c>
       <c r="B202" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C202" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F202" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G202" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H202" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -9256,19 +9273,19 @@
         <v>16801</v>
       </c>
       <c r="B203" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C203" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F203" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G203" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H203" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -9276,19 +9293,19 @@
         <v>16802</v>
       </c>
       <c r="B204" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C204" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F204" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G204" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H204" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -9296,19 +9313,19 @@
         <v>16803</v>
       </c>
       <c r="B205" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C205" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F205" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G205" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H205" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -9316,19 +9333,19 @@
         <v>16804</v>
       </c>
       <c r="B206" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C206" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F206" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G206" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H206" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -9336,19 +9353,19 @@
         <v>16805</v>
       </c>
       <c r="B207" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C207" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F207" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G207" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H207" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -9356,19 +9373,19 @@
         <v>16806</v>
       </c>
       <c r="B208" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C208" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F208" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G208" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H208" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="209" ht="14" spans="1:9">
@@ -9376,19 +9393,19 @@
         <v>19000</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C209" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G209" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H209" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="I209" s="4"/>
     </row>
@@ -9397,16 +9414,16 @@
         <v>19001</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C210" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G210" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -9414,16 +9431,16 @@
         <v>19002</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C211" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="G211" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -9431,16 +9448,16 @@
         <v>19003</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C212" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="G212" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -9448,16 +9465,16 @@
         <v>19004</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C213" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="G213" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -9465,16 +9482,16 @@
         <v>19005</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C214" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G214" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -9482,16 +9499,16 @@
         <v>19006</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C215" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G215" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -9499,16 +9516,16 @@
         <v>19007</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C216" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G216" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -9516,16 +9533,16 @@
         <v>19100</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C217" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G217" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -9536,13 +9553,13 @@
         <v>40</v>
       </c>
       <c r="C218" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F218" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G218" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -9550,16 +9567,16 @@
         <v>19102</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C219" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G219" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -9567,16 +9584,16 @@
         <v>19103</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C220" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="G220" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -9584,16 +9601,16 @@
         <v>19104</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C221" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G221" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -9601,16 +9618,16 @@
         <v>19105</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C222" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G222" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -9618,16 +9635,16 @@
         <v>19106</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C223" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="G223" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -9635,16 +9652,16 @@
         <v>19107</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C224" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G224" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -9652,16 +9669,16 @@
         <v>19108</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C225" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="G225" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -9669,16 +9686,16 @@
         <v>19109</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C226" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="G226" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -9686,19 +9703,19 @@
         <v>20010</v>
       </c>
       <c r="B227" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C227" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F227" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G227" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H227" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -9706,16 +9723,16 @@
         <v>20020</v>
       </c>
       <c r="B228" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C228" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F228" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="G228" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -9723,16 +9740,16 @@
         <v>20030</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C229" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="G229" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -9740,16 +9757,16 @@
         <v>20040</v>
       </c>
       <c r="B230" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C230" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F230" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="G230" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -9757,16 +9774,16 @@
         <v>20050</v>
       </c>
       <c r="B231" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C231" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F231" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="G231" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -9774,16 +9791,16 @@
         <v>20100</v>
       </c>
       <c r="B232" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C232" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F232" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="G232" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -9791,16 +9808,16 @@
         <v>20110</v>
       </c>
       <c r="B233" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C233" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F233" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="G233" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -9808,16 +9825,16 @@
         <v>20111</v>
       </c>
       <c r="B234" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C234" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F234" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="G234" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -9825,16 +9842,16 @@
         <v>20120</v>
       </c>
       <c r="B235" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C235" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F235" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G235" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="236" customFormat="1" spans="1:7">
@@ -9842,16 +9859,16 @@
         <v>20130</v>
       </c>
       <c r="B236" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C236" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F236" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="G236" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -9859,16 +9876,16 @@
         <v>20200</v>
       </c>
       <c r="B237" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C237" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F237" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="G237" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -9876,16 +9893,16 @@
         <v>20201</v>
       </c>
       <c r="B238" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C238" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F238" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="G238" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -9893,16 +9910,16 @@
         <v>20210</v>
       </c>
       <c r="B239" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C239" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F239" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G239" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -9910,16 +9927,16 @@
         <v>20220</v>
       </c>
       <c r="B240" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C240" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F240" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="G240" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -9927,16 +9944,16 @@
         <v>20230</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C241" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="G241" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -9944,16 +9961,16 @@
         <v>20240</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C242" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="G242" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -9961,16 +9978,16 @@
         <v>20250</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C243" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G243" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -9978,16 +9995,16 @@
         <v>20270</v>
       </c>
       <c r="B244" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C244" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F244" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="G244" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="245" customFormat="1" spans="1:7">
@@ -9995,16 +10012,16 @@
         <v>20280</v>
       </c>
       <c r="B245" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C245" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F245" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="G245" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="246" spans="1:7">
@@ -10012,16 +10029,16 @@
         <v>20300</v>
       </c>
       <c r="B246" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C246" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F246" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="G246" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -10029,13 +10046,13 @@
         <v>20301</v>
       </c>
       <c r="B247" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C247" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G247" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -10043,16 +10060,16 @@
         <v>20310</v>
       </c>
       <c r="B248" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C248" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F248" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="G248" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -10060,16 +10077,16 @@
         <v>20320</v>
       </c>
       <c r="B249" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C249" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F249" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G249" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -10077,16 +10094,16 @@
         <v>20330</v>
       </c>
       <c r="B250" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C250" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F250" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="G250" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="251" spans="1:6">
@@ -10094,13 +10111,13 @@
         <v>20340</v>
       </c>
       <c r="B251" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C251" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F251" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="252" spans="1:6">
@@ -10108,13 +10125,13 @@
         <v>20350</v>
       </c>
       <c r="B252" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C252" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F252" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="253" customFormat="1" spans="1:6">
@@ -10122,13 +10139,13 @@
         <v>20360</v>
       </c>
       <c r="B253" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C253" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F253" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="254" customFormat="1" spans="1:6">
@@ -10136,13 +10153,13 @@
         <v>20370</v>
       </c>
       <c r="B254" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C254" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F254" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="255" customFormat="1" spans="1:6">
@@ -10150,13 +10167,13 @@
         <v>20380</v>
       </c>
       <c r="B255" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C255" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F255" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="256" customFormat="1" spans="1:6">
@@ -10164,13 +10181,13 @@
         <v>20390</v>
       </c>
       <c r="B256" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C256" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F256" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="257" customFormat="1" spans="1:6">
@@ -10178,13 +10195,13 @@
         <v>20400</v>
       </c>
       <c r="B257" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C257" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F257" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="258" customFormat="1" spans="1:8">
@@ -10192,16 +10209,16 @@
         <v>20410</v>
       </c>
       <c r="B258" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C258" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F258" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="H258" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="259" customFormat="1" spans="1:6">
@@ -10209,13 +10226,13 @@
         <v>20411</v>
       </c>
       <c r="B259" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C259" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F259" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="260" customFormat="1" spans="1:6">
@@ -10223,13 +10240,13 @@
         <v>20420</v>
       </c>
       <c r="B260" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C260" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F260" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="261" customFormat="1" spans="1:6">
@@ -10237,13 +10254,13 @@
         <v>20430</v>
       </c>
       <c r="B261" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C261" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F261" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="262" customFormat="1" spans="1:6">
@@ -10251,13 +10268,13 @@
         <v>20440</v>
       </c>
       <c r="B262" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C262" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F262" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -10265,16 +10282,16 @@
         <v>31010</v>
       </c>
       <c r="B263" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C263" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F263" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="H263" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="264" spans="1:6">
@@ -10282,13 +10299,13 @@
         <v>31020</v>
       </c>
       <c r="B264" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C264" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F264" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="265" customFormat="1" spans="1:6">
@@ -10296,13 +10313,13 @@
         <v>31030</v>
       </c>
       <c r="B265" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C265" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F265" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="266" customFormat="1" spans="1:6">
@@ -10310,13 +10327,13 @@
         <v>31040</v>
       </c>
       <c r="B266" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C266" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F266" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="267" spans="1:6">
@@ -10324,13 +10341,13 @@
         <v>31050</v>
       </c>
       <c r="B267" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C267" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F267" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="268" customFormat="1" spans="1:6">
@@ -10338,13 +10355,13 @@
         <v>31060</v>
       </c>
       <c r="B268" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C268" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F268" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="269" customFormat="1" spans="1:6">
@@ -10352,13 +10369,13 @@
         <v>31061</v>
       </c>
       <c r="B269" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C269" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F269" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="270" customFormat="1" spans="1:7">
@@ -10366,16 +10383,16 @@
         <v>31070</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C270" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F270" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="G270" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="271" customFormat="1" ht="26" spans="1:7">
@@ -10383,16 +10400,16 @@
         <v>31071</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C271" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="G271" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="272" customFormat="1" spans="1:7">
@@ -10400,16 +10417,16 @@
         <v>31080</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C272" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G272" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -10417,19 +10434,19 @@
         <v>32010</v>
       </c>
       <c r="B273" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C273" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F273" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="G273" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H273" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -10437,16 +10454,16 @@
         <v>32020</v>
       </c>
       <c r="B274" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C274" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F274" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="G274" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -10454,16 +10471,16 @@
         <v>32030</v>
       </c>
       <c r="B275" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C275" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F275" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="G275" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -10471,16 +10488,16 @@
         <v>32040</v>
       </c>
       <c r="B276" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C276" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F276" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="G276" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -10488,16 +10505,16 @@
         <v>32050</v>
       </c>
       <c r="B277" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C277" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F277" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="G277" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -10505,16 +10522,16 @@
         <v>32060</v>
       </c>
       <c r="B278" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C278" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F278" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="G278" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -10522,16 +10539,16 @@
         <v>32070</v>
       </c>
       <c r="B279" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C279" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F279" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G279" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -10539,16 +10556,16 @@
         <v>32080</v>
       </c>
       <c r="B280" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C280" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F280" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="G280" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -10556,16 +10573,16 @@
         <v>32090</v>
       </c>
       <c r="B281" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C281" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F281" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="G281" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -10573,16 +10590,16 @@
         <v>32091</v>
       </c>
       <c r="B282" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C282" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F282" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="G282" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -10590,16 +10607,16 @@
         <v>32092</v>
       </c>
       <c r="B283" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="C283" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F283" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="G283" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -10607,16 +10624,16 @@
         <v>32100</v>
       </c>
       <c r="B284" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C284" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F284" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G284" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="285" customFormat="1" spans="1:7">
@@ -10624,16 +10641,16 @@
         <v>32110</v>
       </c>
       <c r="B285" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C285" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F285" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="G285" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="286" spans="1:8">
@@ -10641,19 +10658,19 @@
         <v>33010</v>
       </c>
       <c r="B286" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C286" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F286" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="G286" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H286" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -10661,16 +10678,16 @@
         <v>33011</v>
       </c>
       <c r="B287" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C287" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F287" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="G287" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -10678,16 +10695,16 @@
         <v>33020</v>
       </c>
       <c r="B288" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C288" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F288" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G288" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -10695,16 +10712,16 @@
         <v>33030</v>
       </c>
       <c r="B289" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="C289" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F289" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="G289" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -10712,16 +10729,16 @@
         <v>33040</v>
       </c>
       <c r="B290" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C290" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F290" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="G290" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="291" spans="1:8">
@@ -10729,19 +10746,19 @@
         <v>34010</v>
       </c>
       <c r="B291" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C291" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F291" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="G291" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H291" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -10749,16 +10766,16 @@
         <v>34020</v>
       </c>
       <c r="B292" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C292" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F292" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="G292" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -10766,16 +10783,16 @@
         <v>34030</v>
       </c>
       <c r="B293" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C293" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F293" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G293" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -10783,16 +10800,16 @@
         <v>34040</v>
       </c>
       <c r="B294" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C294" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F294" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="G294" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -10800,16 +10817,16 @@
         <v>34050</v>
       </c>
       <c r="B295" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C295" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F295" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="G295" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="296" customFormat="1" spans="1:7">
@@ -10817,16 +10834,16 @@
         <v>34060</v>
       </c>
       <c r="B296" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C296" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F296" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="G296" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="297" customFormat="1" spans="1:7">
@@ -10834,16 +10851,16 @@
         <v>34070</v>
       </c>
       <c r="B297" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C297" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F297" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="G297" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="298" spans="1:8">
@@ -10851,16 +10868,16 @@
         <v>35010</v>
       </c>
       <c r="B298" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C298" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F298" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="G298" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -10871,16 +10888,16 @@
         <v>35020</v>
       </c>
       <c r="B299" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C299" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F299" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="G299" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="300" customFormat="1" spans="1:7">
@@ -10888,16 +10905,16 @@
         <v>35021</v>
       </c>
       <c r="B300" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C300" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F300" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="G300" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="301" customFormat="1" spans="1:7">
@@ -10905,16 +10922,16 @@
         <v>35030</v>
       </c>
       <c r="B301" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C301" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F301" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="G301" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="302" customFormat="1" spans="1:7">
@@ -10922,16 +10939,16 @@
         <v>35040</v>
       </c>
       <c r="B302" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="C302" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F302" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="G302" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -10939,19 +10956,19 @@
         <v>36010</v>
       </c>
       <c r="B303" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C303" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F303" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="G303" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H303" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="304" spans="1:7">
@@ -10959,16 +10976,16 @@
         <v>36011</v>
       </c>
       <c r="B304" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C304" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F304" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="G304" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="305" spans="1:8">
@@ -10976,19 +10993,19 @@
         <v>37000</v>
       </c>
       <c r="B305" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C305" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F305" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="G305" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H305" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
     </row>
     <row r="306" spans="1:7">
@@ -10996,16 +11013,16 @@
         <v>37010</v>
       </c>
       <c r="B306" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C306" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F306" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="G306" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -11013,16 +11030,16 @@
         <v>37020</v>
       </c>
       <c r="B307" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C307" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F307" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="G307" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -11030,19 +11047,19 @@
         <v>38010</v>
       </c>
       <c r="B308" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C308" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F308" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="G308" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H308" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -11050,16 +11067,16 @@
         <v>38020</v>
       </c>
       <c r="B309" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C309" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F309" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="G309" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="310" spans="1:7">
@@ -11067,16 +11084,16 @@
         <v>38030</v>
       </c>
       <c r="B310" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C310" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F310" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="G310" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -11084,16 +11101,16 @@
         <v>39010</v>
       </c>
       <c r="B311" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C311" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F311" t="s">
         <v>9</v>
       </c>
       <c r="G311" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -11107,13 +11124,13 @@
         <v>58</v>
       </c>
       <c r="C312" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F312" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="G312" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="313" customFormat="1" spans="1:7">
@@ -11121,16 +11138,16 @@
         <v>39030</v>
       </c>
       <c r="B313" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C313" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F313" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="G313" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="314" spans="1:7">
@@ -11138,16 +11155,16 @@
         <v>39040</v>
       </c>
       <c r="B314" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C314" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F314" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G314" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="315" customFormat="1" spans="1:7">
@@ -11155,16 +11172,16 @@
         <v>39050</v>
       </c>
       <c r="B315" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C315" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F315" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="G315" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="316" customFormat="1" spans="1:7">
@@ -11172,16 +11189,16 @@
         <v>39051</v>
       </c>
       <c r="B316" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C316" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F316" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="G316" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="317" customFormat="1" spans="1:7">
@@ -11189,16 +11206,16 @@
         <v>39060</v>
       </c>
       <c r="B317" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C317" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F317" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="G317" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="318" customFormat="1" spans="1:7">
@@ -11206,16 +11223,16 @@
         <v>39070</v>
       </c>
       <c r="B318" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C318" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F318" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="G318" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="319" customFormat="1" spans="1:7">
@@ -11223,16 +11240,16 @@
         <v>39080</v>
       </c>
       <c r="B319" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C319" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F319" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G319" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="320" customFormat="1" spans="1:7">
@@ -11240,16 +11257,16 @@
         <v>39090</v>
       </c>
       <c r="B320" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C320" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F320" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="G320" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="321" customFormat="1" spans="1:7">
@@ -11257,16 +11274,16 @@
         <v>39100</v>
       </c>
       <c r="B321" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C321" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F321" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="G321" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="322" spans="1:8">
@@ -11274,19 +11291,19 @@
         <v>40010</v>
       </c>
       <c r="B322" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C322" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F322" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="G322" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H322" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
     </row>
     <row r="323" spans="1:7">
@@ -11294,16 +11311,16 @@
         <v>40020</v>
       </c>
       <c r="B323" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C323" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F323" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="G323" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="324" spans="1:8">
@@ -11311,19 +11328,19 @@
         <v>41010</v>
       </c>
       <c r="B324" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C324" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F324" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="G324" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H324" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -11331,19 +11348,19 @@
         <v>42010</v>
       </c>
       <c r="B325" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C325" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F325" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="G325" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H325" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
     </row>
     <row r="326" spans="1:7">
@@ -11351,16 +11368,16 @@
         <v>42011</v>
       </c>
       <c r="B326" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C326" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F326" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="G326" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="327" customFormat="1" spans="1:7">
@@ -11368,16 +11385,16 @@
         <v>42020</v>
       </c>
       <c r="B327" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C327" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F327" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="G327" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="328" customFormat="1" spans="1:7">
@@ -11385,16 +11402,16 @@
         <v>42030</v>
       </c>
       <c r="B328" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C328" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F328" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="G328" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="329" customFormat="1" spans="1:7">
@@ -11402,16 +11419,16 @@
         <v>42040</v>
       </c>
       <c r="B329" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C329" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F329" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="G329" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="330" spans="1:8">
@@ -11419,16 +11436,16 @@
         <v>43010</v>
       </c>
       <c r="B330" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C330" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F330" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="G330" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H330" t="s">
         <v>4</v>
@@ -11439,16 +11456,16 @@
         <v>43020</v>
       </c>
       <c r="B331" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C331" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F331" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G331" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="332" customFormat="1" spans="1:8">
@@ -11456,19 +11473,19 @@
         <v>44010</v>
       </c>
       <c r="B332" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C332" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F332" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="G332" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H332" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -11476,19 +11493,19 @@
         <v>45010</v>
       </c>
       <c r="B333" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C333" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F333" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="G333" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H333" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="334" spans="1:7">
@@ -11496,16 +11513,16 @@
         <v>45020</v>
       </c>
       <c r="B334" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C334" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F334" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="G334" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="335" spans="1:7">
@@ -11513,16 +11530,16 @@
         <v>45030</v>
       </c>
       <c r="B335" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C335" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F335" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="G335" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="766" firstSheet="1" activeTab="5"/>
+    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="766" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="TacticsComand" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="732">
   <si>
     <t>Id</t>
   </si>
@@ -553,7 +553,13 @@
     <t>&lt;遠隔&gt;</t>
   </si>
   <si>
-    <t>L</t>
+    <t>Ranged</t>
+  </si>
+  <si>
+    <t>&lt;同時発動制限&gt;</t>
+  </si>
+  <si>
+    <t>Limited</t>
   </si>
   <si>
     <t>Rank.</t>
@@ -2133,9 +2139,6 @@
   </si>
   <si>
     <t>1個限定</t>
-  </si>
-  <si>
-    <t>Limited</t>
   </si>
   <si>
     <t>神界等級アップ！</t>
@@ -2233,10 +2236,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -2260,38 +2263,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2306,7 +2287,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2315,6 +2310,36 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2329,35 +2354,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -2366,23 +2362,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2398,7 +2378,30 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2419,7 +2422,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2431,13 +2530,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2449,19 +2578,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2473,127 +2590,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2618,21 +2621,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2670,26 +2658,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2704,6 +2674,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2712,22 +2715,22 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -2736,121 +2739,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5777,7 +5780,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I335"/>
+  <dimension ref="A1:I336"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.54545454545455" customWidth="1"/>
@@ -6498,9 +6501,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" customFormat="1" spans="1:7">
       <c r="A42">
-        <v>2300</v>
+        <v>2221</v>
       </c>
       <c r="B42" t="s">
         <v>178</v>
@@ -6508,8 +6511,10 @@
       <c r="C42" t="s">
         <v>116</v>
       </c>
+      <c r="D42"/>
+      <c r="E42"/>
       <c r="F42" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G42" t="s">
         <v>116</v>
@@ -6517,16 +6522,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>2310</v>
+        <v>2300</v>
       </c>
       <c r="B43" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C43" t="s">
         <v>116</v>
       </c>
       <c r="F43" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G43" t="s">
         <v>116</v>
@@ -6534,16 +6539,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>2320</v>
+        <v>2310</v>
       </c>
       <c r="B44" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C44" t="s">
         <v>116</v>
       </c>
       <c r="F44" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G44" t="s">
         <v>116</v>
@@ -6551,16 +6556,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="B45" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C45" t="s">
         <v>116</v>
       </c>
       <c r="F45" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G45" t="s">
         <v>116</v>
@@ -6568,16 +6573,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="B46" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C46" t="s">
         <v>116</v>
       </c>
       <c r="F46" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G46" t="s">
         <v>116</v>
@@ -6585,10 +6590,10 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>2400</v>
+        <v>2340</v>
       </c>
       <c r="B47" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C47" t="s">
         <v>116</v>
@@ -6602,7 +6607,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="B48" t="s">
         <v>185</v>
@@ -6619,7 +6624,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="B49" t="s">
         <v>187</v>
@@ -6636,7 +6641,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="B50" t="s">
         <v>189</v>
@@ -6653,7 +6658,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="B51" t="s">
         <v>191</v>
@@ -6670,7 +6675,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>2500</v>
+        <v>2440</v>
       </c>
       <c r="B52" t="s">
         <v>193</v>
@@ -6685,9 +6690,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="53" customFormat="1" spans="1:7">
+    <row r="53" spans="1:7">
       <c r="A53">
-        <v>2510</v>
+        <v>2500</v>
       </c>
       <c r="B53" t="s">
         <v>195</v>
@@ -6704,7 +6709,7 @@
     </row>
     <row r="54" customFormat="1" spans="1:7">
       <c r="A54">
-        <v>2520</v>
+        <v>2510</v>
       </c>
       <c r="B54" t="s">
         <v>197</v>
@@ -6721,7 +6726,7 @@
     </row>
     <row r="55" customFormat="1" spans="1:7">
       <c r="A55">
-        <v>2530</v>
+        <v>2520</v>
       </c>
       <c r="B55" t="s">
         <v>199</v>
@@ -6736,9 +6741,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" customFormat="1" spans="1:7">
       <c r="A56">
-        <v>2610</v>
+        <v>2530</v>
       </c>
       <c r="B56" t="s">
         <v>201</v>
@@ -6753,29 +6758,26 @@
         <v>116</v>
       </c>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:7">
       <c r="A57">
+        <v>2610</v>
+      </c>
+      <c r="B57" t="s">
+        <v>203</v>
+      </c>
+      <c r="C57" t="s">
+        <v>116</v>
+      </c>
+      <c r="F57" t="s">
+        <v>204</v>
+      </c>
+      <c r="G57" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58">
         <v>3010</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="C57" t="s">
-        <v>116</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="G57" t="s">
-        <v>116</v>
-      </c>
-      <c r="H57" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58">
-        <v>3020</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>205</v>
@@ -6789,13 +6791,16 @@
       <c r="G58" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="59" customFormat="1" spans="1:7">
+      <c r="H58" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C59" t="s">
         <v>116</v>
@@ -6809,7 +6814,7 @@
     </row>
     <row r="60" customFormat="1" spans="1:7">
       <c r="A60">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>208</v>
@@ -6824,9 +6829,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" customFormat="1" spans="1:7">
       <c r="A61">
-        <v>3040</v>
+        <v>3031</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>210</v>
@@ -6843,16 +6848,16 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>3050</v>
+        <v>3040</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>38</v>
+        <v>212</v>
       </c>
       <c r="C62" t="s">
         <v>116</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G62" t="s">
         <v>116</v>
@@ -6860,10 +6865,10 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>213</v>
+        <v>38</v>
       </c>
       <c r="C63" t="s">
         <v>116</v>
@@ -6877,7 +6882,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>215</v>
@@ -6894,15 +6899,15 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65">
-        <v>3100</v>
-      </c>
-      <c r="B65" s="3" t="s">
+        <v>3052</v>
+      </c>
+      <c r="B65" s="2" t="s">
         <v>217</v>
       </c>
       <c r="C65" t="s">
         <v>116</v>
       </c>
-      <c r="F65" s="3" t="s">
+      <c r="F65" s="2" t="s">
         <v>218</v>
       </c>
       <c r="G65" t="s">
@@ -6911,15 +6916,15 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66">
-        <v>3110</v>
-      </c>
-      <c r="B66" s="2" t="s">
+        <v>3100</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>219</v>
       </c>
       <c r="C66" t="s">
         <v>116</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="F66" s="3" t="s">
         <v>220</v>
       </c>
       <c r="G66" t="s">
@@ -6928,7 +6933,7 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67">
-        <v>3120</v>
+        <v>3110</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>221</v>
@@ -6945,7 +6950,7 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68">
-        <v>3130</v>
+        <v>3120</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>223</v>
@@ -6960,9 +6965,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="69" customFormat="1" spans="1:7">
+    <row r="69" spans="1:7">
       <c r="A69">
-        <v>3140</v>
+        <v>3130</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>225</v>
@@ -6979,7 +6984,7 @@
     </row>
     <row r="70" customFormat="1" spans="1:7">
       <c r="A70">
-        <v>3150</v>
+        <v>3140</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>227</v>
@@ -6994,9 +6999,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" customFormat="1" spans="1:7">
       <c r="A71">
-        <v>3200</v>
+        <v>3150</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>229</v>
@@ -7005,7 +7010,7 @@
         <v>116</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G71" t="s">
         <v>116</v>
@@ -7013,112 +7018,112 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72">
+        <v>3200</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C72" t="s">
+        <v>116</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="G72" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73">
         <v>3210</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C72" t="s">
-        <v>116</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="G72" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
-      <c r="A73">
+      <c r="B73" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C73" t="s">
+        <v>116</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G73" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74">
         <v>6001</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="C73" t="s">
-        <v>116</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="G73" t="s">
-        <v>116</v>
-      </c>
-      <c r="H73" t="s">
+      <c r="B74" s="2" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74">
-        <v>6002</v>
-      </c>
-      <c r="B74" s="2" t="s">
+      <c r="C74" t="s">
+        <v>116</v>
+      </c>
+      <c r="F74" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C74" t="s">
-        <v>116</v>
-      </c>
-      <c r="F74" s="2" t="s">
+      <c r="G74" t="s">
+        <v>116</v>
+      </c>
+      <c r="H74" t="s">
         <v>236</v>
-      </c>
-      <c r="G74" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75">
-        <v>6100</v>
+        <v>6002</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>116</v>
+        <v>237</v>
       </c>
       <c r="C75" t="s">
-        <v>237</v>
+        <v>116</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="G75" s="2" t="s">
-        <v>238</v>
+      <c r="G75" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76">
-        <v>6010</v>
+        <v>6100</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C76" t="s">
         <v>239</v>
       </c>
-      <c r="C76" t="s">
+      <c r="F76" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="F76" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="G76" t="s">
-        <v>242</v>
+      <c r="G76" s="2" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77">
-        <v>6011</v>
+        <v>6010</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C77" t="s">
+        <v>242</v>
+      </c>
+      <c r="F77" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C77" t="s">
-        <v>116</v>
-      </c>
-      <c r="F77" s="2" t="s">
+      <c r="G77" t="s">
         <v>244</v>
-      </c>
-      <c r="G77" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>6012</v>
+        <v>6011</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>245</v>
@@ -7135,92 +7140,92 @@
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>6020</v>
+        <v>6012</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>247</v>
       </c>
       <c r="C79" t="s">
+        <v>116</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="F79" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="G79" t="s">
-        <v>250</v>
+        <v>116</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C80" t="s">
+        <v>250</v>
+      </c>
+      <c r="F80" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C80" t="s">
+      <c r="G80" t="s">
         <v>252</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G80" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81">
+        <v>6030</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C81" t="s">
+        <v>254</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="G81" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82">
         <v>6040</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C81" t="s">
-        <v>256</v>
-      </c>
-      <c r="F81" s="2" t="s">
+      <c r="B82" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="G81" t="s">
+      <c r="C82" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="82" customFormat="1" spans="1:7">
-      <c r="A82">
-        <v>6050</v>
-      </c>
-      <c r="B82" s="2" t="s">
+      <c r="F82" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C82" t="s">
+      <c r="G82" t="s">
         <v>260</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="G82" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:7">
       <c r="A83">
-        <v>6051</v>
+        <v>6050</v>
       </c>
       <c r="B83" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C83" t="s">
+        <v>262</v>
+      </c>
+      <c r="F83" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C83" t="s">
-        <v>116</v>
-      </c>
-      <c r="F83" s="2" t="s">
+      <c r="G83" t="s">
         <v>264</v>
-      </c>
-      <c r="G83" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:7">
       <c r="A84">
-        <v>6052</v>
+        <v>6051</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>265</v>
@@ -7235,205 +7240,205 @@
         <v>116</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" customFormat="1" spans="1:7">
       <c r="A85">
-        <v>6210</v>
+        <v>6052</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>267</v>
       </c>
       <c r="C85" t="s">
+        <v>116</v>
+      </c>
+      <c r="F85" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="F85" s="2" t="s">
-        <v>269</v>
-      </c>
       <c r="G85" t="s">
-        <v>270</v>
+        <v>116</v>
       </c>
     </row>
     <row r="86" spans="1:7">
       <c r="A86">
-        <v>6220</v>
+        <v>6210</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C86" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>271</v>
       </c>
       <c r="G86" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="87" spans="1:7">
       <c r="A87">
-        <v>6230</v>
+        <v>6220</v>
       </c>
       <c r="B87" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C87" t="s">
         <v>274</v>
       </c>
-      <c r="C87" t="s">
+      <c r="F87" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="G87" t="s">
         <v>275</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="G87" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88">
-        <v>6240</v>
+        <v>6230</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C88" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>278</v>
       </c>
       <c r="G88" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89">
-        <v>6250</v>
+        <v>6240</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C89" t="s">
         <v>281</v>
       </c>
-      <c r="C89" t="s">
+      <c r="F89" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="G89" t="s">
         <v>282</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="G89" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90">
-        <v>6260</v>
+        <v>6250</v>
       </c>
       <c r="B90" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C90" t="s">
+        <v>284</v>
+      </c>
+      <c r="F90" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="C90" t="s">
+      <c r="G90" t="s">
         <v>286</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="G90" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91">
-        <v>6270</v>
+        <v>6260</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C91" t="s">
+        <v>288</v>
+      </c>
+      <c r="F91" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C91" t="s">
+      <c r="G91" t="s">
         <v>290</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="G91" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92">
-        <v>6280</v>
+        <v>6270</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C92" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>293</v>
       </c>
       <c r="G92" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93">
+        <v>6280</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="93" customFormat="1" spans="1:7">
-      <c r="A93">
-        <v>6290</v>
-      </c>
-      <c r="B93" s="2" t="s">
+      <c r="C93" t="s">
         <v>296</v>
       </c>
-      <c r="C93" t="s">
+      <c r="F93" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G93" t="s">
         <v>297</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G93" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:7">
       <c r="A94">
+        <v>6290</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C94" t="s">
+        <v>299</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="G94" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="95" customFormat="1" spans="1:7">
+      <c r="A95">
         <v>6300</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="C94" t="s">
-        <v>301</v>
-      </c>
-      <c r="F94" s="2" t="s">
+      <c r="B95" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="G94" t="s">
+      <c r="C95" t="s">
         <v>303</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7">
-      <c r="A95">
-        <v>6810</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C95" t="s">
-        <v>116</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>304</v>
       </c>
       <c r="G95" t="s">
-        <v>116</v>
+        <v>305</v>
       </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96">
-        <v>6820</v>
+        <v>6810</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C96" t="s">
         <v>116</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G96" t="s">
         <v>116</v>
@@ -7441,10 +7446,10 @@
     </row>
     <row r="97" spans="1:7">
       <c r="A97">
-        <v>6830</v>
+        <v>6820</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C97" t="s">
         <v>116</v>
@@ -7458,7 +7463,7 @@
     </row>
     <row r="98" spans="1:7">
       <c r="A98">
-        <v>6840</v>
+        <v>6830</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>308</v>
@@ -7475,7 +7480,7 @@
     </row>
     <row r="99" spans="1:7">
       <c r="A99">
-        <v>6850</v>
+        <v>6840</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>310</v>
@@ -7492,7 +7497,7 @@
     </row>
     <row r="100" spans="1:7">
       <c r="A100">
-        <v>6860</v>
+        <v>6850</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>312</v>
@@ -7509,7 +7514,7 @@
     </row>
     <row r="101" spans="1:7">
       <c r="A101">
-        <v>6870</v>
+        <v>6860</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>314</v>
@@ -7526,7 +7531,7 @@
     </row>
     <row r="102" spans="1:7">
       <c r="A102">
-        <v>6880</v>
+        <v>6870</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>316</v>
@@ -7543,7 +7548,7 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103">
-        <v>6890</v>
+        <v>6880</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>318</v>
@@ -7558,9 +7563,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="104" customFormat="1" spans="1:7">
+    <row r="104" spans="1:7">
       <c r="A104">
-        <v>6900</v>
+        <v>6890</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>320</v>
@@ -7577,7 +7582,7 @@
     </row>
     <row r="105" customFormat="1" spans="1:7">
       <c r="A105">
-        <v>6910</v>
+        <v>6900</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>322</v>
@@ -7592,46 +7597,46 @@
         <v>116</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" customFormat="1" spans="1:7">
       <c r="A106">
+        <v>6910</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C106" t="s">
+        <v>116</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G106" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107">
         <v>10010</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="C106" t="s">
-        <v>116</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="G106" t="s">
-        <v>116</v>
-      </c>
-      <c r="H106" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7">
-      <c r="A107">
-        <v>10100</v>
-      </c>
       <c r="B107" s="2" t="s">
-        <v>325</v>
+        <v>185</v>
       </c>
       <c r="C107" t="s">
         <v>116</v>
       </c>
       <c r="F107" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G107" t="s">
+        <v>116</v>
+      </c>
+      <c r="H107" t="s">
         <v>326</v>
-      </c>
-      <c r="G107" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="108" spans="1:7">
       <c r="A108">
-        <v>10101</v>
+        <v>10100</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>327</v>
@@ -7648,7 +7653,7 @@
     </row>
     <row r="109" spans="1:7">
       <c r="A109">
-        <v>10110</v>
+        <v>10101</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>329</v>
@@ -7665,7 +7670,7 @@
     </row>
     <row r="110" spans="1:7">
       <c r="A110">
-        <v>10120</v>
+        <v>10110</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>331</v>
@@ -7682,7 +7687,7 @@
     </row>
     <row r="111" spans="1:7">
       <c r="A111">
-        <v>10121</v>
+        <v>10120</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>333</v>
@@ -7699,7 +7704,7 @@
     </row>
     <row r="112" spans="1:7">
       <c r="A112">
-        <v>10130</v>
+        <v>10121</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>335</v>
@@ -7716,7 +7721,7 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113">
-        <v>10131</v>
+        <v>10130</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>337</v>
@@ -7731,9 +7736,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="114" ht="26" spans="1:7">
+    <row r="114" spans="1:7">
       <c r="A114">
-        <v>10132</v>
+        <v>10131</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>339</v>
@@ -7750,7 +7755,7 @@
     </row>
     <row r="115" ht="26" spans="1:7">
       <c r="A115">
-        <v>10133</v>
+        <v>10132</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>341</v>
@@ -7765,9 +7770,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" ht="26" spans="1:7">
       <c r="A116">
-        <v>10140</v>
+        <v>10133</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>343</v>
@@ -7784,7 +7789,7 @@
     </row>
     <row r="117" spans="1:7">
       <c r="A117">
-        <v>10141</v>
+        <v>10140</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>345</v>
@@ -7799,9 +7804,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="118" customFormat="1" spans="1:7">
+    <row r="118" spans="1:7">
       <c r="A118">
-        <v>10142</v>
+        <v>10141</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>347</v>
@@ -7818,7 +7823,7 @@
     </row>
     <row r="119" customFormat="1" spans="1:7">
       <c r="A119">
-        <v>10143</v>
+        <v>10142</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>349</v>
@@ -7833,9 +7838,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" customFormat="1" spans="1:7">
       <c r="A120">
-        <v>10150</v>
+        <v>10143</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>351</v>
@@ -7852,33 +7857,33 @@
     </row>
     <row r="121" spans="1:7">
       <c r="A121">
+        <v>10150</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C121" t="s">
+        <v>116</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="G121" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122">
         <v>10160</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C121" t="s">
-        <v>116</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="G121" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="122" customFormat="1" spans="1:7">
-      <c r="A122">
-        <v>10170</v>
-      </c>
       <c r="B122" s="2" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="C122" t="s">
         <v>116</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="G122" t="s">
         <v>116</v>
@@ -7886,7 +7891,7 @@
     </row>
     <row r="123" customFormat="1" spans="1:7">
       <c r="A123">
-        <v>10171</v>
+        <v>10170</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>355</v>
@@ -7901,9 +7906,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="124" customFormat="1" ht="26" spans="1:7">
+    <row r="124" customFormat="1" spans="1:7">
       <c r="A124">
-        <v>10180</v>
+        <v>10171</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>357</v>
@@ -7918,9 +7923,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="125" customFormat="1" spans="1:7">
+    <row r="125" customFormat="1" ht="26" spans="1:7">
       <c r="A125">
-        <v>10181</v>
+        <v>10180</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>359</v>
@@ -7935,9 +7940,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="126" customFormat="1" ht="26" spans="1:7">
+    <row r="126" customFormat="1" spans="1:7">
       <c r="A126">
-        <v>10182</v>
+        <v>10181</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>361</v>
@@ -7952,9 +7957,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="127" customFormat="1" spans="1:7">
+    <row r="127" customFormat="1" ht="26" spans="1:7">
       <c r="A127">
-        <v>10190</v>
+        <v>10182</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>363</v>
@@ -7969,9 +7974,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="128" customFormat="1" ht="26" spans="1:7">
+    <row r="128" customFormat="1" spans="1:7">
       <c r="A128">
-        <v>10200</v>
+        <v>10190</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>365</v>
@@ -7986,9 +7991,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="129" customFormat="1" spans="1:7">
+    <row r="129" customFormat="1" ht="26" spans="1:7">
       <c r="A129">
-        <v>10210</v>
+        <v>10200</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>367</v>
@@ -8005,7 +8010,7 @@
     </row>
     <row r="130" customFormat="1" spans="1:7">
       <c r="A130">
-        <v>10220</v>
+        <v>10210</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>369</v>
@@ -8014,18 +8019,18 @@
         <v>116</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G130" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="131" customFormat="1" ht="52" spans="1:7">
+    <row r="131" customFormat="1" spans="1:7">
       <c r="A131">
-        <v>10230</v>
+        <v>10220</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C131" t="s">
         <v>116</v>
@@ -8037,9 +8042,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="132" customFormat="1" spans="1:7">
+    <row r="132" customFormat="1" ht="52" spans="1:7">
       <c r="A132">
-        <v>10240</v>
+        <v>10230</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>372</v>
@@ -8048,52 +8053,52 @@
         <v>116</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>116</v>
+        <v>373</v>
       </c>
       <c r="G132" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="133" ht="26" spans="1:8">
+    <row r="133" customFormat="1" spans="1:7">
       <c r="A133">
+        <v>10240</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C133" t="s">
+        <v>116</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G133" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="134" ht="26" spans="1:8">
+      <c r="A134">
         <v>11010</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="C133" t="s">
-        <v>116</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="G133" t="s">
-        <v>116</v>
-      </c>
-      <c r="H133" t="s">
+      <c r="B134" s="2" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="134" ht="26" spans="1:7">
-      <c r="A134">
+      <c r="C134" t="s">
+        <v>116</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="G134" t="s">
+        <v>116</v>
+      </c>
+      <c r="H134" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="135" ht="26" spans="1:7">
+      <c r="A135">
         <v>11011</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="C134" t="s">
-        <v>116</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="G134" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="135" customFormat="1" spans="1:7">
-      <c r="A135">
-        <v>11012</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>378</v>
@@ -8110,7 +8115,7 @@
     </row>
     <row r="136" customFormat="1" spans="1:7">
       <c r="A136">
-        <v>11013</v>
+        <v>11012</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>380</v>
@@ -8127,7 +8132,7 @@
     </row>
     <row r="137" customFormat="1" spans="1:7">
       <c r="A137">
-        <v>11014</v>
+        <v>11013</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>382</v>
@@ -8142,9 +8147,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" customFormat="1" spans="1:7">
       <c r="A138">
-        <v>11020</v>
+        <v>11014</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>384</v>
@@ -8159,9 +8164,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="139" customFormat="1" spans="1:7">
+    <row r="139" spans="1:7">
       <c r="A139">
-        <v>11030</v>
+        <v>11020</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>386</v>
@@ -8176,9 +8181,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" customFormat="1" spans="1:7">
       <c r="A140">
-        <v>11040</v>
+        <v>11030</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>388</v>
@@ -8193,9 +8198,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="141" customFormat="1" spans="1:7">
+    <row r="141" spans="1:7">
       <c r="A141">
-        <v>11050</v>
+        <v>11040</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>390</v>
@@ -8212,7 +8217,7 @@
     </row>
     <row r="142" customFormat="1" spans="1:7">
       <c r="A142">
-        <v>11060</v>
+        <v>11050</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>392</v>
@@ -8229,7 +8234,7 @@
     </row>
     <row r="143" customFormat="1" spans="1:7">
       <c r="A143">
-        <v>11070</v>
+        <v>11060</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>394</v>
@@ -8244,9 +8249,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="144" ht="52" spans="1:8">
+    <row r="144" customFormat="1" spans="1:7">
       <c r="A144">
-        <v>12010</v>
+        <v>11070</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>396</v>
@@ -8260,21 +8265,18 @@
       <c r="G144" t="s">
         <v>116</v>
       </c>
-      <c r="H144" t="s">
+    </row>
+    <row r="145" ht="52" spans="1:8">
+      <c r="A145">
+        <v>12010</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="145" spans="1:8">
-      <c r="A145">
-        <v>13010</v>
-      </c>
-      <c r="B145" s="3" t="s">
-        <v>399</v>
-      </c>
       <c r="C145" t="s">
         <v>116</v>
       </c>
-      <c r="F145" s="3" t="s">
+      <c r="F145" s="2" t="s">
         <v>399</v>
       </c>
       <c r="G145" t="s">
@@ -8284,9 +8286,9 @@
         <v>400</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:8">
       <c r="A146">
-        <v>13020</v>
+        <v>13010</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>401</v>
@@ -8295,24 +8297,27 @@
         <v>116</v>
       </c>
       <c r="F146" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="G146" t="s">
+        <v>116</v>
+      </c>
+      <c r="H146" t="s">
         <v>402</v>
-      </c>
-      <c r="G146" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="147" spans="1:7">
       <c r="A147">
-        <v>13110</v>
-      </c>
-      <c r="B147" t="s">
+        <v>13020</v>
+      </c>
+      <c r="B147" s="3" t="s">
         <v>403</v>
       </c>
       <c r="C147" t="s">
         <v>116</v>
       </c>
-      <c r="F147" t="s">
-        <v>403</v>
+      <c r="F147" s="3" t="s">
+        <v>404</v>
       </c>
       <c r="G147" t="s">
         <v>116</v>
@@ -8320,15 +8325,15 @@
     </row>
     <row r="148" spans="1:7">
       <c r="A148">
-        <v>13210</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>404</v>
+        <v>13110</v>
+      </c>
+      <c r="B148" t="s">
+        <v>405</v>
       </c>
       <c r="C148" t="s">
         <v>116</v>
       </c>
-      <c r="F148" s="1" t="s">
+      <c r="F148" t="s">
         <v>405</v>
       </c>
       <c r="G148" t="s">
@@ -8337,7 +8342,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149">
-        <v>13220</v>
+        <v>13210</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>406</v>
@@ -8354,7 +8359,7 @@
     </row>
     <row r="150" spans="1:7">
       <c r="A150">
-        <v>13230</v>
+        <v>13220</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>408</v>
@@ -8371,41 +8376,41 @@
     </row>
     <row r="151" spans="1:7">
       <c r="A151">
+        <v>13230</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="C151" t="s">
+        <v>116</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="G151" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152">
         <v>13320</v>
       </c>
-      <c r="B151" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="C151" t="s">
-        <v>116</v>
-      </c>
-      <c r="F151" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="G151" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="152" customFormat="1" spans="1:7">
-      <c r="A152">
+      <c r="B152" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="C152" t="s">
+        <v>116</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="G152" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="153" customFormat="1" spans="1:7">
+      <c r="A153">
         <v>13410</v>
-      </c>
-      <c r="B152" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="C152" t="s">
-        <v>116</v>
-      </c>
-      <c r="F152" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="G152" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7">
-      <c r="A153">
-        <v>13510</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>414</v>
@@ -8420,9 +8425,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:7">
       <c r="A154">
-        <v>14010</v>
+        <v>13510</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>416</v>
@@ -8436,30 +8441,30 @@
       <c r="G154" t="s">
         <v>116</v>
       </c>
-      <c r="H154" t="s">
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155">
+        <v>14010</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>418</v>
       </c>
-    </row>
-    <row r="155" spans="1:7">
-      <c r="A155">
-        <v>14020</v>
-      </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" t="s">
+        <v>116</v>
+      </c>
+      <c r="F155" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="C155" t="s">
-        <v>116</v>
-      </c>
-      <c r="F155" s="1" t="s">
+      <c r="G155" t="s">
+        <v>116</v>
+      </c>
+      <c r="H155" t="s">
         <v>420</v>
-      </c>
-      <c r="G155" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="156" spans="1:7">
       <c r="A156">
-        <v>14021</v>
+        <v>14020</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>421</v>
@@ -8476,7 +8481,7 @@
     </row>
     <row r="157" spans="1:7">
       <c r="A157">
-        <v>14030</v>
+        <v>14021</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>423</v>
@@ -8493,7 +8498,7 @@
     </row>
     <row r="158" spans="1:7">
       <c r="A158">
-        <v>14040</v>
+        <v>14030</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>425</v>
@@ -8510,7 +8515,7 @@
     </row>
     <row r="159" spans="1:7">
       <c r="A159">
-        <v>14050</v>
+        <v>14040</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>427</v>
@@ -8527,16 +8532,16 @@
     </row>
     <row r="160" spans="1:7">
       <c r="A160">
-        <v>14060</v>
+        <v>14050</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>205</v>
+        <v>429</v>
       </c>
       <c r="C160" t="s">
         <v>116</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>205</v>
+        <v>430</v>
       </c>
       <c r="G160" t="s">
         <v>116</v>
@@ -8544,16 +8549,16 @@
     </row>
     <row r="161" spans="1:7">
       <c r="A161">
-        <v>14070</v>
-      </c>
-      <c r="B161" s="6" t="s">
-        <v>429</v>
+        <v>14060</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="C161" t="s">
         <v>116</v>
       </c>
-      <c r="F161" s="6" t="s">
-        <v>429</v>
+      <c r="F161" s="1" t="s">
+        <v>207</v>
       </c>
       <c r="G161" t="s">
         <v>116</v>
@@ -8561,15 +8566,15 @@
     </row>
     <row r="162" spans="1:7">
       <c r="A162">
-        <v>14080</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>430</v>
+        <v>14070</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>431</v>
       </c>
       <c r="C162" t="s">
         <v>116</v>
       </c>
-      <c r="F162" s="1" t="s">
+      <c r="F162" s="6" t="s">
         <v>431</v>
       </c>
       <c r="G162" t="s">
@@ -8578,7 +8583,7 @@
     </row>
     <row r="163" spans="1:7">
       <c r="A163">
-        <v>14090</v>
+        <v>14080</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>432</v>
@@ -8595,7 +8600,7 @@
     </row>
     <row r="164" spans="1:7">
       <c r="A164">
-        <v>14100</v>
+        <v>14090</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>434</v>
@@ -8604,7 +8609,7 @@
         <v>116</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G164" t="s">
         <v>116</v>
@@ -8612,27 +8617,27 @@
     </row>
     <row r="165" spans="1:7">
       <c r="A165">
+        <v>14100</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="C165" t="s">
+        <v>116</v>
+      </c>
+      <c r="F165" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="G165" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166">
         <v>14110</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="C165" t="s">
-        <v>116</v>
-      </c>
-      <c r="F165" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="G165" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="166" customFormat="1" spans="1:7">
-      <c r="A166">
-        <v>14120</v>
-      </c>
       <c r="B166" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C166" t="s">
         <v>116</v>
@@ -8646,7 +8651,7 @@
     </row>
     <row r="167" customFormat="1" spans="1:7">
       <c r="A167">
-        <v>14121</v>
+        <v>14120</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>438</v>
@@ -8655,7 +8660,7 @@
         <v>116</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>137</v>
+        <v>439</v>
       </c>
       <c r="G167" t="s">
         <v>116</v>
@@ -8663,16 +8668,16 @@
     </row>
     <row r="168" customFormat="1" spans="1:7">
       <c r="A168">
-        <v>14122</v>
+        <v>14121</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C168" t="s">
         <v>116</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>440</v>
+        <v>137</v>
       </c>
       <c r="G168" t="s">
         <v>116</v>
@@ -8680,7 +8685,7 @@
     </row>
     <row r="169" customFormat="1" spans="1:7">
       <c r="A169">
-        <v>14123</v>
+        <v>14122</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>441</v>
@@ -8697,7 +8702,7 @@
     </row>
     <row r="170" customFormat="1" spans="1:7">
       <c r="A170">
-        <v>14124</v>
+        <v>14123</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>443</v>
@@ -8714,7 +8719,7 @@
     </row>
     <row r="171" customFormat="1" spans="1:7">
       <c r="A171">
-        <v>14125</v>
+        <v>14124</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>445</v>
@@ -8731,7 +8736,7 @@
     </row>
     <row r="172" customFormat="1" spans="1:7">
       <c r="A172">
-        <v>14126</v>
+        <v>14125</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>447</v>
@@ -8748,7 +8753,7 @@
     </row>
     <row r="173" customFormat="1" spans="1:7">
       <c r="A173">
-        <v>14127</v>
+        <v>14126</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>449</v>
@@ -8765,7 +8770,7 @@
     </row>
     <row r="174" customFormat="1" spans="1:7">
       <c r="A174">
-        <v>14130</v>
+        <v>14127</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>451</v>
@@ -8782,16 +8787,16 @@
     </row>
     <row r="175" customFormat="1" spans="1:7">
       <c r="A175">
-        <v>14140</v>
+        <v>14130</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>225</v>
+        <v>453</v>
       </c>
       <c r="C175" t="s">
         <v>116</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>226</v>
+        <v>454</v>
       </c>
       <c r="G175" t="s">
         <v>116</v>
@@ -8799,16 +8804,16 @@
     </row>
     <row r="176" customFormat="1" spans="1:7">
       <c r="A176">
-        <v>14150</v>
+        <v>14140</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>430</v>
+        <v>227</v>
       </c>
       <c r="C176" t="s">
         <v>116</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>431</v>
+        <v>228</v>
       </c>
       <c r="G176" t="s">
         <v>116</v>
@@ -8816,16 +8821,16 @@
     </row>
     <row r="177" customFormat="1" spans="1:7">
       <c r="A177">
-        <v>14160</v>
+        <v>14150</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="C177" t="s">
         <v>116</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="G177" t="s">
         <v>116</v>
@@ -8833,7 +8838,7 @@
     </row>
     <row r="178" customFormat="1" spans="1:7">
       <c r="A178">
-        <v>14170</v>
+        <v>14160</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>455</v>
@@ -8850,7 +8855,7 @@
     </row>
     <row r="179" customFormat="1" spans="1:7">
       <c r="A179">
-        <v>14180</v>
+        <v>14170</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>457</v>
@@ -8867,7 +8872,7 @@
     </row>
     <row r="180" customFormat="1" spans="1:7">
       <c r="A180">
-        <v>14190</v>
+        <v>14180</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>459</v>
@@ -8875,31 +8880,31 @@
       <c r="C180" t="s">
         <v>116</v>
       </c>
-      <c r="F180" s="1"/>
+      <c r="F180" s="1" t="s">
+        <v>460</v>
+      </c>
       <c r="G180" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="181" customFormat="1" spans="1:7">
       <c r="A181">
-        <v>14200</v>
+        <v>14190</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C181" t="s">
         <v>116</v>
       </c>
-      <c r="F181" s="1" t="s">
-        <v>461</v>
-      </c>
+      <c r="F181" s="1"/>
       <c r="G181" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="182" customFormat="1" spans="1:7">
       <c r="A182">
-        <v>14210</v>
+        <v>14200</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>462</v>
@@ -8916,7 +8921,7 @@
     </row>
     <row r="183" customFormat="1" spans="1:7">
       <c r="A183">
-        <v>14220</v>
+        <v>14210</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>464</v>
@@ -8933,7 +8938,7 @@
     </row>
     <row r="184" customFormat="1" spans="1:7">
       <c r="A184">
-        <v>14230</v>
+        <v>14220</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>466</v>
@@ -8950,7 +8955,7 @@
     </row>
     <row r="185" customFormat="1" spans="1:7">
       <c r="A185">
-        <v>14231</v>
+        <v>14230</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>468</v>
@@ -8967,7 +8972,7 @@
     </row>
     <row r="186" customFormat="1" spans="1:7">
       <c r="A186">
-        <v>14240</v>
+        <v>14231</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>470</v>
@@ -8982,9 +8987,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="187" customFormat="1" spans="1:8">
+    <row r="187" customFormat="1" spans="1:7">
       <c r="A187">
-        <v>15010</v>
+        <v>14240</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>472</v>
@@ -8998,69 +9003,68 @@
       <c r="G187" t="s">
         <v>116</v>
       </c>
-      <c r="H187" t="s">
+    </row>
+    <row r="188" customFormat="1" spans="1:8">
+      <c r="A188">
+        <v>15010</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="188" customFormat="1" spans="1:7">
-      <c r="A188">
+      <c r="C188" t="s">
+        <v>116</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="G188" t="s">
+        <v>116</v>
+      </c>
+      <c r="H188" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="189" customFormat="1" spans="1:7">
+      <c r="A189">
         <v>15020</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C188" t="s">
-        <v>116</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="G188" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="189" ht="14" spans="1:9">
-      <c r="A189">
-        <v>16010</v>
-      </c>
-      <c r="B189" t="s">
-        <v>309</v>
+      <c r="B189" s="1" t="s">
+        <v>477</v>
       </c>
       <c r="C189" t="s">
         <v>116</v>
       </c>
-      <c r="F189" t="s">
-        <v>309</v>
+      <c r="F189" s="1" t="s">
+        <v>478</v>
       </c>
       <c r="G189" t="s">
         <v>116</v>
       </c>
-      <c r="H189" t="s">
-        <v>477</v>
-      </c>
-      <c r="I189" s="4"/>
     </row>
     <row r="190" ht="14" spans="1:9">
       <c r="A190">
-        <v>16020</v>
+        <v>16010</v>
       </c>
       <c r="B190" t="s">
-        <v>478</v>
+        <v>311</v>
       </c>
       <c r="C190" t="s">
         <v>116</v>
       </c>
       <c r="F190" t="s">
+        <v>311</v>
+      </c>
+      <c r="G190" t="s">
+        <v>116</v>
+      </c>
+      <c r="H190" t="s">
         <v>479</v>
-      </c>
-      <c r="G190" t="s">
-        <v>116</v>
       </c>
       <c r="I190" s="4"/>
     </row>
     <row r="191" ht="14" spans="1:9">
       <c r="A191">
-        <v>16030</v>
+        <v>16020</v>
       </c>
       <c r="B191" t="s">
         <v>480</v>
@@ -9078,7 +9082,7 @@
     </row>
     <row r="192" ht="14" spans="1:9">
       <c r="A192">
-        <v>16040</v>
+        <v>16030</v>
       </c>
       <c r="B192" t="s">
         <v>482</v>
@@ -9087,7 +9091,7 @@
         <v>116</v>
       </c>
       <c r="F192" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G192" t="s">
         <v>116</v>
@@ -9096,51 +9100,52 @@
     </row>
     <row r="193" ht="14" spans="1:9">
       <c r="A193">
+        <v>16040</v>
+      </c>
+      <c r="B193" t="s">
+        <v>484</v>
+      </c>
+      <c r="C193" t="s">
+        <v>116</v>
+      </c>
+      <c r="F193" t="s">
+        <v>484</v>
+      </c>
+      <c r="G193" t="s">
+        <v>116</v>
+      </c>
+      <c r="I193" s="4"/>
+    </row>
+    <row r="194" ht="14" spans="1:9">
+      <c r="A194">
         <v>16041</v>
       </c>
-      <c r="B193" t="s">
-        <v>482</v>
-      </c>
-      <c r="C193" t="s">
-        <v>116</v>
-      </c>
-      <c r="F193" t="s">
-        <v>482</v>
-      </c>
-      <c r="G193" t="s">
-        <v>116</v>
-      </c>
-      <c r="I193" s="4"/>
-    </row>
-    <row r="194" spans="1:7">
-      <c r="A194">
-        <v>16100</v>
-      </c>
       <c r="B194" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C194" t="s">
         <v>116</v>
       </c>
       <c r="F194" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G194" t="s">
         <v>116</v>
       </c>
+      <c r="I194" s="4"/>
     </row>
     <row r="195" spans="1:7">
       <c r="A195">
-        <v>16110</v>
+        <v>16100</v>
       </c>
       <c r="B195" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C195" t="s">
         <v>116</v>
       </c>
       <c r="F195" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G195" t="s">
         <v>116</v>
@@ -9148,10 +9153,10 @@
     </row>
     <row r="196" spans="1:7">
       <c r="A196">
-        <v>16200</v>
+        <v>16110</v>
       </c>
       <c r="B196" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C196" t="s">
         <v>116</v>
@@ -9165,7 +9170,7 @@
     </row>
     <row r="197" spans="1:7">
       <c r="A197">
-        <v>16210</v>
+        <v>16200</v>
       </c>
       <c r="B197" t="s">
         <v>487</v>
@@ -9182,7 +9187,7 @@
     </row>
     <row r="198" spans="1:7">
       <c r="A198">
-        <v>16220</v>
+        <v>16210</v>
       </c>
       <c r="B198" t="s">
         <v>489</v>
@@ -9199,7 +9204,7 @@
     </row>
     <row r="199" spans="1:7">
       <c r="A199">
-        <v>16230</v>
+        <v>16220</v>
       </c>
       <c r="B199" t="s">
         <v>491</v>
@@ -9216,15 +9221,15 @@
     </row>
     <row r="200" spans="1:7">
       <c r="A200">
-        <v>16400</v>
-      </c>
-      <c r="B200" s="2" t="s">
+        <v>16230</v>
+      </c>
+      <c r="B200" t="s">
         <v>493</v>
       </c>
       <c r="C200" t="s">
         <v>116</v>
       </c>
-      <c r="F200" s="2" t="s">
+      <c r="F200" t="s">
         <v>494</v>
       </c>
       <c r="G200" t="s">
@@ -9233,7 +9238,7 @@
     </row>
     <row r="201" spans="1:7">
       <c r="A201">
-        <v>16410</v>
+        <v>16400</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>495</v>
@@ -9248,187 +9253,187 @@
         <v>116</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:7">
       <c r="A202">
-        <v>16800</v>
-      </c>
-      <c r="B202" t="s">
-        <v>159</v>
+        <v>16410</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>497</v>
       </c>
       <c r="C202" t="s">
         <v>116</v>
       </c>
-      <c r="F202" t="s">
-        <v>159</v>
+      <c r="F202" s="2" t="s">
+        <v>498</v>
       </c>
       <c r="G202" t="s">
         <v>116</v>
-      </c>
-      <c r="H202" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="203" spans="1:8">
       <c r="A203">
-        <v>16801</v>
+        <v>16800</v>
       </c>
       <c r="B203" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C203" t="s">
         <v>116</v>
       </c>
       <c r="F203" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G203" t="s">
         <v>116</v>
       </c>
       <c r="H203" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="204" spans="1:8">
       <c r="A204">
-        <v>16802</v>
+        <v>16801</v>
       </c>
       <c r="B204" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C204" t="s">
         <v>116</v>
       </c>
       <c r="F204" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G204" t="s">
         <v>116</v>
       </c>
       <c r="H204" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205">
-        <v>16803</v>
+        <v>16802</v>
       </c>
       <c r="B205" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C205" t="s">
         <v>116</v>
       </c>
       <c r="F205" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G205" t="s">
         <v>116</v>
       </c>
       <c r="H205" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="206" spans="1:8">
       <c r="A206">
-        <v>16804</v>
+        <v>16803</v>
       </c>
       <c r="B206" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C206" t="s">
         <v>116</v>
       </c>
       <c r="F206" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G206" t="s">
         <v>116</v>
       </c>
       <c r="H206" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="207" spans="1:8">
       <c r="A207">
-        <v>16805</v>
+        <v>16804</v>
       </c>
       <c r="B207" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C207" t="s">
         <v>116</v>
       </c>
       <c r="F207" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G207" t="s">
         <v>116</v>
       </c>
       <c r="H207" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="208" spans="1:8">
       <c r="A208">
+        <v>16805</v>
+      </c>
+      <c r="B208" t="s">
+        <v>164</v>
+      </c>
+      <c r="C208" t="s">
+        <v>116</v>
+      </c>
+      <c r="F208" t="s">
+        <v>164</v>
+      </c>
+      <c r="G208" t="s">
+        <v>116</v>
+      </c>
+      <c r="H208" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="A209">
         <v>16806</v>
       </c>
-      <c r="B208" t="s">
+      <c r="B209" t="s">
         <v>165</v>
       </c>
-      <c r="C208" t="s">
-        <v>116</v>
-      </c>
-      <c r="F208" t="s">
+      <c r="C209" t="s">
+        <v>116</v>
+      </c>
+      <c r="F209" t="s">
         <v>165</v>
       </c>
-      <c r="G208" t="s">
-        <v>116</v>
-      </c>
-      <c r="H208" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="209" ht="14" spans="1:9">
-      <c r="A209">
+      <c r="G209" t="s">
+        <v>116</v>
+      </c>
+      <c r="H209" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="210" ht="14" spans="1:9">
+      <c r="A210">
         <v>19000</v>
       </c>
-      <c r="B209" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="C209" t="s">
-        <v>116</v>
-      </c>
-      <c r="F209" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="G209" t="s">
-        <v>116</v>
-      </c>
-      <c r="H209" t="s">
+      <c r="B210" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="I209" s="4"/>
-    </row>
-    <row r="210" spans="1:7">
-      <c r="A210">
-        <v>19001</v>
-      </c>
-      <c r="B210" s="1" t="s">
+      <c r="C210" t="s">
+        <v>116</v>
+      </c>
+      <c r="F210" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="C210" t="s">
-        <v>116</v>
-      </c>
-      <c r="F210" s="1" t="s">
+      <c r="G210" t="s">
+        <v>116</v>
+      </c>
+      <c r="H210" t="s">
         <v>502</v>
       </c>
-      <c r="G210" t="s">
-        <v>116</v>
-      </c>
+      <c r="I210" s="4"/>
     </row>
     <row r="211" spans="1:7">
       <c r="A211">
-        <v>19002</v>
+        <v>19001</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>503</v>
@@ -9445,7 +9450,7 @@
     </row>
     <row r="212" spans="1:7">
       <c r="A212">
-        <v>19003</v>
+        <v>19002</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>505</v>
@@ -9462,7 +9467,7 @@
     </row>
     <row r="213" spans="1:7">
       <c r="A213">
-        <v>19004</v>
+        <v>19003</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>507</v>
@@ -9479,7 +9484,7 @@
     </row>
     <row r="214" spans="1:7">
       <c r="A214">
-        <v>19005</v>
+        <v>19004</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>509</v>
@@ -9488,7 +9493,7 @@
         <v>116</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>8</v>
+        <v>510</v>
       </c>
       <c r="G214" t="s">
         <v>116</v>
@@ -9496,16 +9501,16 @@
     </row>
     <row r="215" spans="1:7">
       <c r="A215">
-        <v>19006</v>
+        <v>19005</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C215" t="s">
         <v>116</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>418</v>
+        <v>8</v>
       </c>
       <c r="G215" t="s">
         <v>116</v>
@@ -9513,16 +9518,16 @@
     </row>
     <row r="216" spans="1:7">
       <c r="A216">
-        <v>19007</v>
+        <v>19006</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C216" t="s">
         <v>116</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>9</v>
+        <v>420</v>
       </c>
       <c r="G216" t="s">
         <v>116</v>
@@ -9530,16 +9535,16 @@
     </row>
     <row r="217" spans="1:7">
       <c r="A217">
-        <v>19100</v>
+        <v>19007</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C217" t="s">
         <v>116</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>513</v>
+        <v>9</v>
       </c>
       <c r="G217" t="s">
         <v>116</v>
@@ -9547,50 +9552,50 @@
     </row>
     <row r="218" spans="1:7">
       <c r="A218">
-        <v>19101</v>
-      </c>
-      <c r="B218" t="s">
-        <v>40</v>
+        <v>19100</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>514</v>
       </c>
       <c r="C218" t="s">
-        <v>514</v>
-      </c>
-      <c r="F218" t="s">
+        <v>116</v>
+      </c>
+      <c r="F218" s="1" t="s">
         <v>515</v>
       </c>
       <c r="G218" t="s">
-        <v>516</v>
+        <v>116</v>
       </c>
     </row>
     <row r="219" spans="1:7">
       <c r="A219">
-        <v>19102</v>
-      </c>
-      <c r="B219" s="2" t="s">
+        <v>19101</v>
+      </c>
+      <c r="B219" t="s">
+        <v>40</v>
+      </c>
+      <c r="C219" t="s">
+        <v>516</v>
+      </c>
+      <c r="F219" t="s">
         <v>517</v>
       </c>
-      <c r="C219" t="s">
-        <v>116</v>
-      </c>
-      <c r="F219" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="G219" t="s">
-        <v>116</v>
+        <v>518</v>
       </c>
     </row>
     <row r="220" spans="1:7">
       <c r="A220">
-        <v>19103</v>
+        <v>19102</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C220" t="s">
         <v>116</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>519</v>
+        <v>113</v>
       </c>
       <c r="G220" t="s">
         <v>116</v>
@@ -9598,7 +9603,7 @@
     </row>
     <row r="221" spans="1:7">
       <c r="A221">
-        <v>19104</v>
+        <v>19103</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>520</v>
@@ -9615,7 +9620,7 @@
     </row>
     <row r="222" spans="1:7">
       <c r="A222">
-        <v>19105</v>
+        <v>19104</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>522</v>
@@ -9632,7 +9637,7 @@
     </row>
     <row r="223" spans="1:7">
       <c r="A223">
-        <v>19106</v>
+        <v>19105</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>524</v>
@@ -9649,7 +9654,7 @@
     </row>
     <row r="224" spans="1:7">
       <c r="A224">
-        <v>19107</v>
+        <v>19106</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>526</v>
@@ -9666,7 +9671,7 @@
     </row>
     <row r="225" spans="1:7">
       <c r="A225">
-        <v>19108</v>
+        <v>19107</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>528</v>
@@ -9683,7 +9688,7 @@
     </row>
     <row r="226" spans="1:7">
       <c r="A226">
-        <v>19109</v>
+        <v>19108</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>530</v>
@@ -9698,55 +9703,55 @@
         <v>116</v>
       </c>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:7">
       <c r="A227">
+        <v>19109</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="C227" t="s">
+        <v>116</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="G227" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8">
+      <c r="A228">
         <v>20010</v>
       </c>
-      <c r="B227" t="s">
-        <v>532</v>
-      </c>
-      <c r="C227" t="s">
-        <v>116</v>
-      </c>
-      <c r="F227" t="s">
-        <v>533</v>
-      </c>
-      <c r="G227" t="s">
-        <v>116</v>
-      </c>
-      <c r="H227" t="s">
+      <c r="B228" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="228" spans="1:7">
-      <c r="A228">
-        <v>20020</v>
-      </c>
-      <c r="B228" t="s">
+      <c r="C228" t="s">
+        <v>116</v>
+      </c>
+      <c r="F228" t="s">
         <v>535</v>
       </c>
-      <c r="C228" t="s">
-        <v>116</v>
-      </c>
-      <c r="F228" t="s">
+      <c r="G228" t="s">
+        <v>116</v>
+      </c>
+      <c r="H228" t="s">
         <v>536</v>
-      </c>
-      <c r="G228" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="229" spans="1:7">
       <c r="A229">
-        <v>20030</v>
-      </c>
-      <c r="B229" s="2" t="s">
+        <v>20020</v>
+      </c>
+      <c r="B229" t="s">
         <v>537</v>
       </c>
       <c r="C229" t="s">
         <v>116</v>
       </c>
-      <c r="F229" s="2" t="s">
-        <v>537</v>
+      <c r="F229" t="s">
+        <v>538</v>
       </c>
       <c r="G229" t="s">
         <v>116</v>
@@ -9754,15 +9759,15 @@
     </row>
     <row r="230" spans="1:7">
       <c r="A230">
-        <v>20040</v>
-      </c>
-      <c r="B230" t="s">
-        <v>538</v>
+        <v>20030</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>539</v>
       </c>
       <c r="C230" t="s">
         <v>116</v>
       </c>
-      <c r="F230" t="s">
+      <c r="F230" s="2" t="s">
         <v>539</v>
       </c>
       <c r="G230" t="s">
@@ -9771,7 +9776,7 @@
     </row>
     <row r="231" spans="1:7">
       <c r="A231">
-        <v>20050</v>
+        <v>20040</v>
       </c>
       <c r="B231" t="s">
         <v>540</v>
@@ -9788,7 +9793,7 @@
     </row>
     <row r="232" spans="1:7">
       <c r="A232">
-        <v>20100</v>
+        <v>20050</v>
       </c>
       <c r="B232" t="s">
         <v>542</v>
@@ -9805,7 +9810,7 @@
     </row>
     <row r="233" spans="1:7">
       <c r="A233">
-        <v>20110</v>
+        <v>20100</v>
       </c>
       <c r="B233" t="s">
         <v>544</v>
@@ -9814,7 +9819,7 @@
         <v>116</v>
       </c>
       <c r="F233" t="s">
-        <v>420</v>
+        <v>545</v>
       </c>
       <c r="G233" t="s">
         <v>116</v>
@@ -9822,16 +9827,16 @@
     </row>
     <row r="234" spans="1:7">
       <c r="A234">
-        <v>20111</v>
+        <v>20110</v>
       </c>
       <c r="B234" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C234" t="s">
         <v>116</v>
       </c>
       <c r="F234" t="s">
-        <v>546</v>
+        <v>422</v>
       </c>
       <c r="G234" t="s">
         <v>116</v>
@@ -9839,7 +9844,7 @@
     </row>
     <row r="235" spans="1:7">
       <c r="A235">
-        <v>20120</v>
+        <v>20111</v>
       </c>
       <c r="B235" t="s">
         <v>547</v>
@@ -9854,9 +9859,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="236" customFormat="1" spans="1:7">
+    <row r="236" spans="1:7">
       <c r="A236">
-        <v>20130</v>
+        <v>20120</v>
       </c>
       <c r="B236" t="s">
         <v>549</v>
@@ -9871,9 +9876,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="237" spans="1:7">
+    <row r="237" customFormat="1" spans="1:7">
       <c r="A237">
-        <v>20200</v>
+        <v>20130</v>
       </c>
       <c r="B237" t="s">
         <v>551</v>
@@ -9890,7 +9895,7 @@
     </row>
     <row r="238" spans="1:7">
       <c r="A238">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B238" t="s">
         <v>553</v>
@@ -9907,7 +9912,7 @@
     </row>
     <row r="239" spans="1:7">
       <c r="A239">
-        <v>20210</v>
+        <v>20201</v>
       </c>
       <c r="B239" t="s">
         <v>555</v>
@@ -9916,7 +9921,7 @@
         <v>116</v>
       </c>
       <c r="F239" t="s">
-        <v>548</v>
+        <v>556</v>
       </c>
       <c r="G239" t="s">
         <v>116</v>
@@ -9924,16 +9929,16 @@
     </row>
     <row r="240" spans="1:7">
       <c r="A240">
-        <v>20220</v>
+        <v>20210</v>
       </c>
       <c r="B240" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C240" t="s">
         <v>116</v>
       </c>
       <c r="F240" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="G240" t="s">
         <v>116</v>
@@ -9941,15 +9946,15 @@
     </row>
     <row r="241" spans="1:7">
       <c r="A241">
-        <v>20230</v>
-      </c>
-      <c r="B241" s="2" t="s">
+        <v>20220</v>
+      </c>
+      <c r="B241" t="s">
         <v>558</v>
       </c>
       <c r="C241" t="s">
         <v>116</v>
       </c>
-      <c r="F241" s="2" t="s">
+      <c r="F241" t="s">
         <v>559</v>
       </c>
       <c r="G241" t="s">
@@ -9958,7 +9963,7 @@
     </row>
     <row r="242" spans="1:7">
       <c r="A242">
-        <v>20240</v>
+        <v>20230</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>560</v>
@@ -9975,7 +9980,7 @@
     </row>
     <row r="243" spans="1:7">
       <c r="A243">
-        <v>20250</v>
+        <v>20240</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>562</v>
@@ -9992,24 +9997,24 @@
     </row>
     <row r="244" spans="1:7">
       <c r="A244">
+        <v>20250</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="C244" t="s">
+        <v>116</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="G244" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245">
         <v>20270</v>
-      </c>
-      <c r="B244" t="s">
-        <v>564</v>
-      </c>
-      <c r="C244" t="s">
-        <v>116</v>
-      </c>
-      <c r="F244" t="s">
-        <v>565</v>
-      </c>
-      <c r="G244" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="245" customFormat="1" spans="1:7">
-      <c r="A245">
-        <v>20280</v>
       </c>
       <c r="B245" t="s">
         <v>566</v>
@@ -10024,9 +10029,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="246" spans="1:7">
+    <row r="246" customFormat="1" spans="1:7">
       <c r="A246">
-        <v>20300</v>
+        <v>20280</v>
       </c>
       <c r="B246" t="s">
         <v>568</v>
@@ -10043,13 +10048,16 @@
     </row>
     <row r="247" spans="1:7">
       <c r="A247">
-        <v>20301</v>
+        <v>20300</v>
       </c>
       <c r="B247" t="s">
-        <v>183</v>
+        <v>570</v>
       </c>
       <c r="C247" t="s">
         <v>116</v>
+      </c>
+      <c r="F247" t="s">
+        <v>571</v>
       </c>
       <c r="G247" t="s">
         <v>116</v>
@@ -10057,16 +10065,13 @@
     </row>
     <row r="248" spans="1:7">
       <c r="A248">
-        <v>20310</v>
+        <v>20301</v>
       </c>
       <c r="B248" t="s">
-        <v>570</v>
+        <v>185</v>
       </c>
       <c r="C248" t="s">
         <v>116</v>
-      </c>
-      <c r="F248" t="s">
-        <v>571</v>
       </c>
       <c r="G248" t="s">
         <v>116</v>
@@ -10074,16 +10079,16 @@
     </row>
     <row r="249" spans="1:7">
       <c r="A249">
-        <v>20320</v>
+        <v>20310</v>
       </c>
       <c r="B249" t="s">
-        <v>217</v>
+        <v>572</v>
       </c>
       <c r="C249" t="s">
         <v>116</v>
       </c>
       <c r="F249" t="s">
-        <v>218</v>
+        <v>573</v>
       </c>
       <c r="G249" t="s">
         <v>116</v>
@@ -10091,24 +10096,24 @@
     </row>
     <row r="250" spans="1:7">
       <c r="A250">
+        <v>20320</v>
+      </c>
+      <c r="B250" t="s">
+        <v>219</v>
+      </c>
+      <c r="C250" t="s">
+        <v>116</v>
+      </c>
+      <c r="F250" t="s">
+        <v>220</v>
+      </c>
+      <c r="G250" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251">
         <v>20330</v>
-      </c>
-      <c r="B250" t="s">
-        <v>572</v>
-      </c>
-      <c r="C250" t="s">
-        <v>116</v>
-      </c>
-      <c r="F250" t="s">
-        <v>573</v>
-      </c>
-      <c r="G250" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6">
-      <c r="A251">
-        <v>20340</v>
       </c>
       <c r="B251" t="s">
         <v>574</v>
@@ -10119,10 +10124,13 @@
       <c r="F251" t="s">
         <v>575</v>
       </c>
+      <c r="G251" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="252" spans="1:6">
       <c r="A252">
-        <v>20350</v>
+        <v>20340</v>
       </c>
       <c r="B252" t="s">
         <v>576</v>
@@ -10134,9 +10142,9 @@
         <v>577</v>
       </c>
     </row>
-    <row r="253" customFormat="1" spans="1:6">
+    <row r="253" spans="1:6">
       <c r="A253">
-        <v>20360</v>
+        <v>20350</v>
       </c>
       <c r="B253" t="s">
         <v>578</v>
@@ -10150,7 +10158,7 @@
     </row>
     <row r="254" customFormat="1" spans="1:6">
       <c r="A254">
-        <v>20370</v>
+        <v>20360</v>
       </c>
       <c r="B254" t="s">
         <v>580</v>
@@ -10164,7 +10172,7 @@
     </row>
     <row r="255" customFormat="1" spans="1:6">
       <c r="A255">
-        <v>20380</v>
+        <v>20370</v>
       </c>
       <c r="B255" t="s">
         <v>582</v>
@@ -10178,7 +10186,7 @@
     </row>
     <row r="256" customFormat="1" spans="1:6">
       <c r="A256">
-        <v>20390</v>
+        <v>20380</v>
       </c>
       <c r="B256" t="s">
         <v>584</v>
@@ -10192,7 +10200,7 @@
     </row>
     <row r="257" customFormat="1" spans="1:6">
       <c r="A257">
-        <v>20400</v>
+        <v>20390</v>
       </c>
       <c r="B257" t="s">
         <v>586</v>
@@ -10204,9 +10212,9 @@
         <v>587</v>
       </c>
     </row>
-    <row r="258" customFormat="1" spans="1:8">
+    <row r="258" customFormat="1" spans="1:6">
       <c r="A258">
-        <v>20410</v>
+        <v>20400</v>
       </c>
       <c r="B258" t="s">
         <v>588</v>
@@ -10217,27 +10225,27 @@
       <c r="F258" t="s">
         <v>589</v>
       </c>
-      <c r="H258" t="s">
+    </row>
+    <row r="259" customFormat="1" spans="1:8">
+      <c r="A259">
+        <v>20410</v>
+      </c>
+      <c r="B259" t="s">
         <v>590</v>
       </c>
-    </row>
-    <row r="259" customFormat="1" spans="1:6">
-      <c r="A259">
-        <v>20411</v>
-      </c>
-      <c r="B259" t="s">
+      <c r="C259" t="s">
+        <v>116</v>
+      </c>
+      <c r="F259" t="s">
         <v>591</v>
       </c>
-      <c r="C259" t="s">
-        <v>116</v>
-      </c>
-      <c r="F259" t="s">
+      <c r="H259" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="260" customFormat="1" spans="1:6">
       <c r="A260">
-        <v>20420</v>
+        <v>20411</v>
       </c>
       <c r="B260" t="s">
         <v>593</v>
@@ -10251,7 +10259,7 @@
     </row>
     <row r="261" customFormat="1" spans="1:6">
       <c r="A261">
-        <v>20430</v>
+        <v>20420</v>
       </c>
       <c r="B261" t="s">
         <v>595</v>
@@ -10265,7 +10273,7 @@
     </row>
     <row r="262" customFormat="1" spans="1:6">
       <c r="A262">
-        <v>20440</v>
+        <v>20430</v>
       </c>
       <c r="B262" t="s">
         <v>597</v>
@@ -10277,9 +10285,9 @@
         <v>598</v>
       </c>
     </row>
-    <row r="263" spans="1:8">
+    <row r="263" customFormat="1" spans="1:6">
       <c r="A263">
-        <v>31010</v>
+        <v>20440</v>
       </c>
       <c r="B263" t="s">
         <v>599</v>
@@ -10290,27 +10298,27 @@
       <c r="F263" t="s">
         <v>600</v>
       </c>
-      <c r="H263" t="s">
+    </row>
+    <row r="264" spans="1:8">
+      <c r="A264">
+        <v>31010</v>
+      </c>
+      <c r="B264" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="264" spans="1:6">
-      <c r="A264">
+      <c r="C264" t="s">
+        <v>116</v>
+      </c>
+      <c r="F264" t="s">
+        <v>602</v>
+      </c>
+      <c r="H264" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265">
         <v>31020</v>
-      </c>
-      <c r="B264" t="s">
-        <v>602</v>
-      </c>
-      <c r="C264" t="s">
-        <v>116</v>
-      </c>
-      <c r="F264" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="265" customFormat="1" spans="1:6">
-      <c r="A265">
-        <v>31030</v>
       </c>
       <c r="B265" t="s">
         <v>604</v>
@@ -10319,29 +10327,29 @@
         <v>116</v>
       </c>
       <c r="F265" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="266" customFormat="1" spans="1:6">
       <c r="A266">
+        <v>31030</v>
+      </c>
+      <c r="B266" t="s">
+        <v>606</v>
+      </c>
+      <c r="C266" t="s">
+        <v>116</v>
+      </c>
+      <c r="F266" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="267" customFormat="1" spans="1:6">
+      <c r="A267">
         <v>31040</v>
       </c>
-      <c r="B266" t="s">
-        <v>605</v>
-      </c>
-      <c r="C266" t="s">
-        <v>116</v>
-      </c>
-      <c r="F266" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6">
-      <c r="A267">
-        <v>31050</v>
-      </c>
       <c r="B267" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C267" t="s">
         <v>116</v>
@@ -10350,9 +10358,9 @@
         <v>607</v>
       </c>
     </row>
-    <row r="268" customFormat="1" spans="1:6">
+    <row r="268" spans="1:6">
       <c r="A268">
-        <v>31060</v>
+        <v>31050</v>
       </c>
       <c r="B268" t="s">
         <v>608</v>
@@ -10366,7 +10374,7 @@
     </row>
     <row r="269" customFormat="1" spans="1:6">
       <c r="A269">
-        <v>31061</v>
+        <v>31060</v>
       </c>
       <c r="B269" t="s">
         <v>610</v>
@@ -10378,11 +10386,11 @@
         <v>611</v>
       </c>
     </row>
-    <row r="270" customFormat="1" spans="1:7">
+    <row r="270" customFormat="1" spans="1:6">
       <c r="A270">
-        <v>31070</v>
-      </c>
-      <c r="B270" s="2" t="s">
+        <v>31061</v>
+      </c>
+      <c r="B270" t="s">
         <v>612</v>
       </c>
       <c r="C270" t="s">
@@ -10391,13 +10399,10 @@
       <c r="F270" t="s">
         <v>613</v>
       </c>
-      <c r="G270" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="271" customFormat="1" ht="26" spans="1:7">
+    </row>
+    <row r="271" customFormat="1" spans="1:7">
       <c r="A271">
-        <v>31071</v>
+        <v>31070</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>614</v>
@@ -10405,53 +10410,50 @@
       <c r="C271" t="s">
         <v>116</v>
       </c>
-      <c r="F271" s="2" t="s">
+      <c r="F271" t="s">
         <v>615</v>
       </c>
       <c r="G271" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="272" customFormat="1" spans="1:7">
+    <row r="272" customFormat="1" ht="26" spans="1:7">
       <c r="A272">
+        <v>31071</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C272" t="s">
+        <v>116</v>
+      </c>
+      <c r="F272" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="G272" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="273" customFormat="1" spans="1:7">
+      <c r="A273">
         <v>31080</v>
       </c>
-      <c r="B272" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="C272" t="s">
-        <v>116</v>
-      </c>
-      <c r="F272" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="G272" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8">
-      <c r="A273">
+      <c r="B273" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="C273" t="s">
+        <v>116</v>
+      </c>
+      <c r="F273" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="G273" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8">
+      <c r="A274">
         <v>32010</v>
-      </c>
-      <c r="B273" t="s">
-        <v>616</v>
-      </c>
-      <c r="C273" t="s">
-        <v>116</v>
-      </c>
-      <c r="F273" t="s">
-        <v>607</v>
-      </c>
-      <c r="G273" t="s">
-        <v>116</v>
-      </c>
-      <c r="H273" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7">
-      <c r="A274">
-        <v>32020</v>
       </c>
       <c r="B274" t="s">
         <v>618</v>
@@ -10460,18 +10462,21 @@
         <v>116</v>
       </c>
       <c r="F274" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="G274" t="s">
         <v>116</v>
+      </c>
+      <c r="H274" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="275" spans="1:7">
       <c r="A275">
-        <v>32030</v>
+        <v>32020</v>
       </c>
       <c r="B275" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C275" t="s">
         <v>116</v>
@@ -10485,7 +10490,7 @@
     </row>
     <row r="276" spans="1:7">
       <c r="A276">
-        <v>32040</v>
+        <v>32030</v>
       </c>
       <c r="B276" t="s">
         <v>621</v>
@@ -10502,7 +10507,7 @@
     </row>
     <row r="277" spans="1:7">
       <c r="A277">
-        <v>32050</v>
+        <v>32040</v>
       </c>
       <c r="B277" t="s">
         <v>623</v>
@@ -10519,7 +10524,7 @@
     </row>
     <row r="278" spans="1:7">
       <c r="A278">
-        <v>32060</v>
+        <v>32050</v>
       </c>
       <c r="B278" t="s">
         <v>625</v>
@@ -10528,7 +10533,7 @@
         <v>116</v>
       </c>
       <c r="F278" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G278" t="s">
         <v>116</v>
@@ -10536,16 +10541,16 @@
     </row>
     <row r="279" spans="1:7">
       <c r="A279">
-        <v>32070</v>
+        <v>32060</v>
       </c>
       <c r="B279" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C279" t="s">
         <v>116</v>
       </c>
       <c r="F279" t="s">
-        <v>178</v>
+        <v>627</v>
       </c>
       <c r="G279" t="s">
         <v>116</v>
@@ -10553,16 +10558,16 @@
     </row>
     <row r="280" spans="1:7">
       <c r="A280">
-        <v>32080</v>
+        <v>32070</v>
       </c>
       <c r="B280" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C280" t="s">
         <v>116</v>
       </c>
       <c r="F280" t="s">
-        <v>203</v>
+        <v>180</v>
       </c>
       <c r="G280" t="s">
         <v>116</v>
@@ -10570,16 +10575,16 @@
     </row>
     <row r="281" spans="1:7">
       <c r="A281">
-        <v>32090</v>
+        <v>32080</v>
       </c>
       <c r="B281" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C281" t="s">
         <v>116</v>
       </c>
       <c r="F281" t="s">
-        <v>628</v>
+        <v>205</v>
       </c>
       <c r="G281" t="s">
         <v>116</v>
@@ -10587,16 +10592,16 @@
     </row>
     <row r="282" spans="1:7">
       <c r="A282">
-        <v>32091</v>
+        <v>32090</v>
       </c>
       <c r="B282" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C282" t="s">
         <v>116</v>
       </c>
       <c r="F282" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G282" t="s">
         <v>116</v>
@@ -10604,16 +10609,16 @@
     </row>
     <row r="283" spans="1:7">
       <c r="A283">
-        <v>32092</v>
+        <v>32091</v>
       </c>
       <c r="B283" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C283" t="s">
         <v>116</v>
       </c>
       <c r="F283" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G283" t="s">
         <v>116</v>
@@ -10621,10 +10626,10 @@
     </row>
     <row r="284" spans="1:7">
       <c r="A284">
-        <v>32100</v>
+        <v>32092</v>
       </c>
       <c r="B284" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C284" t="s">
         <v>116</v>
@@ -10636,9 +10641,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="285" customFormat="1" spans="1:7">
+    <row r="285" spans="1:7">
       <c r="A285">
-        <v>32110</v>
+        <v>32100</v>
       </c>
       <c r="B285" t="s">
         <v>633</v>
@@ -10653,9 +10658,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="286" spans="1:8">
+    <row r="286" customFormat="1" spans="1:7">
       <c r="A286">
-        <v>33010</v>
+        <v>32110</v>
       </c>
       <c r="B286" t="s">
         <v>635</v>
@@ -10669,39 +10674,39 @@
       <c r="G286" t="s">
         <v>116</v>
       </c>
-      <c r="H286" t="s">
+    </row>
+    <row r="287" spans="1:8">
+      <c r="A287">
+        <v>33010</v>
+      </c>
+      <c r="B287" t="s">
         <v>637</v>
       </c>
-    </row>
-    <row r="287" spans="1:7">
-      <c r="A287">
-        <v>33011</v>
-      </c>
-      <c r="B287" t="s">
+      <c r="C287" t="s">
+        <v>116</v>
+      </c>
+      <c r="F287" t="s">
         <v>638</v>
       </c>
-      <c r="C287" t="s">
-        <v>116</v>
-      </c>
-      <c r="F287" t="s">
+      <c r="G287" t="s">
+        <v>116</v>
+      </c>
+      <c r="H287" t="s">
         <v>639</v>
-      </c>
-      <c r="G287" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="288" spans="1:7">
       <c r="A288">
-        <v>33020</v>
+        <v>33011</v>
       </c>
       <c r="B288" t="s">
-        <v>178</v>
+        <v>640</v>
       </c>
       <c r="C288" t="s">
         <v>116</v>
       </c>
       <c r="F288" t="s">
-        <v>178</v>
+        <v>641</v>
       </c>
       <c r="G288" t="s">
         <v>116</v>
@@ -10709,16 +10714,16 @@
     </row>
     <row r="289" spans="1:7">
       <c r="A289">
-        <v>33030</v>
+        <v>33020</v>
       </c>
       <c r="B289" t="s">
-        <v>640</v>
+        <v>180</v>
       </c>
       <c r="C289" t="s">
         <v>116</v>
       </c>
       <c r="F289" t="s">
-        <v>641</v>
+        <v>180</v>
       </c>
       <c r="G289" t="s">
         <v>116</v>
@@ -10726,27 +10731,27 @@
     </row>
     <row r="290" spans="1:7">
       <c r="A290">
+        <v>33030</v>
+      </c>
+      <c r="B290" t="s">
+        <v>642</v>
+      </c>
+      <c r="C290" t="s">
+        <v>116</v>
+      </c>
+      <c r="F290" t="s">
+        <v>643</v>
+      </c>
+      <c r="G290" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291">
         <v>33040</v>
       </c>
-      <c r="B290" t="s">
-        <v>570</v>
-      </c>
-      <c r="C290" t="s">
-        <v>116</v>
-      </c>
-      <c r="F290" t="s">
-        <v>642</v>
-      </c>
-      <c r="G290" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="291" spans="1:8">
-      <c r="A291">
-        <v>34010</v>
-      </c>
       <c r="B291" t="s">
-        <v>643</v>
+        <v>572</v>
       </c>
       <c r="C291" t="s">
         <v>116</v>
@@ -10757,39 +10762,39 @@
       <c r="G291" t="s">
         <v>116</v>
       </c>
-      <c r="H291" t="s">
+    </row>
+    <row r="292" spans="1:8">
+      <c r="A292">
+        <v>34010</v>
+      </c>
+      <c r="B292" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="292" spans="1:7">
-      <c r="A292">
-        <v>34020</v>
-      </c>
-      <c r="B292" t="s">
+      <c r="C292" t="s">
+        <v>116</v>
+      </c>
+      <c r="F292" t="s">
         <v>646</v>
       </c>
-      <c r="C292" t="s">
-        <v>116</v>
-      </c>
-      <c r="F292" t="s">
+      <c r="G292" t="s">
+        <v>116</v>
+      </c>
+      <c r="H292" t="s">
         <v>647</v>
-      </c>
-      <c r="G292" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="293" spans="1:7">
       <c r="A293">
-        <v>34030</v>
+        <v>34020</v>
       </c>
       <c r="B293" t="s">
-        <v>347</v>
+        <v>648</v>
       </c>
       <c r="C293" t="s">
         <v>116</v>
       </c>
       <c r="F293" t="s">
-        <v>348</v>
+        <v>649</v>
       </c>
       <c r="G293" t="s">
         <v>116</v>
@@ -10797,16 +10802,16 @@
     </row>
     <row r="294" spans="1:7">
       <c r="A294">
-        <v>34040</v>
+        <v>34030</v>
       </c>
       <c r="B294" t="s">
-        <v>648</v>
+        <v>349</v>
       </c>
       <c r="C294" t="s">
         <v>116</v>
       </c>
       <c r="F294" t="s">
-        <v>649</v>
+        <v>350</v>
       </c>
       <c r="G294" t="s">
         <v>116</v>
@@ -10814,7 +10819,7 @@
     </row>
     <row r="295" spans="1:7">
       <c r="A295">
-        <v>34050</v>
+        <v>34040</v>
       </c>
       <c r="B295" t="s">
         <v>650</v>
@@ -10829,9 +10834,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="296" customFormat="1" spans="1:7">
+    <row r="296" spans="1:7">
       <c r="A296">
-        <v>34060</v>
+        <v>34050</v>
       </c>
       <c r="B296" t="s">
         <v>652</v>
@@ -10848,7 +10853,7 @@
     </row>
     <row r="297" customFormat="1" spans="1:7">
       <c r="A297">
-        <v>34070</v>
+        <v>34060</v>
       </c>
       <c r="B297" t="s">
         <v>654</v>
@@ -10863,9 +10868,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="298" spans="1:8">
+    <row r="298" customFormat="1" spans="1:7">
       <c r="A298">
-        <v>35010</v>
+        <v>34070</v>
       </c>
       <c r="B298" t="s">
         <v>656</v>
@@ -10879,13 +10884,10 @@
       <c r="G298" t="s">
         <v>116</v>
       </c>
-      <c r="H298" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7">
+    </row>
+    <row r="299" spans="1:8">
       <c r="A299">
-        <v>35020</v>
+        <v>35010</v>
       </c>
       <c r="B299" t="s">
         <v>658</v>
@@ -10899,10 +10901,13 @@
       <c r="G299" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="300" customFormat="1" spans="1:7">
+      <c r="H299" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
       <c r="A300">
-        <v>35021</v>
+        <v>35020</v>
       </c>
       <c r="B300" t="s">
         <v>660</v>
@@ -10919,7 +10924,7 @@
     </row>
     <row r="301" customFormat="1" spans="1:7">
       <c r="A301">
-        <v>35030</v>
+        <v>35021</v>
       </c>
       <c r="B301" t="s">
         <v>662</v>
@@ -10936,7 +10941,7 @@
     </row>
     <row r="302" customFormat="1" spans="1:7">
       <c r="A302">
-        <v>35040</v>
+        <v>35030</v>
       </c>
       <c r="B302" t="s">
         <v>664</v>
@@ -10951,9 +10956,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="303" spans="1:8">
+    <row r="303" customFormat="1" spans="1:7">
       <c r="A303">
-        <v>36010</v>
+        <v>35040</v>
       </c>
       <c r="B303" t="s">
         <v>666</v>
@@ -10967,30 +10972,30 @@
       <c r="G303" t="s">
         <v>116</v>
       </c>
-      <c r="H303" t="s">
+    </row>
+    <row r="304" spans="1:8">
+      <c r="A304">
+        <v>36010</v>
+      </c>
+      <c r="B304" t="s">
         <v>668</v>
       </c>
-    </row>
-    <row r="304" spans="1:7">
-      <c r="A304">
+      <c r="C304" t="s">
+        <v>116</v>
+      </c>
+      <c r="F304" t="s">
+        <v>669</v>
+      </c>
+      <c r="G304" t="s">
+        <v>116</v>
+      </c>
+      <c r="H304" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7">
+      <c r="A305">
         <v>36011</v>
-      </c>
-      <c r="B304" t="s">
-        <v>669</v>
-      </c>
-      <c r="C304" t="s">
-        <v>116</v>
-      </c>
-      <c r="F304" t="s">
-        <v>670</v>
-      </c>
-      <c r="G304" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="305" spans="1:8">
-      <c r="A305">
-        <v>37000</v>
       </c>
       <c r="B305" t="s">
         <v>671</v>
@@ -11004,30 +11009,30 @@
       <c r="G305" t="s">
         <v>116</v>
       </c>
-      <c r="H305" t="s">
+    </row>
+    <row r="306" spans="1:8">
+      <c r="A306">
+        <v>37000</v>
+      </c>
+      <c r="B306" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="306" spans="1:7">
-      <c r="A306">
-        <v>37010</v>
-      </c>
-      <c r="B306" t="s">
+      <c r="C306" t="s">
+        <v>116</v>
+      </c>
+      <c r="F306" t="s">
         <v>674</v>
       </c>
-      <c r="C306" t="s">
-        <v>116</v>
-      </c>
-      <c r="F306" t="s">
+      <c r="G306" t="s">
+        <v>116</v>
+      </c>
+      <c r="H306" t="s">
         <v>675</v>
-      </c>
-      <c r="G306" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="307" spans="1:7">
       <c r="A307">
-        <v>37020</v>
+        <v>37010</v>
       </c>
       <c r="B307" t="s">
         <v>676</v>
@@ -11042,9 +11047,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="308" spans="1:8">
+    <row r="308" spans="1:7">
       <c r="A308">
-        <v>38010</v>
+        <v>37020</v>
       </c>
       <c r="B308" t="s">
         <v>678</v>
@@ -11058,30 +11063,30 @@
       <c r="G308" t="s">
         <v>116</v>
       </c>
-      <c r="H308" t="s">
+    </row>
+    <row r="309" spans="1:8">
+      <c r="A309">
+        <v>38010</v>
+      </c>
+      <c r="B309" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="309" spans="1:7">
-      <c r="A309">
-        <v>38020</v>
-      </c>
-      <c r="B309" t="s">
+      <c r="C309" t="s">
+        <v>116</v>
+      </c>
+      <c r="F309" t="s">
         <v>681</v>
       </c>
-      <c r="C309" t="s">
-        <v>116</v>
-      </c>
-      <c r="F309" t="s">
+      <c r="G309" t="s">
+        <v>116</v>
+      </c>
+      <c r="H309" t="s">
         <v>682</v>
-      </c>
-      <c r="G309" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="310" spans="1:7">
       <c r="A310">
-        <v>38030</v>
+        <v>38020</v>
       </c>
       <c r="B310" t="s">
         <v>683</v>
@@ -11096,9 +11101,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="311" spans="1:8">
+    <row r="311" spans="1:7">
       <c r="A311">
-        <v>39010</v>
+        <v>38030</v>
       </c>
       <c r="B311" t="s">
         <v>685</v>
@@ -11107,38 +11112,38 @@
         <v>116</v>
       </c>
       <c r="F311" t="s">
+        <v>686</v>
+      </c>
+      <c r="G311" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8">
+      <c r="A312">
+        <v>39010</v>
+      </c>
+      <c r="B312" t="s">
+        <v>687</v>
+      </c>
+      <c r="C312" t="s">
+        <v>116</v>
+      </c>
+      <c r="F312" t="s">
         <v>9</v>
       </c>
-      <c r="G311" t="s">
-        <v>116</v>
-      </c>
-      <c r="H311" t="s">
+      <c r="G312" t="s">
+        <v>116</v>
+      </c>
+      <c r="H312" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="312" spans="1:7">
-      <c r="A312">
+    <row r="313" spans="1:7">
+      <c r="A313">
         <v>39020</v>
       </c>
-      <c r="B312" t="s">
+      <c r="B313" t="s">
         <v>58</v>
-      </c>
-      <c r="C312" t="s">
-        <v>116</v>
-      </c>
-      <c r="F312" t="s">
-        <v>686</v>
-      </c>
-      <c r="G312" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="313" customFormat="1" spans="1:7">
-      <c r="A313">
-        <v>39030</v>
-      </c>
-      <c r="B313" t="s">
-        <v>687</v>
       </c>
       <c r="C313" t="s">
         <v>116</v>
@@ -11150,9 +11155,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="314" spans="1:7">
+    <row r="314" customFormat="1" spans="1:7">
       <c r="A314">
-        <v>39040</v>
+        <v>39030</v>
       </c>
       <c r="B314" t="s">
         <v>689</v>
@@ -11167,18 +11172,18 @@
         <v>116</v>
       </c>
     </row>
-    <row r="315" customFormat="1" spans="1:7">
+    <row r="315" spans="1:7">
       <c r="A315">
-        <v>39050</v>
+        <v>39040</v>
       </c>
       <c r="B315" t="s">
-        <v>681</v>
+        <v>691</v>
       </c>
       <c r="C315" t="s">
         <v>116</v>
       </c>
       <c r="F315" t="s">
-        <v>682</v>
+        <v>692</v>
       </c>
       <c r="G315" t="s">
         <v>116</v>
@@ -11186,16 +11191,16 @@
     </row>
     <row r="316" customFormat="1" spans="1:7">
       <c r="A316">
-        <v>39051</v>
+        <v>39050</v>
       </c>
       <c r="B316" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="C316" t="s">
         <v>116</v>
       </c>
       <c r="F316" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="G316" t="s">
         <v>116</v>
@@ -11203,7 +11208,7 @@
     </row>
     <row r="317" customFormat="1" spans="1:7">
       <c r="A317">
-        <v>39060</v>
+        <v>39051</v>
       </c>
       <c r="B317" t="s">
         <v>693</v>
@@ -11220,7 +11225,7 @@
     </row>
     <row r="318" customFormat="1" spans="1:7">
       <c r="A318">
-        <v>39070</v>
+        <v>39060</v>
       </c>
       <c r="B318" t="s">
         <v>695</v>
@@ -11237,7 +11242,7 @@
     </row>
     <row r="319" customFormat="1" spans="1:7">
       <c r="A319">
-        <v>39080</v>
+        <v>39070</v>
       </c>
       <c r="B319" t="s">
         <v>697</v>
@@ -11254,16 +11259,16 @@
     </row>
     <row r="320" customFormat="1" spans="1:7">
       <c r="A320">
-        <v>39090</v>
+        <v>39080</v>
       </c>
       <c r="B320" t="s">
-        <v>643</v>
+        <v>699</v>
       </c>
       <c r="C320" t="s">
         <v>116</v>
       </c>
       <c r="F320" t="s">
-        <v>644</v>
+        <v>700</v>
       </c>
       <c r="G320" t="s">
         <v>116</v>
@@ -11271,24 +11276,24 @@
     </row>
     <row r="321" customFormat="1" spans="1:7">
       <c r="A321">
+        <v>39090</v>
+      </c>
+      <c r="B321" t="s">
+        <v>645</v>
+      </c>
+      <c r="C321" t="s">
+        <v>116</v>
+      </c>
+      <c r="F321" t="s">
+        <v>646</v>
+      </c>
+      <c r="G321" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="322" customFormat="1" spans="1:7">
+      <c r="A322">
         <v>39100</v>
-      </c>
-      <c r="B321" t="s">
-        <v>699</v>
-      </c>
-      <c r="C321" t="s">
-        <v>116</v>
-      </c>
-      <c r="F321" t="s">
-        <v>700</v>
-      </c>
-      <c r="G321" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="322" spans="1:8">
-      <c r="A322">
-        <v>40010</v>
       </c>
       <c r="B322" t="s">
         <v>701</v>
@@ -11297,38 +11302,38 @@
         <v>116</v>
       </c>
       <c r="F322" t="s">
+        <v>179</v>
+      </c>
+      <c r="G322" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8">
+      <c r="A323">
+        <v>40010</v>
+      </c>
+      <c r="B323" t="s">
         <v>702</v>
       </c>
-      <c r="G322" t="s">
-        <v>116</v>
-      </c>
-      <c r="H322" t="s">
+      <c r="C323" t="s">
+        <v>116</v>
+      </c>
+      <c r="F323" t="s">
         <v>703</v>
       </c>
-    </row>
-    <row r="323" spans="1:7">
-      <c r="A323">
+      <c r="G323" t="s">
+        <v>116</v>
+      </c>
+      <c r="H323" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7">
+      <c r="A324">
         <v>40020</v>
       </c>
-      <c r="B323" t="s">
-        <v>626</v>
-      </c>
-      <c r="C323" t="s">
-        <v>116</v>
-      </c>
-      <c r="F323" t="s">
-        <v>704</v>
-      </c>
-      <c r="G323" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="324" spans="1:8">
-      <c r="A324">
-        <v>41010</v>
-      </c>
       <c r="B324" t="s">
-        <v>705</v>
+        <v>628</v>
       </c>
       <c r="C324" t="s">
         <v>116</v>
@@ -11339,59 +11344,59 @@
       <c r="G324" t="s">
         <v>116</v>
       </c>
-      <c r="H324" t="s">
-        <v>706</v>
-      </c>
     </row>
     <row r="325" spans="1:8">
       <c r="A325">
+        <v>41010</v>
+      </c>
+      <c r="B325" t="s">
+        <v>706</v>
+      </c>
+      <c r="C325" t="s">
+        <v>116</v>
+      </c>
+      <c r="F325" t="s">
+        <v>706</v>
+      </c>
+      <c r="G325" t="s">
+        <v>116</v>
+      </c>
+      <c r="H325" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8">
+      <c r="A326">
         <v>42010</v>
       </c>
-      <c r="B325" t="s">
-        <v>707</v>
-      </c>
-      <c r="C325" t="s">
-        <v>116</v>
-      </c>
-      <c r="F325" t="s">
+      <c r="B326" t="s">
         <v>708</v>
       </c>
-      <c r="G325" t="s">
-        <v>116</v>
-      </c>
-      <c r="H325" t="s">
+      <c r="C326" t="s">
+        <v>116</v>
+      </c>
+      <c r="F326" t="s">
         <v>709</v>
       </c>
-    </row>
-    <row r="326" spans="1:7">
-      <c r="A326">
+      <c r="G326" t="s">
+        <v>116</v>
+      </c>
+      <c r="H326" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="327" spans="1:7">
+      <c r="A327">
         <v>42011</v>
       </c>
-      <c r="B326" t="s">
-        <v>710</v>
-      </c>
-      <c r="C326" t="s">
-        <v>116</v>
-      </c>
-      <c r="F326" t="s">
+      <c r="B327" t="s">
         <v>711</v>
       </c>
-      <c r="G326" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="327" customFormat="1" spans="1:7">
-      <c r="A327">
-        <v>42020</v>
-      </c>
-      <c r="B327" t="s">
+      <c r="C327" t="s">
+        <v>116</v>
+      </c>
+      <c r="F327" t="s">
         <v>712</v>
-      </c>
-      <c r="C327" t="s">
-        <v>116</v>
-      </c>
-      <c r="F327" t="s">
-        <v>713</v>
       </c>
       <c r="G327" t="s">
         <v>116</v>
@@ -11399,16 +11404,16 @@
     </row>
     <row r="328" customFormat="1" spans="1:7">
       <c r="A328">
-        <v>42030</v>
+        <v>42020</v>
       </c>
       <c r="B328" t="s">
+        <v>713</v>
+      </c>
+      <c r="C328" t="s">
+        <v>116</v>
+      </c>
+      <c r="F328" t="s">
         <v>714</v>
-      </c>
-      <c r="C328" t="s">
-        <v>116</v>
-      </c>
-      <c r="F328" t="s">
-        <v>715</v>
       </c>
       <c r="G328" t="s">
         <v>116</v>
@@ -11416,61 +11421,61 @@
     </row>
     <row r="329" customFormat="1" spans="1:7">
       <c r="A329">
+        <v>42030</v>
+      </c>
+      <c r="B329" t="s">
+        <v>715</v>
+      </c>
+      <c r="C329" t="s">
+        <v>116</v>
+      </c>
+      <c r="F329" t="s">
+        <v>716</v>
+      </c>
+      <c r="G329" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="330" customFormat="1" spans="1:7">
+      <c r="A330">
         <v>42040</v>
       </c>
-      <c r="B329" t="s">
-        <v>716</v>
-      </c>
-      <c r="C329" t="s">
-        <v>116</v>
-      </c>
-      <c r="F329" t="s">
+      <c r="B330" t="s">
         <v>717</v>
       </c>
-      <c r="G329" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="330" spans="1:8">
-      <c r="A330">
+      <c r="C330" t="s">
+        <v>116</v>
+      </c>
+      <c r="F330" t="s">
+        <v>718</v>
+      </c>
+      <c r="G330" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8">
+      <c r="A331">
         <v>43010</v>
       </c>
-      <c r="B330" t="s">
-        <v>718</v>
-      </c>
-      <c r="C330" t="s">
-        <v>116</v>
-      </c>
-      <c r="F330" t="s">
+      <c r="B331" t="s">
         <v>719</v>
       </c>
-      <c r="G330" t="s">
-        <v>116</v>
-      </c>
-      <c r="H330" t="s">
+      <c r="C331" t="s">
+        <v>116</v>
+      </c>
+      <c r="F331" t="s">
+        <v>720</v>
+      </c>
+      <c r="G331" t="s">
+        <v>116</v>
+      </c>
+      <c r="H331" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="331" spans="1:7">
-      <c r="A331">
+    <row r="332" spans="1:7">
+      <c r="A332">
         <v>43020</v>
-      </c>
-      <c r="B331" t="s">
-        <v>720</v>
-      </c>
-      <c r="C331" t="s">
-        <v>116</v>
-      </c>
-      <c r="F331" t="s">
-        <v>496</v>
-      </c>
-      <c r="G331" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="332" customFormat="1" spans="1:8">
-      <c r="A332">
-        <v>44010</v>
       </c>
       <c r="B332" t="s">
         <v>721</v>
@@ -11479,66 +11484,83 @@
         <v>116</v>
       </c>
       <c r="F332" t="s">
+        <v>498</v>
+      </c>
+      <c r="G332" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="333" customFormat="1" spans="1:8">
+      <c r="A333">
+        <v>44010</v>
+      </c>
+      <c r="B333" t="s">
         <v>722</v>
       </c>
-      <c r="G332" t="s">
-        <v>116</v>
-      </c>
-      <c r="H332" t="s">
+      <c r="C333" t="s">
+        <v>116</v>
+      </c>
+      <c r="F333" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="333" spans="1:8">
-      <c r="A333">
+      <c r="G333" t="s">
+        <v>116</v>
+      </c>
+      <c r="H333" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8">
+      <c r="A334">
         <v>45010</v>
       </c>
-      <c r="B333" t="s">
-        <v>724</v>
-      </c>
-      <c r="C333" t="s">
-        <v>116</v>
-      </c>
-      <c r="F333" t="s">
+      <c r="B334" t="s">
         <v>725</v>
       </c>
-      <c r="G333" t="s">
-        <v>116</v>
-      </c>
-      <c r="H333" t="s">
+      <c r="C334" t="s">
+        <v>116</v>
+      </c>
+      <c r="F334" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="334" spans="1:7">
-      <c r="A334">
-        <v>45020</v>
-      </c>
-      <c r="B334" t="s">
+      <c r="G334" t="s">
+        <v>116</v>
+      </c>
+      <c r="H334" t="s">
         <v>727</v>
-      </c>
-      <c r="C334" t="s">
-        <v>116</v>
-      </c>
-      <c r="F334" t="s">
-        <v>728</v>
-      </c>
-      <c r="G334" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="335" spans="1:7">
       <c r="A335">
+        <v>45020</v>
+      </c>
+      <c r="B335" t="s">
+        <v>728</v>
+      </c>
+      <c r="C335" t="s">
+        <v>116</v>
+      </c>
+      <c r="F335" t="s">
+        <v>729</v>
+      </c>
+      <c r="G335" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7">
+      <c r="A336">
         <v>45030</v>
       </c>
-      <c r="B335" t="s">
-        <v>729</v>
-      </c>
-      <c r="C335" t="s">
-        <v>116</v>
-      </c>
-      <c r="F335" t="s">
+      <c r="B336" t="s">
         <v>730</v>
       </c>
-      <c r="G335" t="s">
+      <c r="C336" t="s">
+        <v>116</v>
+      </c>
+      <c r="F336" t="s">
+        <v>731</v>
+      </c>
+      <c r="G336" t="s">
         <v>116</v>
       </c>
     </row>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1659" uniqueCount="732">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="736">
   <si>
     <t>Id</t>
   </si>
@@ -2009,10 +2009,10 @@
     <t>Equipment Candidate Selection</t>
   </si>
   <si>
-    <t>を転送しますか？\n転送した仲間は次のChapterまで戻ってきません！</t>
-  </si>
-  <si>
-    <t>Do you want to transfer? \n Transferred comrades will not return until the next chapter!</t>
+    <t>を転送しますか？\n転送した仲間は次のPeriodまで戻ってきません！</t>
+  </si>
+  <si>
+    <t>Do you want to transfer? \n Transferred comrades will not return until the next period!</t>
   </si>
   <si>
     <t>主人公は転送できません！</t>
@@ -2033,10 +2033,22 @@
     <t>Gained Exp</t>
   </si>
   <si>
-    <t>成果報酬：</t>
-  </si>
-  <si>
-    <t>Achievement Reward:</t>
+    <t>成果報酬</t>
+  </si>
+  <si>
+    <t>Achievement Reward</t>
+  </si>
+  <si>
+    <t>評価値 +{0}</t>
+  </si>
+  <si>
+    <t>Evaluate +{0}</t>
+  </si>
+  <si>
+    <t>獲得Exp +{0}</t>
+  </si>
+  <si>
+    <t>Gained Exp +{0}</t>
   </si>
   <si>
     <t>課題を達成！</t>
@@ -2236,9 +2248,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
@@ -2264,10 +2276,123 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2286,124 +2411,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2422,7 +2434,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2434,37 +2494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2476,13 +2506,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2500,7 +2536,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2518,85 +2596,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2607,6 +2619,17 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2621,6 +2644,33 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2655,35 +2705,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -2698,15 +2719,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2715,145 +2727,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5780,7 +5792,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I336"/>
+  <dimension ref="A1:I338"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.54545454545455" customWidth="1"/>
@@ -6511,8 +6523,6 @@
       <c r="C42" t="s">
         <v>116</v>
       </c>
-      <c r="D42"/>
-      <c r="E42"/>
       <c r="F42" t="s">
         <v>179</v>
       </c>
@@ -10973,9 +10983,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="304" spans="1:8">
+    <row r="304" customFormat="1" spans="1:7">
       <c r="A304">
-        <v>36010</v>
+        <v>35050</v>
       </c>
       <c r="B304" t="s">
         <v>668</v>
@@ -10989,22 +10999,19 @@
       <c r="G304" t="s">
         <v>116</v>
       </c>
-      <c r="H304" t="s">
+    </row>
+    <row r="305" customFormat="1" spans="1:7">
+      <c r="A305">
+        <v>35060</v>
+      </c>
+      <c r="B305" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="305" spans="1:7">
-      <c r="A305">
-        <v>36011</v>
-      </c>
-      <c r="B305" t="s">
+      <c r="C305" t="s">
+        <v>116</v>
+      </c>
+      <c r="F305" t="s">
         <v>671</v>
-      </c>
-      <c r="C305" t="s">
-        <v>116</v>
-      </c>
-      <c r="F305" t="s">
-        <v>672</v>
       </c>
       <c r="G305" t="s">
         <v>116</v>
@@ -11012,61 +11019,64 @@
     </row>
     <row r="306" spans="1:8">
       <c r="A306">
-        <v>37000</v>
+        <v>36010</v>
       </c>
       <c r="B306" t="s">
+        <v>672</v>
+      </c>
+      <c r="C306" t="s">
+        <v>116</v>
+      </c>
+      <c r="F306" t="s">
         <v>673</v>
       </c>
-      <c r="C306" t="s">
-        <v>116</v>
-      </c>
-      <c r="F306" t="s">
+      <c r="G306" t="s">
+        <v>116</v>
+      </c>
+      <c r="H306" t="s">
         <v>674</v>
-      </c>
-      <c r="G306" t="s">
-        <v>116</v>
-      </c>
-      <c r="H306" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="307" spans="1:7">
       <c r="A307">
+        <v>36011</v>
+      </c>
+      <c r="B307" t="s">
+        <v>675</v>
+      </c>
+      <c r="C307" t="s">
+        <v>116</v>
+      </c>
+      <c r="F307" t="s">
+        <v>676</v>
+      </c>
+      <c r="G307" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8">
+      <c r="A308">
+        <v>37000</v>
+      </c>
+      <c r="B308" t="s">
+        <v>677</v>
+      </c>
+      <c r="C308" t="s">
+        <v>116</v>
+      </c>
+      <c r="F308" t="s">
+        <v>678</v>
+      </c>
+      <c r="G308" t="s">
+        <v>116</v>
+      </c>
+      <c r="H308" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7">
+      <c r="A309">
         <v>37010</v>
-      </c>
-      <c r="B307" t="s">
-        <v>676</v>
-      </c>
-      <c r="C307" t="s">
-        <v>116</v>
-      </c>
-      <c r="F307" t="s">
-        <v>677</v>
-      </c>
-      <c r="G307" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7">
-      <c r="A308">
-        <v>37020</v>
-      </c>
-      <c r="B308" t="s">
-        <v>678</v>
-      </c>
-      <c r="C308" t="s">
-        <v>116</v>
-      </c>
-      <c r="F308" t="s">
-        <v>679</v>
-      </c>
-      <c r="G308" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="309" spans="1:8">
-      <c r="A309">
-        <v>38010</v>
       </c>
       <c r="B309" t="s">
         <v>680</v>
@@ -11080,47 +11090,47 @@
       <c r="G309" t="s">
         <v>116</v>
       </c>
-      <c r="H309" t="s">
-        <v>682</v>
-      </c>
     </row>
     <row r="310" spans="1:7">
       <c r="A310">
+        <v>37020</v>
+      </c>
+      <c r="B310" t="s">
+        <v>682</v>
+      </c>
+      <c r="C310" t="s">
+        <v>116</v>
+      </c>
+      <c r="F310" t="s">
+        <v>683</v>
+      </c>
+      <c r="G310" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8">
+      <c r="A311">
+        <v>38010</v>
+      </c>
+      <c r="B311" t="s">
+        <v>684</v>
+      </c>
+      <c r="C311" t="s">
+        <v>116</v>
+      </c>
+      <c r="F311" t="s">
+        <v>685</v>
+      </c>
+      <c r="G311" t="s">
+        <v>116</v>
+      </c>
+      <c r="H311" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7">
+      <c r="A312">
         <v>38020</v>
-      </c>
-      <c r="B310" t="s">
-        <v>683</v>
-      </c>
-      <c r="C310" t="s">
-        <v>116</v>
-      </c>
-      <c r="F310" t="s">
-        <v>684</v>
-      </c>
-      <c r="G310" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="311" spans="1:7">
-      <c r="A311">
-        <v>38030</v>
-      </c>
-      <c r="B311" t="s">
-        <v>685</v>
-      </c>
-      <c r="C311" t="s">
-        <v>116</v>
-      </c>
-      <c r="F311" t="s">
-        <v>686</v>
-      </c>
-      <c r="G311" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="312" spans="1:8">
-      <c r="A312">
-        <v>39010</v>
       </c>
       <c r="B312" t="s">
         <v>687</v>
@@ -11129,55 +11139,55 @@
         <v>116</v>
       </c>
       <c r="F312" t="s">
-        <v>9</v>
+        <v>688</v>
       </c>
       <c r="G312" t="s">
         <v>116</v>
-      </c>
-      <c r="H312" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="313" spans="1:7">
       <c r="A313">
-        <v>39020</v>
+        <v>38030</v>
       </c>
       <c r="B313" t="s">
-        <v>58</v>
+        <v>689</v>
       </c>
       <c r="C313" t="s">
         <v>116</v>
       </c>
       <c r="F313" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G313" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="314" customFormat="1" spans="1:7">
+    <row r="314" spans="1:8">
       <c r="A314">
-        <v>39030</v>
+        <v>39010</v>
       </c>
       <c r="B314" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C314" t="s">
         <v>116</v>
       </c>
       <c r="F314" t="s">
-        <v>690</v>
+        <v>9</v>
       </c>
       <c r="G314" t="s">
         <v>116</v>
+      </c>
+      <c r="H314" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="315" spans="1:7">
       <c r="A315">
-        <v>39040</v>
+        <v>39020</v>
       </c>
       <c r="B315" t="s">
-        <v>691</v>
+        <v>58</v>
       </c>
       <c r="C315" t="s">
         <v>116</v>
@@ -11191,33 +11201,33 @@
     </row>
     <row r="316" customFormat="1" spans="1:7">
       <c r="A316">
-        <v>39050</v>
+        <v>39030</v>
       </c>
       <c r="B316" t="s">
-        <v>683</v>
+        <v>693</v>
       </c>
       <c r="C316" t="s">
         <v>116</v>
       </c>
       <c r="F316" t="s">
-        <v>684</v>
+        <v>694</v>
       </c>
       <c r="G316" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="317" customFormat="1" spans="1:7">
+    <row r="317" spans="1:7">
       <c r="A317">
-        <v>39051</v>
+        <v>39040</v>
       </c>
       <c r="B317" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C317" t="s">
         <v>116</v>
       </c>
       <c r="F317" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="G317" t="s">
         <v>116</v>
@@ -11225,16 +11235,16 @@
     </row>
     <row r="318" customFormat="1" spans="1:7">
       <c r="A318">
-        <v>39060</v>
+        <v>39050</v>
       </c>
       <c r="B318" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="C318" t="s">
         <v>116</v>
       </c>
       <c r="F318" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="G318" t="s">
         <v>116</v>
@@ -11242,7 +11252,7 @@
     </row>
     <row r="319" customFormat="1" spans="1:7">
       <c r="A319">
-        <v>39070</v>
+        <v>39051</v>
       </c>
       <c r="B319" t="s">
         <v>697</v>
@@ -11259,7 +11269,7 @@
     </row>
     <row r="320" customFormat="1" spans="1:7">
       <c r="A320">
-        <v>39080</v>
+        <v>39060</v>
       </c>
       <c r="B320" t="s">
         <v>699</v>
@@ -11276,16 +11286,16 @@
     </row>
     <row r="321" customFormat="1" spans="1:7">
       <c r="A321">
-        <v>39090</v>
+        <v>39070</v>
       </c>
       <c r="B321" t="s">
-        <v>645</v>
+        <v>701</v>
       </c>
       <c r="C321" t="s">
         <v>116</v>
       </c>
       <c r="F321" t="s">
-        <v>646</v>
+        <v>702</v>
       </c>
       <c r="G321" t="s">
         <v>116</v>
@@ -11293,53 +11303,50 @@
     </row>
     <row r="322" customFormat="1" spans="1:7">
       <c r="A322">
+        <v>39080</v>
+      </c>
+      <c r="B322" t="s">
+        <v>703</v>
+      </c>
+      <c r="C322" t="s">
+        <v>116</v>
+      </c>
+      <c r="F322" t="s">
+        <v>704</v>
+      </c>
+      <c r="G322" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="323" customFormat="1" spans="1:7">
+      <c r="A323">
+        <v>39090</v>
+      </c>
+      <c r="B323" t="s">
+        <v>645</v>
+      </c>
+      <c r="C323" t="s">
+        <v>116</v>
+      </c>
+      <c r="F323" t="s">
+        <v>646</v>
+      </c>
+      <c r="G323" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="324" customFormat="1" spans="1:7">
+      <c r="A324">
         <v>39100</v>
       </c>
-      <c r="B322" t="s">
-        <v>701</v>
-      </c>
-      <c r="C322" t="s">
-        <v>116</v>
-      </c>
-      <c r="F322" t="s">
+      <c r="B324" t="s">
+        <v>705</v>
+      </c>
+      <c r="C324" t="s">
+        <v>116</v>
+      </c>
+      <c r="F324" t="s">
         <v>179</v>
-      </c>
-      <c r="G322" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="323" spans="1:8">
-      <c r="A323">
-        <v>40010</v>
-      </c>
-      <c r="B323" t="s">
-        <v>702</v>
-      </c>
-      <c r="C323" t="s">
-        <v>116</v>
-      </c>
-      <c r="F323" t="s">
-        <v>703</v>
-      </c>
-      <c r="G323" t="s">
-        <v>116</v>
-      </c>
-      <c r="H323" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="324" spans="1:7">
-      <c r="A324">
-        <v>40020</v>
-      </c>
-      <c r="B324" t="s">
-        <v>628</v>
-      </c>
-      <c r="C324" t="s">
-        <v>116</v>
-      </c>
-      <c r="F324" t="s">
-        <v>705</v>
       </c>
       <c r="G324" t="s">
         <v>116</v>
@@ -11347,7 +11354,7 @@
     </row>
     <row r="325" spans="1:8">
       <c r="A325">
-        <v>41010</v>
+        <v>40010</v>
       </c>
       <c r="B325" t="s">
         <v>706</v>
@@ -11356,21 +11363,21 @@
         <v>116</v>
       </c>
       <c r="F325" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="G325" t="s">
         <v>116</v>
       </c>
       <c r="H325" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="326" spans="1:8">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="326" spans="1:7">
       <c r="A326">
-        <v>42010</v>
+        <v>40020</v>
       </c>
       <c r="B326" t="s">
-        <v>708</v>
+        <v>628</v>
       </c>
       <c r="C326" t="s">
         <v>116</v>
@@ -11381,47 +11388,50 @@
       <c r="G326" t="s">
         <v>116</v>
       </c>
-      <c r="H326" t="s">
+    </row>
+    <row r="327" spans="1:8">
+      <c r="A327">
+        <v>41010</v>
+      </c>
+      <c r="B327" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="327" spans="1:7">
-      <c r="A327">
+      <c r="C327" t="s">
+        <v>116</v>
+      </c>
+      <c r="F327" t="s">
+        <v>710</v>
+      </c>
+      <c r="G327" t="s">
+        <v>116</v>
+      </c>
+      <c r="H327" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8">
+      <c r="A328">
+        <v>42010</v>
+      </c>
+      <c r="B328" t="s">
+        <v>712</v>
+      </c>
+      <c r="C328" t="s">
+        <v>116</v>
+      </c>
+      <c r="F328" t="s">
+        <v>713</v>
+      </c>
+      <c r="G328" t="s">
+        <v>116</v>
+      </c>
+      <c r="H328" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="329" spans="1:7">
+      <c r="A329">
         <v>42011</v>
-      </c>
-      <c r="B327" t="s">
-        <v>711</v>
-      </c>
-      <c r="C327" t="s">
-        <v>116</v>
-      </c>
-      <c r="F327" t="s">
-        <v>712</v>
-      </c>
-      <c r="G327" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="328" customFormat="1" spans="1:7">
-      <c r="A328">
-        <v>42020</v>
-      </c>
-      <c r="B328" t="s">
-        <v>713</v>
-      </c>
-      <c r="C328" t="s">
-        <v>116</v>
-      </c>
-      <c r="F328" t="s">
-        <v>714</v>
-      </c>
-      <c r="G328" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="329" customFormat="1" spans="1:7">
-      <c r="A329">
-        <v>42030</v>
       </c>
       <c r="B329" t="s">
         <v>715</v>
@@ -11438,7 +11448,7 @@
     </row>
     <row r="330" customFormat="1" spans="1:7">
       <c r="A330">
-        <v>42040</v>
+        <v>42020</v>
       </c>
       <c r="B330" t="s">
         <v>717</v>
@@ -11453,9 +11463,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="331" spans="1:8">
+    <row r="331" customFormat="1" spans="1:7">
       <c r="A331">
-        <v>43010</v>
+        <v>42030</v>
       </c>
       <c r="B331" t="s">
         <v>719</v>
@@ -11469,13 +11479,10 @@
       <c r="G331" t="s">
         <v>116</v>
       </c>
-      <c r="H331" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="332" spans="1:7">
+    </row>
+    <row r="332" customFormat="1" spans="1:7">
       <c r="A332">
-        <v>43020</v>
+        <v>42040</v>
       </c>
       <c r="B332" t="s">
         <v>721</v>
@@ -11484,35 +11491,35 @@
         <v>116</v>
       </c>
       <c r="F332" t="s">
-        <v>498</v>
+        <v>722</v>
       </c>
       <c r="G332" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="333" customFormat="1" spans="1:8">
+    <row r="333" spans="1:8">
       <c r="A333">
-        <v>44010</v>
+        <v>43010</v>
       </c>
       <c r="B333" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C333" t="s">
         <v>116</v>
       </c>
       <c r="F333" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G333" t="s">
         <v>116</v>
       </c>
       <c r="H333" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="334" spans="1:8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="334" spans="1:7">
       <c r="A334">
-        <v>45010</v>
+        <v>43020</v>
       </c>
       <c r="B334" t="s">
         <v>725</v>
@@ -11521,46 +11528,83 @@
         <v>116</v>
       </c>
       <c r="F334" t="s">
+        <v>498</v>
+      </c>
+      <c r="G334" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="335" customFormat="1" spans="1:8">
+      <c r="A335">
+        <v>44010</v>
+      </c>
+      <c r="B335" t="s">
         <v>726</v>
       </c>
-      <c r="G334" t="s">
-        <v>116</v>
-      </c>
-      <c r="H334" t="s">
+      <c r="C335" t="s">
+        <v>116</v>
+      </c>
+      <c r="F335" t="s">
         <v>727</v>
       </c>
-    </row>
-    <row r="335" spans="1:7">
-      <c r="A335">
+      <c r="G335" t="s">
+        <v>116</v>
+      </c>
+      <c r="H335" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8">
+      <c r="A336">
+        <v>45010</v>
+      </c>
+      <c r="B336" t="s">
+        <v>729</v>
+      </c>
+      <c r="C336" t="s">
+        <v>116</v>
+      </c>
+      <c r="F336" t="s">
+        <v>730</v>
+      </c>
+      <c r="G336" t="s">
+        <v>116</v>
+      </c>
+      <c r="H336" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="337" spans="1:7">
+      <c r="A337">
         <v>45020</v>
       </c>
-      <c r="B335" t="s">
-        <v>728</v>
-      </c>
-      <c r="C335" t="s">
-        <v>116</v>
-      </c>
-      <c r="F335" t="s">
-        <v>729</v>
-      </c>
-      <c r="G335" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="336" spans="1:7">
-      <c r="A336">
+      <c r="B337" t="s">
+        <v>732</v>
+      </c>
+      <c r="C337" t="s">
+        <v>116</v>
+      </c>
+      <c r="F337" t="s">
+        <v>733</v>
+      </c>
+      <c r="G337" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7">
+      <c r="A338">
         <v>45030</v>
       </c>
-      <c r="B336" t="s">
-        <v>730</v>
-      </c>
-      <c r="C336" t="s">
-        <v>116</v>
-      </c>
-      <c r="F336" t="s">
-        <v>731</v>
-      </c>
-      <c r="G336" t="s">
+      <c r="B338" t="s">
+        <v>734</v>
+      </c>
+      <c r="C338" t="s">
+        <v>116</v>
+      </c>
+      <c r="F338" t="s">
+        <v>735</v>
+      </c>
+      <c r="G338" t="s">
         <v>116</v>
       </c>
     </row>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1667" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="746">
   <si>
     <t>Id</t>
   </si>
@@ -2241,6 +2241,36 @@
   </si>
   <si>
     <t>Exchangeable Equipment</t>
+  </si>
+  <si>
+    <t>人物特性</t>
+  </si>
+  <si>
+    <t>Traits</t>
+  </si>
+  <si>
+    <t>ランク</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>修正値</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>総計</t>
+  </si>
+  <si>
+    <t>All Rating</t>
+  </si>
+  <si>
+    <t>人物特性補正</t>
+  </si>
+  <si>
+    <t>Traits Rating</t>
   </si>
 </sst>
 </file>
@@ -2249,8 +2279,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
@@ -2275,17 +2305,16 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2300,15 +2329,22 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2322,15 +2358,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2343,16 +2381,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2360,14 +2405,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2382,7 +2428,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2390,32 +2443,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2428,84 +2458,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2513,6 +2465,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2530,7 +2488,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2542,13 +2578,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2566,49 +2626,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2633,6 +2663,39 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -2644,24 +2707,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2704,21 +2749,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2727,145 +2757,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5792,7 +5822,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I338"/>
+  <dimension ref="A1:I343"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6.54545454545455" customWidth="1"/>
@@ -11608,6 +11638,96 @@
         <v>116</v>
       </c>
     </row>
+    <row r="339" spans="1:8">
+      <c r="A339">
+        <v>46010</v>
+      </c>
+      <c r="B339" t="s">
+        <v>736</v>
+      </c>
+      <c r="C339" t="s">
+        <v>116</v>
+      </c>
+      <c r="F339" t="s">
+        <v>737</v>
+      </c>
+      <c r="G339" t="s">
+        <v>116</v>
+      </c>
+      <c r="H339" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="340" spans="1:7">
+      <c r="A340">
+        <v>46020</v>
+      </c>
+      <c r="B340" t="s">
+        <v>738</v>
+      </c>
+      <c r="C340" t="s">
+        <v>116</v>
+      </c>
+      <c r="F340" t="s">
+        <v>739</v>
+      </c>
+      <c r="G340" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7">
+      <c r="A341">
+        <v>46030</v>
+      </c>
+      <c r="B341" t="s">
+        <v>740</v>
+      </c>
+      <c r="C341" t="s">
+        <v>116</v>
+      </c>
+      <c r="F341" t="s">
+        <v>741</v>
+      </c>
+      <c r="G341" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="342" customFormat="1" spans="1:7">
+      <c r="A342">
+        <v>46040</v>
+      </c>
+      <c r="B342" t="s">
+        <v>742</v>
+      </c>
+      <c r="C342" t="s">
+        <v>116</v>
+      </c>
+      <c r="D342"/>
+      <c r="E342"/>
+      <c r="F342" t="s">
+        <v>743</v>
+      </c>
+      <c r="G342" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="343" customFormat="1" spans="1:7">
+      <c r="A343">
+        <v>46050</v>
+      </c>
+      <c r="B343" t="s">
+        <v>744</v>
+      </c>
+      <c r="C343" t="s">
+        <v>116</v>
+      </c>
+      <c r="F343" t="s">
+        <v>745</v>
+      </c>
+      <c r="G343" t="s">
+        <v>116</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="766" firstSheet="1" activeTab="6"/>
+    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="766" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="TacticsComand" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="747">
   <si>
     <t>Id</t>
   </si>
@@ -302,6 +302,9 @@
   </si>
   <si>
     <t>StartStageId</t>
+  </si>
+  <si>
+    <t>ChapterCount</t>
   </si>
   <si>
     <t>PeriodTurns</t>
@@ -2278,9 +2281,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
@@ -2306,31 +2309,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2344,7 +2330,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2358,62 +2351,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2434,8 +2374,49 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2448,6 +2429,28 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -2455,18 +2458,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2482,7 +2473,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2500,7 +2497,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2512,31 +2599,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2560,6 +2629,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2567,78 +2642,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2652,13 +2655,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2687,54 +2727,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -2749,6 +2741,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2757,145 +2760,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5655,7 +5658,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="20.5454545454545" customWidth="1"/>
@@ -5704,15 +5707,15 @@
         <v>94</v>
       </c>
       <c r="B5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6">
         <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -5720,7 +5723,7 @@
         <v>96</v>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -5728,7 +5731,7 @@
         <v>97</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -5736,7 +5739,7 @@
         <v>98</v>
       </c>
       <c r="B9">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -5744,73 +5747,81 @@
         <v>99</v>
       </c>
       <c r="B10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>100</v>
       </c>
       <c r="B11">
-        <v>50</v>
-      </c>
-      <c r="C11" t="s">
-        <v>101</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
         <v>102</v>
-      </c>
-      <c r="B12">
-        <v>20</v>
-      </c>
-      <c r="C12" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
+        <v>103</v>
+      </c>
+      <c r="B13">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
         <v>104</v>
-      </c>
-      <c r="B13">
-        <v>10</v>
-      </c>
-      <c r="C13" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B14">
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
         <v>108</v>
-      </c>
-      <c r="B15">
-        <v>20</v>
-      </c>
-      <c r="C15" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
         <v>110</v>
       </c>
-      <c r="B16">
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>111</v>
+      </c>
+      <c r="B17">
         <v>5</v>
       </c>
-      <c r="C16" t="s">
-        <v>111</v>
+      <c r="C17" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -5839,16 +5850,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -5856,16 +5867,16 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -5873,16 +5884,16 @@
         <v>400</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -5890,16 +5901,16 @@
         <v>401</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -5907,16 +5918,16 @@
         <v>402</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" customFormat="1" spans="1:7">
@@ -5924,16 +5935,16 @@
         <v>403</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:7">
@@ -5941,16 +5952,16 @@
         <v>404</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:7">
@@ -5958,16 +5969,16 @@
         <v>405</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -5975,19 +5986,19 @@
         <v>600</v>
       </c>
       <c r="B9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5995,16 +6006,16 @@
         <v>601</v>
       </c>
       <c r="B10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -6012,16 +6023,16 @@
         <v>602</v>
       </c>
       <c r="B11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -6029,16 +6040,16 @@
         <v>603</v>
       </c>
       <c r="B12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -6046,16 +6057,16 @@
         <v>606</v>
       </c>
       <c r="B13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -6063,16 +6074,16 @@
         <v>611</v>
       </c>
       <c r="B14" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -6080,16 +6091,16 @@
         <v>620</v>
       </c>
       <c r="B15" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -6097,16 +6108,16 @@
         <v>621</v>
       </c>
       <c r="B16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -6114,16 +6125,16 @@
         <v>622</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -6131,16 +6142,16 @@
         <v>623</v>
       </c>
       <c r="B18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -6148,16 +6159,16 @@
         <v>624</v>
       </c>
       <c r="B19" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -6165,16 +6176,16 @@
         <v>625</v>
       </c>
       <c r="B20" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F20" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G20" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -6182,16 +6193,16 @@
         <v>651</v>
       </c>
       <c r="B21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -6199,16 +6210,16 @@
         <v>652</v>
       </c>
       <c r="B22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -6216,16 +6227,16 @@
         <v>1000</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G23" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -6233,19 +6244,19 @@
         <v>2000</v>
       </c>
       <c r="B24" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F24" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G24" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -6253,16 +6264,16 @@
         <v>2001</v>
       </c>
       <c r="B25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -6270,16 +6281,16 @@
         <v>2002</v>
       </c>
       <c r="B26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G26" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -6287,16 +6298,16 @@
         <v>2003</v>
       </c>
       <c r="B27" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F27" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G27" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -6304,16 +6315,16 @@
         <v>2004</v>
       </c>
       <c r="B28" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C28" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F28" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G28" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -6321,16 +6332,16 @@
         <v>2005</v>
       </c>
       <c r="B29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -6338,16 +6349,16 @@
         <v>2006</v>
       </c>
       <c r="B30" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F30" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G30" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -6355,16 +6366,16 @@
         <v>2007</v>
       </c>
       <c r="B31" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F31" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G31" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -6372,19 +6383,19 @@
         <v>2100</v>
       </c>
       <c r="B32" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F32" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H32" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -6392,16 +6403,16 @@
         <v>2101</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -6409,16 +6420,16 @@
         <v>2102</v>
       </c>
       <c r="B34" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F34" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G34" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -6426,16 +6437,16 @@
         <v>2103</v>
       </c>
       <c r="B35" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F35" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -6443,16 +6454,16 @@
         <v>2104</v>
       </c>
       <c r="B36" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C36" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F36" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G36" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -6460,16 +6471,16 @@
         <v>2105</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C37" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G37" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -6477,16 +6488,16 @@
         <v>2106</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C38" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G38" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -6494,19 +6505,19 @@
         <v>2200</v>
       </c>
       <c r="B39" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C39" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F39" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G39" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H39" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -6514,16 +6525,16 @@
         <v>2210</v>
       </c>
       <c r="B40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C40" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G40" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -6531,16 +6542,16 @@
         <v>2220</v>
       </c>
       <c r="B41" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F41" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42" customFormat="1" spans="1:7">
@@ -6548,16 +6559,16 @@
         <v>2221</v>
       </c>
       <c r="B42" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C42" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F42" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G42" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -6565,16 +6576,16 @@
         <v>2300</v>
       </c>
       <c r="B43" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C43" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F43" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G43" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -6582,16 +6593,16 @@
         <v>2310</v>
       </c>
       <c r="B44" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C44" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F44" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G44" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -6599,16 +6610,16 @@
         <v>2320</v>
       </c>
       <c r="B45" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F45" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -6616,16 +6627,16 @@
         <v>2330</v>
       </c>
       <c r="B46" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F46" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G46" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -6633,16 +6644,16 @@
         <v>2340</v>
       </c>
       <c r="B47" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C47" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F47" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G47" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -6650,16 +6661,16 @@
         <v>2400</v>
       </c>
       <c r="B48" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C48" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F48" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G48" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -6667,16 +6678,16 @@
         <v>2410</v>
       </c>
       <c r="B49" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C49" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F49" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G49" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -6684,16 +6695,16 @@
         <v>2420</v>
       </c>
       <c r="B50" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C50" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F50" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G50" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -6701,16 +6712,16 @@
         <v>2430</v>
       </c>
       <c r="B51" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C51" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F51" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G51" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -6718,16 +6729,16 @@
         <v>2440</v>
       </c>
       <c r="B52" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C52" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F52" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G52" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -6735,16 +6746,16 @@
         <v>2500</v>
       </c>
       <c r="B53" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C53" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F53" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G53" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" customFormat="1" spans="1:7">
@@ -6752,16 +6763,16 @@
         <v>2510</v>
       </c>
       <c r="B54" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C54" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F54" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G54" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" customFormat="1" spans="1:7">
@@ -6769,16 +6780,16 @@
         <v>2520</v>
       </c>
       <c r="B55" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C55" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F55" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G55" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" customFormat="1" spans="1:7">
@@ -6786,16 +6797,16 @@
         <v>2530</v>
       </c>
       <c r="B56" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C56" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F56" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G56" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -6803,16 +6814,16 @@
         <v>2610</v>
       </c>
       <c r="B57" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C57" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F57" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G57" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -6820,19 +6831,19 @@
         <v>3010</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C58" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G58" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H58" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -6840,16 +6851,16 @@
         <v>3020</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C59" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G59" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="60" customFormat="1" spans="1:7">
@@ -6857,16 +6868,16 @@
         <v>3030</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G60" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" customFormat="1" spans="1:7">
@@ -6874,16 +6885,16 @@
         <v>3031</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C61" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G61" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -6891,16 +6902,16 @@
         <v>3040</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C62" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G62" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -6911,13 +6922,13 @@
         <v>38</v>
       </c>
       <c r="C63" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G63" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -6925,16 +6936,16 @@
         <v>3051</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C64" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G64" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -6942,16 +6953,16 @@
         <v>3052</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C65" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G65" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -6959,16 +6970,16 @@
         <v>3100</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C66" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G66" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -6976,16 +6987,16 @@
         <v>3110</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C67" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G67" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -6993,16 +7004,16 @@
         <v>3120</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C68" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G68" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -7010,16 +7021,16 @@
         <v>3130</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C69" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G69" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="70" customFormat="1" spans="1:7">
@@ -7027,16 +7038,16 @@
         <v>3140</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C70" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G70" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="71" customFormat="1" spans="1:7">
@@ -7044,16 +7055,16 @@
         <v>3150</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C71" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G71" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -7061,16 +7072,16 @@
         <v>3200</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C72" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G72" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -7078,16 +7089,16 @@
         <v>3210</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C73" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G73" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -7095,19 +7106,19 @@
         <v>6001</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C74" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G74" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H74" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -7115,16 +7126,16 @@
         <v>6002</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C75" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G75" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -7132,16 +7143,16 @@
         <v>6100</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C76" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -7149,16 +7160,16 @@
         <v>6010</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C77" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G77" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -7166,16 +7177,16 @@
         <v>6011</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C78" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G78" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -7183,16 +7194,16 @@
         <v>6012</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C79" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G79" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -7200,16 +7211,16 @@
         <v>6020</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C80" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G80" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -7217,16 +7228,16 @@
         <v>6030</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C81" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G81" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -7234,16 +7245,16 @@
         <v>6040</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C82" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G82" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83" customFormat="1" spans="1:7">
@@ -7251,16 +7262,16 @@
         <v>6050</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G83" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="84" customFormat="1" spans="1:7">
@@ -7268,16 +7279,16 @@
         <v>6051</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C84" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G84" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="85" customFormat="1" spans="1:7">
@@ -7285,16 +7296,16 @@
         <v>6052</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C85" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G85" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -7302,16 +7313,16 @@
         <v>6210</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C86" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G86" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -7319,16 +7330,16 @@
         <v>6220</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C87" t="s">
+        <v>275</v>
+      </c>
+      <c r="F87" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="F87" s="2" t="s">
-        <v>273</v>
-      </c>
       <c r="G87" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -7336,16 +7347,16 @@
         <v>6230</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C88" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G88" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -7353,16 +7364,16 @@
         <v>6240</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C89" t="s">
+        <v>282</v>
+      </c>
+      <c r="F89" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="F89" s="2" t="s">
-        <v>280</v>
-      </c>
       <c r="G89" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -7370,16 +7381,16 @@
         <v>6250</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C90" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G90" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -7387,16 +7398,16 @@
         <v>6260</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C91" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G91" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -7404,16 +7415,16 @@
         <v>6270</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C92" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G92" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -7421,16 +7432,16 @@
         <v>6280</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C93" t="s">
+        <v>297</v>
+      </c>
+      <c r="F93" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="F93" s="2" t="s">
-        <v>295</v>
-      </c>
       <c r="G93" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="94" customFormat="1" spans="1:7">
@@ -7438,16 +7449,16 @@
         <v>6290</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C94" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G94" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="95" customFormat="1" spans="1:7">
@@ -7455,16 +7466,16 @@
         <v>6300</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C95" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G95" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -7472,16 +7483,16 @@
         <v>6810</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C96" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G96" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -7489,16 +7500,16 @@
         <v>6820</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C97" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G97" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -7506,16 +7517,16 @@
         <v>6830</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C98" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G98" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -7523,16 +7534,16 @@
         <v>6840</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C99" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G99" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -7540,16 +7551,16 @@
         <v>6850</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C100" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G100" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -7557,16 +7568,16 @@
         <v>6860</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C101" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G101" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -7574,16 +7585,16 @@
         <v>6870</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C102" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G102" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -7591,16 +7602,16 @@
         <v>6880</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C103" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G103" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -7608,16 +7619,16 @@
         <v>6890</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C104" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G104" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="105" customFormat="1" spans="1:7">
@@ -7625,16 +7636,16 @@
         <v>6900</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C105" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G105" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="106" customFormat="1" spans="1:7">
@@ -7642,16 +7653,16 @@
         <v>6910</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C106" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G106" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -7659,19 +7670,19 @@
         <v>10010</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C107" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G107" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H107" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -7679,16 +7690,16 @@
         <v>10100</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C108" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G108" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -7696,16 +7707,16 @@
         <v>10101</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C109" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G109" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -7713,16 +7724,16 @@
         <v>10110</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C110" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G110" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -7730,16 +7741,16 @@
         <v>10120</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C111" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G111" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -7747,16 +7758,16 @@
         <v>10121</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C112" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G112" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -7764,16 +7775,16 @@
         <v>10130</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C113" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G113" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -7781,16 +7792,16 @@
         <v>10131</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C114" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G114" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="115" ht="26" spans="1:7">
@@ -7798,16 +7809,16 @@
         <v>10132</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C115" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G115" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="116" ht="26" spans="1:7">
@@ -7815,16 +7826,16 @@
         <v>10133</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C116" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G116" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -7832,16 +7843,16 @@
         <v>10140</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C117" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G117" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -7849,16 +7860,16 @@
         <v>10141</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C118" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G118" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="119" customFormat="1" spans="1:7">
@@ -7866,16 +7877,16 @@
         <v>10142</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C119" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G119" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="120" customFormat="1" spans="1:7">
@@ -7883,16 +7894,16 @@
         <v>10143</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C120" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G120" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -7900,16 +7911,16 @@
         <v>10150</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C121" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G121" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -7917,16 +7928,16 @@
         <v>10160</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C122" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G122" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="123" customFormat="1" spans="1:7">
@@ -7934,16 +7945,16 @@
         <v>10170</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C123" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G123" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="124" customFormat="1" spans="1:7">
@@ -7951,16 +7962,16 @@
         <v>10171</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C124" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G124" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="125" customFormat="1" ht="26" spans="1:7">
@@ -7968,16 +7979,16 @@
         <v>10180</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C125" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G125" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="126" customFormat="1" spans="1:7">
@@ -7985,16 +7996,16 @@
         <v>10181</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C126" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G126" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="127" customFormat="1" ht="26" spans="1:7">
@@ -8002,16 +8013,16 @@
         <v>10182</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C127" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G127" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="128" customFormat="1" spans="1:7">
@@ -8019,16 +8030,16 @@
         <v>10190</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C128" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G128" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="129" customFormat="1" ht="26" spans="1:7">
@@ -8036,16 +8047,16 @@
         <v>10200</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C129" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G129" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="130" customFormat="1" spans="1:7">
@@ -8053,16 +8064,16 @@
         <v>10210</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C130" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G130" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="131" customFormat="1" spans="1:7">
@@ -8070,16 +8081,16 @@
         <v>10220</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C131" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G131" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="132" customFormat="1" ht="52" spans="1:7">
@@ -8087,16 +8098,16 @@
         <v>10230</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C132" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G132" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="133" customFormat="1" spans="1:7">
@@ -8104,16 +8115,16 @@
         <v>10240</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C133" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G133" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="134" ht="26" spans="1:8">
@@ -8121,19 +8132,19 @@
         <v>11010</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C134" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G134" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H134" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="135" ht="26" spans="1:7">
@@ -8141,16 +8152,16 @@
         <v>11011</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C135" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G135" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="136" customFormat="1" spans="1:7">
@@ -8158,16 +8169,16 @@
         <v>11012</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C136" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G136" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="137" customFormat="1" spans="1:7">
@@ -8175,16 +8186,16 @@
         <v>11013</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C137" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G137" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="138" customFormat="1" spans="1:7">
@@ -8192,16 +8203,16 @@
         <v>11014</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C138" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G138" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -8209,16 +8220,16 @@
         <v>11020</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C139" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G139" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="140" customFormat="1" spans="1:7">
@@ -8226,16 +8237,16 @@
         <v>11030</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C140" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G140" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -8243,16 +8254,16 @@
         <v>11040</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C141" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G141" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="142" customFormat="1" spans="1:7">
@@ -8260,16 +8271,16 @@
         <v>11050</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C142" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G142" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="143" customFormat="1" spans="1:7">
@@ -8277,16 +8288,16 @@
         <v>11060</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C143" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G143" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="144" customFormat="1" spans="1:7">
@@ -8294,16 +8305,16 @@
         <v>11070</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C144" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G144" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="145" ht="52" spans="1:8">
@@ -8311,19 +8322,19 @@
         <v>12010</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C145" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G145" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H145" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -8331,19 +8342,19 @@
         <v>13010</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C146" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G146" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H146" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -8351,16 +8362,16 @@
         <v>13020</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C147" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G147" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -8368,16 +8379,16 @@
         <v>13110</v>
       </c>
       <c r="B148" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C148" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F148" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G148" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -8385,16 +8396,16 @@
         <v>13210</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C149" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G149" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -8402,16 +8413,16 @@
         <v>13220</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C150" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G150" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -8419,16 +8430,16 @@
         <v>13230</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C151" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G151" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -8436,16 +8447,16 @@
         <v>13320</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C152" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G152" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="153" customFormat="1" spans="1:7">
@@ -8453,16 +8464,16 @@
         <v>13410</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C153" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G153" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -8470,16 +8481,16 @@
         <v>13510</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C154" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G154" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -8487,19 +8498,19 @@
         <v>14010</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C155" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G155" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H155" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -8507,16 +8518,16 @@
         <v>14020</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C156" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G156" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -8524,16 +8535,16 @@
         <v>14021</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C157" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G157" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -8541,16 +8552,16 @@
         <v>14030</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C158" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G158" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -8558,16 +8569,16 @@
         <v>14040</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C159" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G159" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -8575,16 +8586,16 @@
         <v>14050</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C160" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G160" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -8592,16 +8603,16 @@
         <v>14060</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C161" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G161" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -8609,16 +8620,16 @@
         <v>14070</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C162" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G162" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -8626,16 +8637,16 @@
         <v>14080</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C163" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G163" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -8643,16 +8654,16 @@
         <v>14090</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C164" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G164" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -8660,16 +8671,16 @@
         <v>14100</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C165" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G165" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -8677,16 +8688,16 @@
         <v>14110</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C166" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G166" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="167" customFormat="1" spans="1:7">
@@ -8694,16 +8705,16 @@
         <v>14120</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C167" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G167" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="168" customFormat="1" spans="1:7">
@@ -8711,16 +8722,16 @@
         <v>14121</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C168" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G168" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="169" customFormat="1" spans="1:7">
@@ -8728,16 +8739,16 @@
         <v>14122</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C169" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G169" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="170" customFormat="1" spans="1:7">
@@ -8745,16 +8756,16 @@
         <v>14123</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C170" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G170" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="171" customFormat="1" spans="1:7">
@@ -8762,16 +8773,16 @@
         <v>14124</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C171" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G171" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="172" customFormat="1" spans="1:7">
@@ -8779,16 +8790,16 @@
         <v>14125</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C172" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G172" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="173" customFormat="1" spans="1:7">
@@ -8796,16 +8807,16 @@
         <v>14126</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C173" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G173" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="174" customFormat="1" spans="1:7">
@@ -8813,16 +8824,16 @@
         <v>14127</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C174" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G174" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="175" customFormat="1" spans="1:7">
@@ -8830,16 +8841,16 @@
         <v>14130</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C175" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G175" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="176" customFormat="1" spans="1:7">
@@ -8847,16 +8858,16 @@
         <v>14140</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C176" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G176" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="177" customFormat="1" spans="1:7">
@@ -8864,16 +8875,16 @@
         <v>14150</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C177" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G177" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="178" customFormat="1" spans="1:7">
@@ -8881,16 +8892,16 @@
         <v>14160</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C178" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G178" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="179" customFormat="1" spans="1:7">
@@ -8898,16 +8909,16 @@
         <v>14170</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C179" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G179" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="180" customFormat="1" spans="1:7">
@@ -8915,16 +8926,16 @@
         <v>14180</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C180" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G180" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="181" customFormat="1" spans="1:7">
@@ -8932,14 +8943,14 @@
         <v>14190</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C181" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F181" s="1"/>
       <c r="G181" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="182" customFormat="1" spans="1:7">
@@ -8947,16 +8958,16 @@
         <v>14200</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C182" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G182" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="183" customFormat="1" spans="1:7">
@@ -8964,16 +8975,16 @@
         <v>14210</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C183" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G183" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="184" customFormat="1" spans="1:7">
@@ -8981,16 +8992,16 @@
         <v>14220</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C184" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G184" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="185" customFormat="1" spans="1:7">
@@ -8998,16 +9009,16 @@
         <v>14230</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C185" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G185" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="186" customFormat="1" spans="1:7">
@@ -9015,16 +9026,16 @@
         <v>14231</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C186" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G186" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="187" customFormat="1" spans="1:7">
@@ -9032,16 +9043,16 @@
         <v>14240</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C187" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G187" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="188" customFormat="1" spans="1:8">
@@ -9049,19 +9060,19 @@
         <v>15010</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C188" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G188" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H188" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="189" customFormat="1" spans="1:7">
@@ -9069,16 +9080,16 @@
         <v>15020</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C189" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G189" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="190" ht="14" spans="1:9">
@@ -9086,19 +9097,19 @@
         <v>16010</v>
       </c>
       <c r="B190" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C190" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F190" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G190" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H190" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I190" s="4"/>
     </row>
@@ -9107,16 +9118,16 @@
         <v>16020</v>
       </c>
       <c r="B191" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C191" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F191" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G191" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I191" s="4"/>
     </row>
@@ -9125,16 +9136,16 @@
         <v>16030</v>
       </c>
       <c r="B192" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C192" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F192" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G192" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I192" s="4"/>
     </row>
@@ -9143,16 +9154,16 @@
         <v>16040</v>
       </c>
       <c r="B193" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C193" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F193" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G193" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I193" s="4"/>
     </row>
@@ -9161,16 +9172,16 @@
         <v>16041</v>
       </c>
       <c r="B194" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C194" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F194" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G194" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I194" s="4"/>
     </row>
@@ -9179,16 +9190,16 @@
         <v>16100</v>
       </c>
       <c r="B195" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C195" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F195" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G195" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -9196,16 +9207,16 @@
         <v>16110</v>
       </c>
       <c r="B196" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C196" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F196" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G196" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -9213,16 +9224,16 @@
         <v>16200</v>
       </c>
       <c r="B197" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C197" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F197" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G197" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -9230,16 +9241,16 @@
         <v>16210</v>
       </c>
       <c r="B198" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C198" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F198" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G198" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -9247,16 +9258,16 @@
         <v>16220</v>
       </c>
       <c r="B199" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C199" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F199" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G199" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -9264,16 +9275,16 @@
         <v>16230</v>
       </c>
       <c r="B200" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C200" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F200" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G200" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -9281,16 +9292,16 @@
         <v>16400</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C201" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G201" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="202" spans="1:7">
@@ -9298,16 +9309,16 @@
         <v>16410</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C202" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G202" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -9315,19 +9326,19 @@
         <v>16800</v>
       </c>
       <c r="B203" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C203" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F203" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G203" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H203" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -9335,19 +9346,19 @@
         <v>16801</v>
       </c>
       <c r="B204" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C204" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F204" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G204" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H204" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -9355,19 +9366,19 @@
         <v>16802</v>
       </c>
       <c r="B205" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C205" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F205" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G205" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H205" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -9375,19 +9386,19 @@
         <v>16803</v>
       </c>
       <c r="B206" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C206" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F206" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G206" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H206" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -9395,19 +9406,19 @@
         <v>16804</v>
       </c>
       <c r="B207" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C207" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F207" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G207" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H207" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -9415,19 +9426,19 @@
         <v>16805</v>
       </c>
       <c r="B208" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C208" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F208" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G208" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H208" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -9435,19 +9446,19 @@
         <v>16806</v>
       </c>
       <c r="B209" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C209" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F209" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G209" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H209" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="210" ht="14" spans="1:9">
@@ -9455,19 +9466,19 @@
         <v>19000</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C210" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G210" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H210" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="I210" s="4"/>
     </row>
@@ -9476,16 +9487,16 @@
         <v>19001</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C211" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G211" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -9493,16 +9504,16 @@
         <v>19002</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C212" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G212" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="213" spans="1:7">
@@ -9510,16 +9521,16 @@
         <v>19003</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C213" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G213" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="214" spans="1:7">
@@ -9527,16 +9538,16 @@
         <v>19004</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C214" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G214" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -9544,16 +9555,16 @@
         <v>19005</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C215" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>8</v>
       </c>
       <c r="G215" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -9561,16 +9572,16 @@
         <v>19006</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C216" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G216" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -9578,16 +9589,16 @@
         <v>19007</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C217" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G217" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="218" spans="1:7">
@@ -9595,16 +9606,16 @@
         <v>19100</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C218" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G218" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -9615,13 +9626,13 @@
         <v>40</v>
       </c>
       <c r="C219" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F219" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G219" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -9629,16 +9640,16 @@
         <v>19102</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C220" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G220" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -9646,16 +9657,16 @@
         <v>19103</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C221" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G221" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -9663,16 +9674,16 @@
         <v>19104</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C222" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G222" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -9680,16 +9691,16 @@
         <v>19105</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C223" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G223" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -9697,16 +9708,16 @@
         <v>19106</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C224" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G224" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -9714,16 +9725,16 @@
         <v>19107</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C225" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G225" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -9731,16 +9742,16 @@
         <v>19108</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C226" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G226" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -9748,16 +9759,16 @@
         <v>19109</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C227" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G227" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="228" spans="1:8">
@@ -9765,19 +9776,19 @@
         <v>20010</v>
       </c>
       <c r="B228" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C228" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F228" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="G228" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H228" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -9785,16 +9796,16 @@
         <v>20020</v>
       </c>
       <c r="B229" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C229" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F229" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G229" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -9802,16 +9813,16 @@
         <v>20030</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C230" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G230" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -9819,16 +9830,16 @@
         <v>20040</v>
       </c>
       <c r="B231" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C231" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F231" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="G231" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -9836,16 +9847,16 @@
         <v>20050</v>
       </c>
       <c r="B232" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C232" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F232" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="G232" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -9853,16 +9864,16 @@
         <v>20100</v>
       </c>
       <c r="B233" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C233" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F233" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="G233" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -9870,16 +9881,16 @@
         <v>20110</v>
       </c>
       <c r="B234" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C234" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F234" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G234" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -9887,16 +9898,16 @@
         <v>20111</v>
       </c>
       <c r="B235" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C235" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F235" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G235" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -9904,16 +9915,16 @@
         <v>20120</v>
       </c>
       <c r="B236" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C236" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F236" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="G236" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="237" customFormat="1" spans="1:7">
@@ -9921,16 +9932,16 @@
         <v>20130</v>
       </c>
       <c r="B237" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C237" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F237" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="G237" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -9938,16 +9949,16 @@
         <v>20200</v>
       </c>
       <c r="B238" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C238" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F238" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G238" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -9955,16 +9966,16 @@
         <v>20201</v>
       </c>
       <c r="B239" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C239" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F239" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="G239" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -9972,16 +9983,16 @@
         <v>20210</v>
       </c>
       <c r="B240" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C240" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F240" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="G240" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -9989,16 +10000,16 @@
         <v>20220</v>
       </c>
       <c r="B241" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C241" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F241" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="G241" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -10006,16 +10017,16 @@
         <v>20230</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C242" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G242" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -10023,16 +10034,16 @@
         <v>20240</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C243" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="G243" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -10040,16 +10051,16 @@
         <v>20250</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C244" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="G244" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -10057,16 +10068,16 @@
         <v>20270</v>
       </c>
       <c r="B245" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C245" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F245" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="G245" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="246" customFormat="1" spans="1:7">
@@ -10074,16 +10085,16 @@
         <v>20280</v>
       </c>
       <c r="B246" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C246" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F246" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="G246" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="247" spans="1:7">
@@ -10091,16 +10102,16 @@
         <v>20300</v>
       </c>
       <c r="B247" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C247" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F247" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G247" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="248" spans="1:7">
@@ -10108,13 +10119,13 @@
         <v>20301</v>
       </c>
       <c r="B248" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C248" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G248" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="249" spans="1:7">
@@ -10122,16 +10133,16 @@
         <v>20310</v>
       </c>
       <c r="B249" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C249" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F249" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="G249" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="250" spans="1:7">
@@ -10139,16 +10150,16 @@
         <v>20320</v>
       </c>
       <c r="B250" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C250" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F250" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G250" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -10156,16 +10167,16 @@
         <v>20330</v>
       </c>
       <c r="B251" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C251" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F251" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="G251" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="252" spans="1:6">
@@ -10173,13 +10184,13 @@
         <v>20340</v>
       </c>
       <c r="B252" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C252" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F252" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -10187,13 +10198,13 @@
         <v>20350</v>
       </c>
       <c r="B253" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C253" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F253" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="254" customFormat="1" spans="1:6">
@@ -10201,13 +10212,13 @@
         <v>20360</v>
       </c>
       <c r="B254" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C254" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F254" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="255" customFormat="1" spans="1:6">
@@ -10215,13 +10226,13 @@
         <v>20370</v>
       </c>
       <c r="B255" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C255" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F255" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="256" customFormat="1" spans="1:6">
@@ -10229,13 +10240,13 @@
         <v>20380</v>
       </c>
       <c r="B256" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C256" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F256" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="257" customFormat="1" spans="1:6">
@@ -10243,13 +10254,13 @@
         <v>20390</v>
       </c>
       <c r="B257" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C257" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F257" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="258" customFormat="1" spans="1:6">
@@ -10257,13 +10268,13 @@
         <v>20400</v>
       </c>
       <c r="B258" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C258" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F258" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="259" customFormat="1" spans="1:8">
@@ -10271,16 +10282,16 @@
         <v>20410</v>
       </c>
       <c r="B259" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C259" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F259" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H259" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="260" customFormat="1" spans="1:6">
@@ -10288,13 +10299,13 @@
         <v>20411</v>
       </c>
       <c r="B260" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C260" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F260" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="261" customFormat="1" spans="1:6">
@@ -10302,13 +10313,13 @@
         <v>20420</v>
       </c>
       <c r="B261" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C261" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F261" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="262" customFormat="1" spans="1:6">
@@ -10316,13 +10327,13 @@
         <v>20430</v>
       </c>
       <c r="B262" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C262" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F262" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="263" customFormat="1" spans="1:6">
@@ -10330,13 +10341,13 @@
         <v>20440</v>
       </c>
       <c r="B263" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C263" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F263" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -10344,16 +10355,16 @@
         <v>31010</v>
       </c>
       <c r="B264" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C264" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F264" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H264" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -10361,13 +10372,13 @@
         <v>31020</v>
       </c>
       <c r="B265" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C265" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F265" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="266" customFormat="1" spans="1:6">
@@ -10375,13 +10386,13 @@
         <v>31030</v>
       </c>
       <c r="B266" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C266" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F266" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="267" customFormat="1" spans="1:6">
@@ -10389,13 +10400,13 @@
         <v>31040</v>
       </c>
       <c r="B267" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C267" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F267" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -10403,13 +10414,13 @@
         <v>31050</v>
       </c>
       <c r="B268" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C268" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F268" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="269" customFormat="1" spans="1:6">
@@ -10417,13 +10428,13 @@
         <v>31060</v>
       </c>
       <c r="B269" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C269" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F269" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="270" customFormat="1" spans="1:6">
@@ -10431,13 +10442,13 @@
         <v>31061</v>
       </c>
       <c r="B270" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C270" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F270" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="271" customFormat="1" spans="1:7">
@@ -10445,16 +10456,16 @@
         <v>31070</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C271" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F271" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G271" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="272" customFormat="1" ht="26" spans="1:7">
@@ -10462,16 +10473,16 @@
         <v>31071</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C272" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="G272" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="273" customFormat="1" spans="1:7">
@@ -10479,16 +10490,16 @@
         <v>31080</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C273" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G273" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -10496,19 +10507,19 @@
         <v>32010</v>
       </c>
       <c r="B274" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C274" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F274" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="G274" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H274" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -10516,16 +10527,16 @@
         <v>32020</v>
       </c>
       <c r="B275" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C275" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F275" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G275" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -10533,16 +10544,16 @@
         <v>32030</v>
       </c>
       <c r="B276" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C276" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F276" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="G276" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -10550,16 +10561,16 @@
         <v>32040</v>
       </c>
       <c r="B277" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C277" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F277" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G277" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -10567,16 +10578,16 @@
         <v>32050</v>
       </c>
       <c r="B278" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C278" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F278" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="G278" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -10584,16 +10595,16 @@
         <v>32060</v>
       </c>
       <c r="B279" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C279" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F279" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G279" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -10601,16 +10612,16 @@
         <v>32070</v>
       </c>
       <c r="B280" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C280" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F280" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G280" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -10618,16 +10629,16 @@
         <v>32080</v>
       </c>
       <c r="B281" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C281" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F281" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G281" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -10635,16 +10646,16 @@
         <v>32090</v>
       </c>
       <c r="B282" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C282" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F282" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="G282" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -10652,16 +10663,16 @@
         <v>32091</v>
       </c>
       <c r="B283" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C283" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F283" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G283" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -10669,16 +10680,16 @@
         <v>32092</v>
       </c>
       <c r="B284" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C284" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F284" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G284" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -10686,16 +10697,16 @@
         <v>32100</v>
       </c>
       <c r="B285" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C285" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F285" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="G285" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="286" customFormat="1" spans="1:7">
@@ -10703,16 +10714,16 @@
         <v>32110</v>
       </c>
       <c r="B286" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C286" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F286" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G286" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="287" spans="1:8">
@@ -10720,19 +10731,19 @@
         <v>33010</v>
       </c>
       <c r="B287" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C287" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F287" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G287" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H287" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -10740,16 +10751,16 @@
         <v>33011</v>
       </c>
       <c r="B288" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C288" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F288" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G288" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -10757,16 +10768,16 @@
         <v>33020</v>
       </c>
       <c r="B289" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C289" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F289" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G289" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -10774,16 +10785,16 @@
         <v>33030</v>
       </c>
       <c r="B290" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C290" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F290" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="G290" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -10791,16 +10802,16 @@
         <v>33040</v>
       </c>
       <c r="B291" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C291" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F291" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="G291" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="292" spans="1:8">
@@ -10808,19 +10819,19 @@
         <v>34010</v>
       </c>
       <c r="B292" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C292" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F292" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G292" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H292" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -10828,16 +10839,16 @@
         <v>34020</v>
       </c>
       <c r="B293" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C293" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F293" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="G293" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -10845,16 +10856,16 @@
         <v>34030</v>
       </c>
       <c r="B294" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C294" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F294" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G294" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -10862,16 +10873,16 @@
         <v>34040</v>
       </c>
       <c r="B295" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C295" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F295" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="G295" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -10879,16 +10890,16 @@
         <v>34050</v>
       </c>
       <c r="B296" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C296" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F296" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="G296" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="297" customFormat="1" spans="1:7">
@@ -10896,16 +10907,16 @@
         <v>34060</v>
       </c>
       <c r="B297" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C297" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F297" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G297" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="298" customFormat="1" spans="1:7">
@@ -10913,16 +10924,16 @@
         <v>34070</v>
       </c>
       <c r="B298" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C298" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F298" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G298" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="299" spans="1:8">
@@ -10930,16 +10941,16 @@
         <v>35010</v>
       </c>
       <c r="B299" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C299" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F299" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="G299" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -10950,16 +10961,16 @@
         <v>35020</v>
       </c>
       <c r="B300" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C300" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F300" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="G300" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="301" customFormat="1" spans="1:7">
@@ -10967,16 +10978,16 @@
         <v>35021</v>
       </c>
       <c r="B301" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C301" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F301" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="G301" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="302" customFormat="1" spans="1:7">
@@ -10984,16 +10995,16 @@
         <v>35030</v>
       </c>
       <c r="B302" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C302" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F302" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="G302" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="303" customFormat="1" spans="1:7">
@@ -11001,16 +11012,16 @@
         <v>35040</v>
       </c>
       <c r="B303" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C303" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F303" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G303" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="304" customFormat="1" spans="1:7">
@@ -11018,16 +11029,16 @@
         <v>35050</v>
       </c>
       <c r="B304" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C304" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F304" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="G304" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="305" customFormat="1" spans="1:7">
@@ -11035,16 +11046,16 @@
         <v>35060</v>
       </c>
       <c r="B305" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C305" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F305" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="G305" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="306" spans="1:8">
@@ -11052,19 +11063,19 @@
         <v>36010</v>
       </c>
       <c r="B306" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C306" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F306" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="G306" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H306" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -11072,16 +11083,16 @@
         <v>36011</v>
       </c>
       <c r="B307" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C307" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F307" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="G307" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="308" spans="1:8">
@@ -11089,19 +11100,19 @@
         <v>37000</v>
       </c>
       <c r="B308" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C308" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F308" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="G308" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H308" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -11109,16 +11120,16 @@
         <v>37010</v>
       </c>
       <c r="B309" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C309" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F309" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="G309" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="310" spans="1:7">
@@ -11126,16 +11137,16 @@
         <v>37020</v>
       </c>
       <c r="B310" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C310" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F310" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="G310" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="311" spans="1:8">
@@ -11143,19 +11154,19 @@
         <v>38010</v>
       </c>
       <c r="B311" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C311" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F311" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="G311" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H311" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -11163,16 +11174,16 @@
         <v>38020</v>
       </c>
       <c r="B312" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C312" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F312" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="G312" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="313" spans="1:7">
@@ -11180,16 +11191,16 @@
         <v>38030</v>
       </c>
       <c r="B313" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C313" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F313" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="G313" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="314" spans="1:8">
@@ -11197,16 +11208,16 @@
         <v>39010</v>
       </c>
       <c r="B314" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C314" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F314" t="s">
         <v>9</v>
       </c>
       <c r="G314" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H314" t="s">
         <v>9</v>
@@ -11220,13 +11231,13 @@
         <v>58</v>
       </c>
       <c r="C315" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F315" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="G315" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="316" customFormat="1" spans="1:7">
@@ -11234,16 +11245,16 @@
         <v>39030</v>
       </c>
       <c r="B316" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C316" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F316" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="G316" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="317" spans="1:7">
@@ -11251,16 +11262,16 @@
         <v>39040</v>
       </c>
       <c r="B317" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C317" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F317" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="G317" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="318" customFormat="1" spans="1:7">
@@ -11268,16 +11279,16 @@
         <v>39050</v>
       </c>
       <c r="B318" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C318" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F318" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="G318" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="319" customFormat="1" spans="1:7">
@@ -11285,16 +11296,16 @@
         <v>39051</v>
       </c>
       <c r="B319" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C319" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F319" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="G319" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="320" customFormat="1" spans="1:7">
@@ -11302,16 +11313,16 @@
         <v>39060</v>
       </c>
       <c r="B320" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C320" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F320" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="G320" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="321" customFormat="1" spans="1:7">
@@ -11319,16 +11330,16 @@
         <v>39070</v>
       </c>
       <c r="B321" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C321" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F321" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G321" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="322" customFormat="1" spans="1:7">
@@ -11336,16 +11347,16 @@
         <v>39080</v>
       </c>
       <c r="B322" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C322" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F322" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="G322" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="323" customFormat="1" spans="1:7">
@@ -11353,16 +11364,16 @@
         <v>39090</v>
       </c>
       <c r="B323" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C323" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F323" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="G323" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="324" customFormat="1" spans="1:7">
@@ -11370,16 +11381,16 @@
         <v>39100</v>
       </c>
       <c r="B324" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C324" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F324" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G324" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="325" spans="1:8">
@@ -11387,19 +11398,19 @@
         <v>40010</v>
       </c>
       <c r="B325" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C325" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F325" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G325" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H325" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="326" spans="1:7">
@@ -11407,16 +11418,16 @@
         <v>40020</v>
       </c>
       <c r="B326" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C326" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F326" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="G326" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="327" spans="1:8">
@@ -11424,19 +11435,19 @@
         <v>41010</v>
       </c>
       <c r="B327" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C327" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F327" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="G327" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H327" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -11444,19 +11455,19 @@
         <v>42010</v>
       </c>
       <c r="B328" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="C328" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F328" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G328" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H328" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="329" spans="1:7">
@@ -11464,16 +11475,16 @@
         <v>42011</v>
       </c>
       <c r="B329" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C329" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F329" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="G329" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="330" customFormat="1" spans="1:7">
@@ -11481,16 +11492,16 @@
         <v>42020</v>
       </c>
       <c r="B330" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C330" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F330" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="G330" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="331" customFormat="1" spans="1:7">
@@ -11498,16 +11509,16 @@
         <v>42030</v>
       </c>
       <c r="B331" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C331" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F331" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="G331" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="332" customFormat="1" spans="1:7">
@@ -11515,16 +11526,16 @@
         <v>42040</v>
       </c>
       <c r="B332" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C332" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F332" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="G332" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="333" spans="1:8">
@@ -11532,16 +11543,16 @@
         <v>43010</v>
       </c>
       <c r="B333" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C333" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F333" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="G333" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H333" t="s">
         <v>4</v>
@@ -11552,16 +11563,16 @@
         <v>43020</v>
       </c>
       <c r="B334" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C334" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F334" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G334" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="335" customFormat="1" spans="1:8">
@@ -11569,19 +11580,19 @@
         <v>44010</v>
       </c>
       <c r="B335" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C335" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F335" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="G335" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H335" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="336" spans="1:8">
@@ -11589,19 +11600,19 @@
         <v>45010</v>
       </c>
       <c r="B336" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C336" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F336" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="G336" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H336" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="337" spans="1:7">
@@ -11609,16 +11620,16 @@
         <v>45020</v>
       </c>
       <c r="B337" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C337" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F337" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="G337" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="338" spans="1:7">
@@ -11626,16 +11637,16 @@
         <v>45030</v>
       </c>
       <c r="B338" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C338" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F338" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="G338" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="339" spans="1:8">
@@ -11643,19 +11654,19 @@
         <v>46010</v>
       </c>
       <c r="B339" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="C339" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F339" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="G339" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H339" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="340" spans="1:7">
@@ -11663,16 +11674,16 @@
         <v>46020</v>
       </c>
       <c r="B340" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C340" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F340" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="G340" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="341" spans="1:7">
@@ -11680,16 +11691,16 @@
         <v>46030</v>
       </c>
       <c r="B341" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C341" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F341" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="G341" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="342" customFormat="1" spans="1:7">
@@ -11697,18 +11708,16 @@
         <v>46040</v>
       </c>
       <c r="B342" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C342" t="s">
-        <v>116</v>
-      </c>
-      <c r="D342"/>
-      <c r="E342"/>
+        <v>117</v>
+      </c>
       <c r="F342" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G342" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="343" customFormat="1" spans="1:7">
@@ -11716,16 +11725,16 @@
         <v>46050</v>
       </c>
       <c r="B343" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C343" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F343" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="G343" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="766" firstSheet="1" activeTab="5"/>
+    <workbookView windowWidth="18650" windowHeight="8390" tabRatio="766" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="TacticsComand" sheetId="1" r:id="rId1"/>
@@ -1211,7 +1211,7 @@
     <t>終末まで　　残り　{0}　Period</t>
   </si>
   <si>
-    <t>{0} Periods remaining until the End of World</t>
+    <t>{0} Periods remaining until the End</t>
   </si>
   <si>
     <t>交戦中</t>
@@ -2281,10 +2281,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -2308,8 +2308,25 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2323,12 +2340,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2337,23 +2362,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2367,6 +2376,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2374,19 +2391,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2407,7 +2415,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -2424,7 +2432,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2432,21 +2447,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2467,7 +2467,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2479,7 +2479,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2491,19 +2521,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2515,25 +2539,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2545,13 +2563,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2563,19 +2581,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2593,19 +2599,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2617,31 +2623,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2670,6 +2670,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -2687,9 +2711,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2697,17 +2723,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2727,28 +2744,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2760,22 +2760,22 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -2784,121 +2784,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/System.xlsx
+++ b/Assets/Data/System.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="748">
   <si>
     <t>Id</t>
   </si>
@@ -1153,6 +1153,9 @@
   </si>
   <si>
     <t>アーティファクトを持ち込んだため評価値が減少しました！</t>
+  </si>
+  <si>
+    <t>Evaluation decreased because an artifact was brought in!</t>
   </si>
   <si>
     <t>エインフェリアを招聘しますか？
@@ -2281,10 +2284,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -2308,11 +2311,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2324,16 +2326,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2353,9 +2348,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2368,17 +2362,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2391,8 +2376,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2408,14 +2394,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -2432,9 +2410,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2445,8 +2423,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2467,18 +2470,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2491,109 +2482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2611,13 +2500,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2629,19 +2626,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2673,23 +2676,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2705,26 +2693,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2748,7 +2716,42 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2760,22 +2763,22 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -2784,121 +2787,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -8121,7 +8124,7 @@
         <v>117</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>117</v>
+        <v>376</v>
       </c>
       <c r="G133" t="s">
         <v>117</v>
@@ -8132,19 +8135,19 @@
         <v>11010</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C134" t="s">
         <v>117</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G134" t="s">
         <v>117</v>
       </c>
       <c r="H134" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="135" ht="26" spans="1:7">
@@ -8152,13 +8155,13 @@
         <v>11011</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C135" t="s">
         <v>117</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G135" t="s">
         <v>117</v>
@@ -8169,13 +8172,13 @@
         <v>11012</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C136" t="s">
         <v>117</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G136" t="s">
         <v>117</v>
@@ -8186,13 +8189,13 @@
         <v>11013</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C137" t="s">
         <v>117</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G137" t="s">
         <v>117</v>
@@ -8203,13 +8206,13 @@
         <v>11014</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C138" t="s">
         <v>117</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G138" t="s">
         <v>117</v>
@@ -8220,13 +8223,13 @@
         <v>11020</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C139" t="s">
         <v>117</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G139" t="s">
         <v>117</v>
@@ -8237,13 +8240,13 @@
         <v>11030</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C140" t="s">
         <v>117</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G140" t="s">
         <v>117</v>
@@ -8254,13 +8257,13 @@
         <v>11040</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C141" t="s">
         <v>117</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G141" t="s">
         <v>117</v>
@@ -8271,13 +8274,13 @@
         <v>11050</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C142" t="s">
         <v>117</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G142" t="s">
         <v>117</v>
@@ -8288,13 +8291,13 @@
         <v>11060</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C143" t="s">
         <v>117</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G143" t="s">
         <v>117</v>
@@ -8305,13 +8308,13 @@
         <v>11070</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C144" t="s">
         <v>117</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G144" t="s">
         <v>117</v>
@@ -8322,19 +8325,19 @@
         <v>12010</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C145" t="s">
         <v>117</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G145" t="s">
         <v>117</v>
       </c>
       <c r="H145" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -8342,19 +8345,19 @@
         <v>13010</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C146" t="s">
         <v>117</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G146" t="s">
         <v>117</v>
       </c>
       <c r="H146" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -8362,13 +8365,13 @@
         <v>13020</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C147" t="s">
         <v>117</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G147" t="s">
         <v>117</v>
@@ -8379,13 +8382,13 @@
         <v>13110</v>
       </c>
       <c r="B148" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C148" t="s">
         <v>117</v>
       </c>
       <c r="F148" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G148" t="s">
         <v>117</v>
@@ -8396,13 +8399,13 @@
         <v>13210</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C149" t="s">
         <v>117</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G149" t="s">
         <v>117</v>
@@ -8413,13 +8416,13 @@
         <v>13220</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C150" t="s">
         <v>117</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G150" t="s">
         <v>117</v>
@@ -8430,13 +8433,13 @@
         <v>13230</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C151" t="s">
         <v>117</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G151" t="s">
         <v>117</v>
@@ -8447,13 +8450,13 @@
         <v>13320</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C152" t="s">
         <v>117</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G152" t="s">
         <v>117</v>
@@ -8464,13 +8467,13 @@
         <v>13410</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C153" t="s">
         <v>117</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G153" t="s">
         <v>117</v>
@@ -8481,13 +8484,13 @@
         <v>13510</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C154" t="s">
         <v>117</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G154" t="s">
         <v>117</v>
@@ -8498,19 +8501,19 @@
         <v>14010</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C155" t="s">
         <v>117</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G155" t="s">
         <v>117</v>
       </c>
       <c r="H155" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -8518,13 +8521,13 @@
         <v>14020</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C156" t="s">
         <v>117</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G156" t="s">
         <v>117</v>
@@ -8535,13 +8538,13 @@
         <v>14021</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C157" t="s">
         <v>117</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G157" t="s">
         <v>117</v>
@@ -8552,13 +8555,13 @@
         <v>14030</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C158" t="s">
         <v>117</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G158" t="s">
         <v>117</v>
@@ -8569,13 +8572,13 @@
         <v>14040</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C159" t="s">
         <v>117</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G159" t="s">
         <v>117</v>
@@ -8586,13 +8589,13 @@
         <v>14050</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C160" t="s">
         <v>117</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G160" t="s">
         <v>117</v>
@@ -8620,13 +8623,13 @@
         <v>14070</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C162" t="s">
         <v>117</v>
       </c>
       <c r="F162" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G162" t="s">
         <v>117</v>
@@ -8637,13 +8640,13 @@
         <v>14080</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C163" t="s">
         <v>117</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G163" t="s">
         <v>117</v>
@@ -8654,13 +8657,13 @@
         <v>14090</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C164" t="s">
         <v>117</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G164" t="s">
         <v>117</v>
@@ -8671,13 +8674,13 @@
         <v>14100</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C165" t="s">
         <v>117</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G165" t="s">
         <v>117</v>
@@ -8688,13 +8691,13 @@
         <v>14110</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C166" t="s">
         <v>117</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G166" t="s">
         <v>117</v>
@@ -8705,13 +8708,13 @@
         <v>14120</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C167" t="s">
         <v>117</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G167" t="s">
         <v>117</v>
@@ -8722,7 +8725,7 @@
         <v>14121</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C168" t="s">
         <v>117</v>
@@ -8739,13 +8742,13 @@
         <v>14122</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C169" t="s">
         <v>117</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G169" t="s">
         <v>117</v>
@@ -8756,13 +8759,13 @@
         <v>14123</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C170" t="s">
         <v>117</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G170" t="s">
         <v>117</v>
@@ -8773,13 +8776,13 @@
         <v>14124</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C171" t="s">
         <v>117</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G171" t="s">
         <v>117</v>
@@ -8790,13 +8793,13 @@
         <v>14125</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C172" t="s">
         <v>117</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G172" t="s">
         <v>117</v>
@@ -8807,13 +8810,13 @@
         <v>14126</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C173" t="s">
         <v>117</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G173" t="s">
         <v>117</v>
@@ -8824,13 +8827,13 @@
         <v>14127</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C174" t="s">
         <v>117</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G174" t="s">
         <v>117</v>
@@ -8841,13 +8844,13 @@
         <v>14130</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C175" t="s">
         <v>117</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G175" t="s">
         <v>117</v>
@@ -8875,13 +8878,13 @@
         <v>14150</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C177" t="s">
         <v>117</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G177" t="s">
         <v>117</v>
@@ -8892,13 +8895,13 @@
         <v>14160</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C178" t="s">
         <v>117</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G178" t="s">
         <v>117</v>
@@ -8909,13 +8912,13 @@
         <v>14170</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C179" t="s">
         <v>117</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G179" t="s">
         <v>117</v>
@@ -8926,13 +8929,13 @@
         <v>14180</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C180" t="s">
         <v>117</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G180" t="s">
         <v>117</v>
@@ -8943,7 +8946,7 @@
         <v>14190</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C181" t="s">
         <v>117</v>
@@ -8958,13 +8961,13 @@
         <v>14200</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C182" t="s">
         <v>117</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G182" t="s">
         <v>117</v>
@@ -8975,13 +8978,13 @@
         <v>14210</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C183" t="s">
         <v>117</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G183" t="s">
         <v>117</v>
@@ -8992,13 +8995,13 @@
         <v>14220</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C184" t="s">
         <v>117</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G184" t="s">
         <v>117</v>
@@ -9009,13 +9012,13 @@
         <v>14230</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C185" t="s">
         <v>117</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G185" t="s">
         <v>117</v>
@@ -9026,13 +9029,13 @@
         <v>14231</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C186" t="s">
         <v>117</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G186" t="s">
         <v>117</v>
@@ -9043,13 +9046,13 @@
         <v>14240</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C187" t="s">
         <v>117</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G187" t="s">
         <v>117</v>
@@ -9060,19 +9063,19 @@
         <v>15010</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C188" t="s">
         <v>117</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G188" t="s">
         <v>117</v>
       </c>
       <c r="H188" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="189" customFormat="1" spans="1:7">
@@ -9080,13 +9083,13 @@
         <v>15020</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C189" t="s">
         <v>117</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G189" t="s">
         <v>117</v>
@@ -9109,7 +9112,7 @@
         <v>117</v>
       </c>
       <c r="H190" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="I190" s="4"/>
     </row>
@@ -9118,13 +9121,13 @@
         <v>16020</v>
       </c>
       <c r="B191" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C191" t="s">
         <v>117</v>
       </c>
       <c r="F191" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G191" t="s">
         <v>117</v>
@@ -9136,13 +9139,13 @@
         <v>16030</v>
       </c>
       <c r="B192" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C192" t="s">
         <v>117</v>
       </c>
       <c r="F192" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G192" t="s">
         <v>117</v>
@@ -9154,13 +9157,13 @@
         <v>16040</v>
       </c>
       <c r="B193" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C193" t="s">
         <v>117</v>
       </c>
       <c r="F193" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G193" t="s">
         <v>117</v>
@@ -9172,13 +9175,13 @@
         <v>16041</v>
       </c>
       <c r="B194" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C194" t="s">
         <v>117</v>
       </c>
       <c r="F194" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G194" t="s">
         <v>117</v>
@@ -9190,13 +9193,13 @@
         <v>16100</v>
       </c>
       <c r="B195" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C195" t="s">
         <v>117</v>
       </c>
       <c r="F195" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G195" t="s">
         <v>117</v>
@@ -9207,13 +9210,13 @@
         <v>16110</v>
       </c>
       <c r="B196" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C196" t="s">
         <v>117</v>
       </c>
       <c r="F196" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G196" t="s">
         <v>117</v>
@@ -9224,13 +9227,13 @@
         <v>16200</v>
       </c>
       <c r="B197" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C197" t="s">
         <v>117</v>
       </c>
       <c r="F197" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G197" t="s">
         <v>117</v>
@@ -9241,13 +9244,13 @@
         <v>16210</v>
       </c>
       <c r="B198" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C198" t="s">
         <v>117</v>
       </c>
       <c r="F198" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G198" t="s">
         <v>117</v>
@@ -9258,13 +9261,13 @@
         <v>16220</v>
       </c>
       <c r="B199" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C199" t="s">
         <v>117</v>
       </c>
       <c r="F199" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G199" t="s">
         <v>117</v>
@@ -9275,13 +9278,13 @@
         <v>16230</v>
       </c>
       <c r="B200" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C200" t="s">
         <v>117</v>
       </c>
       <c r="F200" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G200" t="s">
         <v>117</v>
@@ -9292,13 +9295,13 @@
         <v>16400</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C201" t="s">
         <v>117</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G201" t="s">
         <v>117</v>
@@ -9309,13 +9312,13 @@
         <v>16410</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C202" t="s">
         <v>117</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G202" t="s">
         <v>117</v>
@@ -9338,7 +9341,7 @@
         <v>117</v>
       </c>
       <c r="H203" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -9358,7 +9361,7 @@
         <v>117</v>
       </c>
       <c r="H204" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="205" spans="1:8">
@@ -9378,7 +9381,7 @@
         <v>117</v>
       </c>
       <c r="H205" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -9398,7 +9401,7 @@
         <v>117</v>
       </c>
       <c r="H206" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="207" spans="1:8">
@@ -9418,7 +9421,7 @@
         <v>117</v>
       </c>
       <c r="H207" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="208" spans="1:8">
@@ -9438,7 +9441,7 @@
         <v>117</v>
       </c>
       <c r="H208" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="209" spans="1:8">
@@ -9458,7 +9461,7 @@
         <v>117</v>
       </c>
       <c r="H209" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="210" ht="14" spans="1:9">
@@ -9466,19 +9469,19 @@
         <v>19000</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C210" t="s">
         <v>117</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G210" t="s">
         <v>117</v>
       </c>
       <c r="H210" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I210" s="4"/>
     </row>
@@ -9487,13 +9490,13 @@
         <v>19001</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C211" t="s">
         <v>117</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G211" t="s">
         <v>117</v>
@@ -9504,13 +9507,13 @@
         <v>19002</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C212" t="s">
         <v>117</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G212" t="s">
         <v>117</v>
@@ -9521,13 +9524,13 @@
         <v>19003</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C213" t="s">
         <v>117</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G213" t="s">
         <v>117</v>
@@ -9538,13 +9541,13 @@
         <v>19004</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C214" t="s">
         <v>117</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G214" t="s">
         <v>117</v>
@@ -9555,7 +9558,7 @@
         <v>19005</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C215" t="s">
         <v>117</v>
@@ -9572,13 +9575,13 @@
         <v>19006</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C216" t="s">
         <v>117</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G216" t="s">
         <v>117</v>
@@ -9589,7 +9592,7 @@
         <v>19007</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C217" t="s">
         <v>117</v>
@@ -9606,13 +9609,13 @@
         <v>19100</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C218" t="s">
         <v>117</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G218" t="s">
         <v>117</v>
@@ -9626,13 +9629,13 @@
         <v>40</v>
       </c>
       <c r="C219" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F219" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G219" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -9640,7 +9643,7 @@
         <v>19102</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C220" t="s">
         <v>117</v>
@@ -9657,13 +9660,13 @@
         <v>19103</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C221" t="s">
         <v>117</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G221" t="s">
         <v>117</v>
@@ -9674,13 +9677,13 @@
         <v>19104</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C222" t="s">
         <v>117</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G222" t="s">
         <v>117</v>
@@ -9691,13 +9694,13 @@
         <v>19105</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C223" t="s">
         <v>117</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="G223" t="s">
         <v>117</v>
@@ -9708,13 +9711,13 @@
         <v>19106</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C224" t="s">
         <v>117</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G224" t="s">
         <v>117</v>
@@ -9725,13 +9728,13 @@
         <v>19107</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C225" t="s">
         <v>117</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G225" t="s">
         <v>117</v>
@@ -9742,13 +9745,13 @@
         <v>19108</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C226" t="s">
         <v>117</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G226" t="s">
         <v>117</v>
@@ -9759,13 +9762,13 @@
         <v>19109</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C227" t="s">
         <v>117</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="G227" t="s">
         <v>117</v>
@@ -9776,19 +9779,19 @@
         <v>20010</v>
       </c>
       <c r="B228" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C228" t="s">
         <v>117</v>
       </c>
       <c r="F228" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G228" t="s">
         <v>117</v>
       </c>
       <c r="H228" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -9796,13 +9799,13 @@
         <v>20020</v>
       </c>
       <c r="B229" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C229" t="s">
         <v>117</v>
       </c>
       <c r="F229" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G229" t="s">
         <v>117</v>
@@ -9813,13 +9816,13 @@
         <v>20030</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C230" t="s">
         <v>117</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="G230" t="s">
         <v>117</v>
@@ -9830,13 +9833,13 @@
         <v>20040</v>
       </c>
       <c r="B231" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C231" t="s">
         <v>117</v>
       </c>
       <c r="F231" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="G231" t="s">
         <v>117</v>
@@ -9847,13 +9850,13 @@
         <v>20050</v>
       </c>
       <c r="B232" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C232" t="s">
         <v>117</v>
       </c>
       <c r="F232" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="G232" t="s">
         <v>117</v>
@@ -9864,13 +9867,13 @@
         <v>20100</v>
       </c>
       <c r="B233" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C233" t="s">
         <v>117</v>
       </c>
       <c r="F233" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G233" t="s">
         <v>117</v>
@@ -9881,13 +9884,13 @@
         <v>20110</v>
       </c>
       <c r="B234" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C234" t="s">
         <v>117</v>
       </c>
       <c r="F234" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G234" t="s">
         <v>117</v>
@@ -9898,13 +9901,13 @@
         <v>20111</v>
       </c>
       <c r="B235" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C235" t="s">
         <v>117</v>
       </c>
       <c r="F235" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="G235" t="s">
         <v>117</v>
@@ -9915,13 +9918,13 @@
         <v>20120</v>
       </c>
       <c r="B236" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C236" t="s">
         <v>117</v>
       </c>
       <c r="F236" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G236" t="s">
         <v>117</v>
@@ -9932,13 +9935,13 @@
         <v>20130</v>
       </c>
       <c r="B237" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C237" t="s">
         <v>117</v>
       </c>
       <c r="F237" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G237" t="s">
         <v>117</v>
@@ -9949,13 +9952,13 @@
         <v>20200</v>
       </c>
       <c r="B238" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C238" t="s">
         <v>117</v>
       </c>
       <c r="F238" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G238" t="s">
         <v>117</v>
@@ -9966,13 +9969,13 @@
         <v>20201</v>
       </c>
       <c r="B239" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C239" t="s">
         <v>117</v>
       </c>
       <c r="F239" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G239" t="s">
         <v>117</v>
@@ -9983,13 +9986,13 @@
         <v>20210</v>
       </c>
       <c r="B240" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C240" t="s">
         <v>117</v>
       </c>
       <c r="F240" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="G240" t="s">
         <v>117</v>
@@ -10000,13 +10003,13 @@
         <v>20220</v>
       </c>
       <c r="B241" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C241" t="s">
         <v>117</v>
       </c>
       <c r="F241" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G241" t="s">
         <v>117</v>
@@ -10017,13 +10020,13 @@
         <v>20230</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C242" t="s">
         <v>117</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="G242" t="s">
         <v>117</v>
@@ -10034,13 +10037,13 @@
         <v>20240</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C243" t="s">
         <v>117</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G243" t="s">
         <v>117</v>
@@ -10051,13 +10054,13 @@
         <v>20250</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C244" t="s">
         <v>117</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="G244" t="s">
         <v>117</v>
@@ -10068,13 +10071,13 @@
         <v>20270</v>
       </c>
       <c r="B245" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C245" t="s">
         <v>117</v>
       </c>
       <c r="F245" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="G245" t="s">
         <v>117</v>
@@ -10085,13 +10088,13 @@
         <v>20280</v>
       </c>
       <c r="B246" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C246" t="s">
         <v>117</v>
       </c>
       <c r="F246" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="G246" t="s">
         <v>117</v>
@@ -10102,13 +10105,13 @@
         <v>20300</v>
       </c>
       <c r="B247" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C247" t="s">
         <v>117</v>
       </c>
       <c r="F247" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G247" t="s">
         <v>117</v>
@@ -10133,13 +10136,13 @@
         <v>20310</v>
       </c>
       <c r="B249" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C249" t="s">
         <v>117</v>
       </c>
       <c r="F249" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="G249" t="s">
         <v>117</v>
@@ -10167,13 +10170,13 @@
         <v>20330</v>
       </c>
       <c r="B251" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C251" t="s">
         <v>117</v>
       </c>
       <c r="F251" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="G251" t="s">
         <v>117</v>
@@ -10184,13 +10187,13 @@
         <v>20340</v>
       </c>
       <c r="B252" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C252" t="s">
         <v>117</v>
       </c>
       <c r="F252" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="253" spans="1:6">
@@ -10198,13 +10201,13 @@
         <v>20350</v>
       </c>
       <c r="B253" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C253" t="s">
         <v>117</v>
       </c>
       <c r="F253" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="254" customFormat="1" spans="1:6">
@@ -10212,13 +10215,13 @@
         <v>20360</v>
       </c>
       <c r="B254" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C254" t="s">
         <v>117</v>
       </c>
       <c r="F254" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="255" customFormat="1" spans="1:6">
@@ -10226,13 +10229,13 @@
         <v>20370</v>
       </c>
       <c r="B255" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C255" t="s">
         <v>117</v>
       </c>
       <c r="F255" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="256" customFormat="1" spans="1:6">
@@ -10240,13 +10243,13 @@
         <v>20380</v>
       </c>
       <c r="B256" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C256" t="s">
         <v>117</v>
       </c>
       <c r="F256" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="257" customFormat="1" spans="1:6">
@@ -10254,13 +10257,13 @@
         <v>20390</v>
       </c>
       <c r="B257" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C257" t="s">
         <v>117</v>
       </c>
       <c r="F257" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="258" customFormat="1" spans="1:6">
@@ -10268,13 +10271,13 @@
         <v>20400</v>
       </c>
       <c r="B258" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C258" t="s">
         <v>117</v>
       </c>
       <c r="F258" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="259" customFormat="1" spans="1:8">
@@ -10282,16 +10285,16 @@
         <v>20410</v>
       </c>
       <c r="B259" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C259" t="s">
         <v>117</v>
       </c>
       <c r="F259" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H259" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="260" customFormat="1" spans="1:6">
@@ -10299,13 +10302,13 @@
         <v>20411</v>
       </c>
       <c r="B260" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C260" t="s">
         <v>117</v>
       </c>
       <c r="F260" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="261" customFormat="1" spans="1:6">
@@ -10313,13 +10316,13 @@
         <v>20420</v>
       </c>
       <c r="B261" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C261" t="s">
         <v>117</v>
       </c>
       <c r="F261" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="262" customFormat="1" spans="1:6">
@@ -10327,13 +10330,13 @@
         <v>20430</v>
       </c>
       <c r="B262" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C262" t="s">
         <v>117</v>
       </c>
       <c r="F262" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="263" customFormat="1" spans="1:6">
@@ -10341,13 +10344,13 @@
         <v>20440</v>
       </c>
       <c r="B263" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C263" t="s">
         <v>117</v>
       </c>
       <c r="F263" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -10355,16 +10358,16 @@
         <v>31010</v>
       </c>
       <c r="B264" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C264" t="s">
         <v>117</v>
       </c>
       <c r="F264" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H264" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -10372,13 +10375,13 @@
         <v>31020</v>
       </c>
       <c r="B265" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C265" t="s">
         <v>117</v>
       </c>
       <c r="F265" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="266" customFormat="1" spans="1:6">
@@ -10386,13 +10389,13 @@
         <v>31030</v>
       </c>
       <c r="B266" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C266" t="s">
         <v>117</v>
       </c>
       <c r="F266" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="267" customFormat="1" spans="1:6">
@@ -10400,13 +10403,13 @@
         <v>31040</v>
       </c>
       <c r="B267" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C267" t="s">
         <v>117</v>
       </c>
       <c r="F267" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -10414,13 +10417,13 @@
         <v>31050</v>
       </c>
       <c r="B268" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C268" t="s">
         <v>117</v>
       </c>
       <c r="F268" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="269" customFormat="1" spans="1:6">
@@ -10428,13 +10431,13 @@
         <v>31060</v>
       </c>
       <c r="B269" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C269" t="s">
         <v>117</v>
       </c>
       <c r="F269" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="270" customFormat="1" spans="1:6">
@@ -10442,13 +10445,13 @@
         <v>31061</v>
       </c>
       <c r="B270" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C270" t="s">
         <v>117</v>
       </c>
       <c r="F270" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="271" customFormat="1" spans="1:7">
@@ -10456,13 +10459,13 @@
         <v>31070</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C271" t="s">
         <v>117</v>
       </c>
       <c r="F271" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="G271" t="s">
         <v>117</v>
@@ -10473,13 +10476,13 @@
         <v>31071</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C272" t="s">
         <v>117</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G272" t="s">
         <v>117</v>
@@ -10490,13 +10493,13 @@
         <v>31080</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C273" t="s">
         <v>117</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G273" t="s">
         <v>117</v>
@@ -10507,19 +10510,19 @@
         <v>32010</v>
       </c>
       <c r="B274" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C274" t="s">
         <v>117</v>
       </c>
       <c r="F274" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="G274" t="s">
         <v>117</v>
       </c>
       <c r="H274" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -10527,13 +10530,13 @@
         <v>32020</v>
       </c>
       <c r="B275" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C275" t="s">
         <v>117</v>
       </c>
       <c r="F275" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G275" t="s">
         <v>117</v>
@@ -10544,13 +10547,13 @@
         <v>32030</v>
       </c>
       <c r="B276" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C276" t="s">
         <v>117</v>
       </c>
       <c r="F276" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="G276" t="s">
         <v>117</v>
@@ -10561,13 +10564,13 @@
         <v>32040</v>
       </c>
       <c r="B277" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C277" t="s">
         <v>117</v>
       </c>
       <c r="F277" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G277" t="s">
         <v>117</v>
@@ -10578,13 +10581,13 @@
         <v>32050</v>
       </c>
       <c r="B278" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C278" t="s">
         <v>117</v>
       </c>
       <c r="F278" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G278" t="s">
         <v>117</v>
@@ -10595,13 +10598,13 @@
         <v>32060</v>
       </c>
       <c r="B279" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C279" t="s">
         <v>117</v>
       </c>
       <c r="F279" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G279" t="s">
         <v>117</v>
@@ -10612,7 +10615,7 @@
         <v>32070</v>
       </c>
       <c r="B280" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C280" t="s">
         <v>117</v>
@@ -10629,7 +10632,7 @@
         <v>32080</v>
       </c>
       <c r="B281" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C281" t="s">
         <v>117</v>
@@ -10646,13 +10649,13 @@
         <v>32090</v>
       </c>
       <c r="B282" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C282" t="s">
         <v>117</v>
       </c>
       <c r="F282" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="G282" t="s">
         <v>117</v>
@@ -10663,13 +10666,13 @@
         <v>32091</v>
       </c>
       <c r="B283" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C283" t="s">
         <v>117</v>
       </c>
       <c r="F283" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G283" t="s">
         <v>117</v>
@@ -10680,13 +10683,13 @@
         <v>32092</v>
       </c>
       <c r="B284" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C284" t="s">
         <v>117</v>
       </c>
       <c r="F284" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G284" t="s">
         <v>117</v>
@@ -10697,13 +10700,13 @@
         <v>32100</v>
       </c>
       <c r="B285" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C285" t="s">
         <v>117</v>
       </c>
       <c r="F285" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="G285" t="s">
         <v>117</v>
@@ -10714,13 +10717,13 @@
         <v>32110</v>
       </c>
       <c r="B286" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C286" t="s">
         <v>117</v>
       </c>
       <c r="F286" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="G286" t="s">
         <v>117</v>
@@ -10731,19 +10734,19 @@
         <v>33010</v>
       </c>
       <c r="B287" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C287" t="s">
         <v>117</v>
       </c>
       <c r="F287" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="G287" t="s">
         <v>117</v>
       </c>
       <c r="H287" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -10751,13 +10754,13 @@
         <v>33011</v>
       </c>
       <c r="B288" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C288" t="s">
         <v>117</v>
       </c>
       <c r="F288" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="G288" t="s">
         <v>117</v>
@@ -10785,13 +10788,13 @@
         <v>33030</v>
       </c>
       <c r="B290" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C290" t="s">
         <v>117</v>
       </c>
       <c r="F290" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="G290" t="s">
         <v>117</v>
@@ -10802,13 +10805,13 @@
         <v>33040</v>
       </c>
       <c r="B291" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C291" t="s">
         <v>117</v>
       </c>
       <c r="F291" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="G291" t="s">
         <v>117</v>
@@ -10819,19 +10822,19 @@
         <v>34010</v>
       </c>
       <c r="B292" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C292" t="s">
         <v>117</v>
       </c>
       <c r="F292" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G292" t="s">
         <v>117</v>
       </c>
       <c r="H292" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -10839,13 +10842,13 @@
         <v>34020</v>
       </c>
       <c r="B293" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C293" t="s">
         <v>117</v>
       </c>
       <c r="F293" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="G293" t="s">
         <v>117</v>
@@ -10873,13 +10876,13 @@
         <v>34040</v>
       </c>
       <c r="B295" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C295" t="s">
         <v>117</v>
       </c>
       <c r="F295" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="G295" t="s">
         <v>117</v>
@@ -10890,13 +10893,13 @@
         <v>34050</v>
       </c>
       <c r="B296" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C296" t="s">
         <v>117</v>
       </c>
       <c r="F296" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G296" t="s">
         <v>117</v>
@@ -10907,13 +10910,13 @@
         <v>34060</v>
       </c>
       <c r="B297" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C297" t="s">
         <v>117</v>
       </c>
       <c r="F297" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G297" t="s">
         <v>117</v>
@@ -10924,13 +10927,13 @@
         <v>34070</v>
       </c>
       <c r="B298" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C298" t="s">
         <v>117</v>
       </c>
       <c r="F298" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G298" t="s">
         <v>117</v>
@@ -10941,13 +10944,13 @@
         <v>35010</v>
       </c>
       <c r="B299" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C299" t="s">
         <v>117</v>
       </c>
       <c r="F299" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G299" t="s">
         <v>117</v>
@@ -10961,13 +10964,13 @@
         <v>35020</v>
       </c>
       <c r="B300" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C300" t="s">
         <v>117</v>
       </c>
       <c r="F300" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="G300" t="s">
         <v>117</v>
@@ -10978,13 +10981,13 @@
         <v>35021</v>
       </c>
       <c r="B301" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C301" t="s">
         <v>117</v>
       </c>
       <c r="F301" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G301" t="s">
         <v>117</v>
@@ -10995,13 +10998,13 @@
         <v>35030</v>
       </c>
       <c r="B302" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C302" t="s">
         <v>117</v>
       </c>
       <c r="F302" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="G302" t="s">
         <v>117</v>
@@ -11012,13 +11015,13 @@
         <v>35040</v>
       </c>
       <c r="B303" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C303" t="s">
         <v>117</v>
       </c>
       <c r="F303" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="G303" t="s">
         <v>117</v>
@@ -11029,13 +11032,13 @@
         <v>35050</v>
       </c>
       <c r="B304" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C304" t="s">
         <v>117</v>
       </c>
       <c r="F304" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="G304" t="s">
         <v>117</v>
@@ -11046,13 +11049,13 @@
         <v>35060</v>
       </c>
       <c r="B305" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C305" t="s">
         <v>117</v>
       </c>
       <c r="F305" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="G305" t="s">
         <v>117</v>
@@ -11063,19 +11066,19 @@
         <v>36010</v>
       </c>
       <c r="B306" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C306" t="s">
         <v>117</v>
       </c>
       <c r="F306" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="G306" t="s">
         <v>117</v>
       </c>
       <c r="H306" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -11083,13 +11086,13 @@
         <v>36011</v>
       </c>
       <c r="B307" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C307" t="s">
         <v>117</v>
       </c>
       <c r="F307" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="G307" t="s">
         <v>117</v>
@@ -11100,19 +11103,19 @@
         <v>37000</v>
       </c>
       <c r="B308" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C308" t="s">
         <v>117</v>
       </c>
       <c r="F308" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="G308" t="s">
         <v>117</v>
       </c>
       <c r="H308" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -11120,13 +11123,13 @@
         <v>37010</v>
       </c>
       <c r="B309" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C309" t="s">
         <v>117</v>
       </c>
       <c r="F309" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="G309" t="s">
         <v>117</v>
@@ -11137,13 +11140,13 @@
         <v>37020</v>
       </c>
       <c r="B310" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C310" t="s">
         <v>117</v>
       </c>
       <c r="F310" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="G310" t="s">
         <v>117</v>
@@ -11154,19 +11157,19 @@
         <v>38010</v>
       </c>
       <c r="B311" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C311" t="s">
         <v>117</v>
       </c>
       <c r="F311" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="G311" t="s">
         <v>117</v>
       </c>
       <c r="H311" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -11174,13 +11177,13 @@
         <v>38020</v>
       </c>
       <c r="B312" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C312" t="s">
         <v>117</v>
       </c>
       <c r="F312" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="G312" t="s">
         <v>117</v>
@@ -11191,13 +11194,13 @@
         <v>38030</v>
       </c>
       <c r="B313" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C313" t="s">
         <v>117</v>
       </c>
       <c r="F313" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G313" t="s">
         <v>117</v>
@@ -11208,7 +11211,7 @@
         <v>39010</v>
       </c>
       <c r="B314" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C314" t="s">
         <v>117</v>
@@ -11234,7 +11237,7 @@
         <v>117</v>
       </c>
       <c r="F315" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="G315" t="s">
         <v>117</v>
@@ -11245,13 +11248,13 @@
         <v>39030</v>
       </c>
       <c r="B316" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C316" t="s">
         <v>117</v>
       </c>
       <c r="F316" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G316" t="s">
         <v>117</v>
@@ -11262,13 +11265,13 @@
         <v>39040</v>
       </c>
       <c r="B317" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C317" t="s">
         <v>117</v>
       </c>
       <c r="F317" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="G317" t="s">
         <v>117</v>
@@ -11279,13 +11282,13 @@
         <v>39050</v>
       </c>
       <c r="B318" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C318" t="s">
         <v>117</v>
       </c>
       <c r="F318" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="G318" t="s">
         <v>117</v>
@@ -11296,13 +11299,13 @@
         <v>39051</v>
       </c>
       <c r="B319" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C319" t="s">
         <v>117</v>
       </c>
       <c r="F319" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="G319" t="s">
         <v>117</v>
@@ -11313,13 +11316,13 @@
         <v>39060</v>
       </c>
       <c r="B320" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C320" t="s">
         <v>117</v>
       </c>
       <c r="F320" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="G320" t="s">
         <v>117</v>
@@ -11330,13 +11333,13 @@
         <v>39070</v>
       </c>
       <c r="B321" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C321" t="s">
         <v>117</v>
       </c>
       <c r="F321" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="G321" t="s">
         <v>117</v>
@@ -11347,13 +11350,13 @@
         <v>39080</v>
       </c>
       <c r="B322" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C322" t="s">
         <v>117</v>
       </c>
       <c r="F322" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G322" t="s">
         <v>117</v>
@@ -11364,13 +11367,13 @@
         <v>39090</v>
       </c>
       <c r="B323" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C323" t="s">
         <v>117</v>
       </c>
       <c r="F323" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="G323" t="s">
         <v>117</v>
@@ -11381,7 +11384,7 @@
         <v>39100</v>
       </c>
       <c r="B324" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C324" t="s">
         <v>117</v>
@@ -11398,19 +11401,19 @@
         <v>40010</v>
       </c>
       <c r="B325" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C325" t="s">
         <v>117</v>
       </c>
       <c r="F325" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="G325" t="s">
         <v>117</v>
       </c>
       <c r="H325" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="326" spans="1:7">
@@ -11418,13 +11421,13 @@
         <v>40020</v>
       </c>
       <c r="B326" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C326" t="s">
         <v>117</v>
       </c>
       <c r="F326" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="G326" t="s">
         <v>117</v>
@@ -11435,19 +11438,19 @@
         <v>41010</v>
       </c>
       <c r="B327" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C327" t="s">
         <v>117</v>
       </c>
       <c r="F327" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="G327" t="s">
         <v>117</v>
       </c>
       <c r="H327" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="328" spans="1:8">
@@ -11455,19 +11458,19 @@
         <v>42010</v>
       </c>
       <c r="B328" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C328" t="s">
         <v>117</v>
       </c>
       <c r="F328" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="G328" t="s">
         <v>117</v>
       </c>
       <c r="H328" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="329" spans="1:7">
@@ -11475,13 +11478,13 @@
         <v>42011</v>
       </c>
       <c r="B329" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C329" t="s">
         <v>117</v>
       </c>
       <c r="F329" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="G329" t="s">
         <v>117</v>
@@ -11492,13 +11495,13 @@
         <v>42020</v>
       </c>
       <c r="B330" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C330" t="s">
         <v>117</v>
       </c>
       <c r="F330" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="G330" t="s">
         <v>117</v>
@@ -11509,13 +11512,13 @@
         <v>42030</v>
       </c>
       <c r="B331" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C331" t="s">
         <v>117</v>
       </c>
       <c r="F331" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="G331" t="s">
         <v>117</v>
@@ -11526,13 +11529,13 @@
         <v>42040</v>
       </c>
       <c r="B332" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C332" t="s">
         <v>117</v>
       </c>
       <c r="F332" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G332" t="s">
         <v>117</v>
@@ -11543,13 +11546,13 @@
         <v>43010</v>
       </c>
       <c r="B333" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C333" t="s">
         <v>117</v>
       </c>
       <c r="F333" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="G333" t="s">
         <v>117</v>
@@ -11563,13 +11566,13 @@
         <v>43020</v>
       </c>
       <c r="B334" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C334" t="s">
         <v>117</v>
       </c>
       <c r="F334" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G334" t="s">
         <v>117</v>
@@ -11580,19 +11583,19 @@
         <v>44010</v>
       </c>
       <c r="B335" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C335" t="s">
         <v>117</v>
       </c>
       <c r="F335" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="G335" t="s">
         <v>117</v>
       </c>
       <c r="H335" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="336" spans="1:8">
@@ -11600,19 +11603,19 @@
         <v>45010</v>
       </c>
       <c r="B336" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C336" t="s">
         <v>117</v>
       </c>
       <c r="F336" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="G336" t="s">
         <v>117</v>
       </c>
       <c r="H336" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="337" spans="1:7">
@@ -11620,13 +11623,13 @@
         <v>45020</v>
       </c>
       <c r="B337" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C337" t="s">
         <v>117</v>
       </c>
       <c r="F337" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="G337" t="s">
         <v>117</v>
@@ -11637,13 +11640,13 @@
         <v>45030</v>
       </c>
       <c r="B338" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C338" t="s">
         <v>117</v>
       </c>
       <c r="F338" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="G338" t="s">
         <v>117</v>
@@ -11654,19 +11657,19 @@
         <v>46010</v>
       </c>
       <c r="B339" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C339" t="s">
         <v>117</v>
       </c>
       <c r="F339" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="G339" t="s">
         <v>117</v>
       </c>
       <c r="H339" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="340" spans="1:7">
@@ -11674,13 +11677,13 @@
         <v>46020</v>
       </c>
       <c r="B340" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C340" t="s">
         <v>117</v>
       </c>
       <c r="F340" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="G340" t="s">
         <v>117</v>
@@ -11691,13 +11694,13 @@
         <v>46030</v>
       </c>
       <c r="B341" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C341" t="s">
         <v>117</v>
       </c>
       <c r="F341" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="G341" t="s">
         <v>117</v>
@@ -11708,13 +11711,13 @@
         <v>46040</v>
       </c>
       <c r="B342" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C342" t="s">
         <v>117</v>
       </c>
       <c r="F342" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="G342" t="s">
         <v>117</v>
@@ -11725,13 +11728,13 @@
         <v>46050</v>
       </c>
       <c r="B343" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C343" t="s">
         <v>117</v>
       </c>
       <c r="F343" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="G343" t="s">
         <v>117</v>
